--- a/Financial Analysis/Models.xlsx
+++ b/Financial Analysis/Models.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76C9F60C-EFE8-4EBC-9BE9-559F073A337A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA233384-99B8-451D-AF9C-77D4A0F68391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{40711DBD-7A53-4994-9FF1-9E754821B18D}"/>
   </bookViews>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="134">
   <si>
     <t>Tech</t>
   </si>
@@ -500,6 +500,9 @@
   </si>
   <si>
     <t>Do not short good companies! (maybe only at &gt;-70% and a short period of time)</t>
+  </si>
+  <si>
+    <t>For every 10 stocks, one good short, one good long?</t>
   </si>
 </sst>
 </file>
@@ -962,13 +965,13 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="M3">
-            <v>22.679034854684605</v>
+            <v>24.283566190892213</v>
           </cell>
           <cell r="T3">
-            <v>3.4178769674376195</v>
+            <v>3.6446667598884601</v>
           </cell>
           <cell r="Z3">
-            <v>-0.12975489028566323</v>
+            <v>-0.19615953856979987</v>
           </cell>
         </row>
         <row r="4">
@@ -1058,17 +1061,17 @@
         </row>
         <row r="21">
           <cell r="B21" t="str">
-            <v>Fiserv</v>
+            <v>Spotify</v>
           </cell>
         </row>
         <row r="22">
           <cell r="B22" t="str">
-            <v>Intel</v>
+            <v>Fiserv</v>
           </cell>
         </row>
         <row r="23">
           <cell r="B23" t="str">
-            <v>Spotify</v>
+            <v>Intel</v>
           </cell>
         </row>
         <row r="24">
@@ -1088,12 +1091,12 @@
         </row>
         <row r="27">
           <cell r="B27" t="str">
-            <v>Global Payments</v>
+            <v>Roblox</v>
           </cell>
         </row>
         <row r="28">
           <cell r="B28" t="str">
-            <v>Roblox</v>
+            <v>Global Payments</v>
           </cell>
         </row>
         <row r="29">
@@ -1143,12 +1146,12 @@
         </row>
         <row r="38">
           <cell r="B38" t="str">
-            <v>EPAM</v>
+            <v>Roku</v>
           </cell>
         </row>
         <row r="39">
           <cell r="B39" t="str">
-            <v>Roku</v>
+            <v>EPAM</v>
           </cell>
         </row>
         <row r="40">
@@ -1824,7 +1827,7 @@
             <v>2.2678747573429807</v>
           </cell>
           <cell r="AE3">
-            <v>-0.23973616282793675</v>
+            <v>-0.33193217039371187</v>
           </cell>
         </row>
         <row r="4">
@@ -1915,6 +1918,11 @@
         <row r="21">
           <cell r="B21" t="str">
             <v>Unusual Machines</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23" t="str">
+            <v>Embraer</v>
           </cell>
         </row>
       </sheetData>
@@ -2428,22 +2436,22 @@
       </c>
       <c r="D3" s="64">
         <f>[1]Models!$Z$3</f>
-        <v>-0.12975489028566323</v>
+        <v>-0.19615953856979987</v>
       </c>
       <c r="E3" s="66">
         <f>[1]Models!$M$3</f>
-        <v>22.679034854684605</v>
+        <v>24.283566190892213</v>
       </c>
       <c r="F3" s="67">
         <f>[1]Models!$T$3</f>
-        <v>3.4178769674376195</v>
+        <v>3.6446667598884601</v>
       </c>
       <c r="G3" s="60">
         <v>45771</v>
       </c>
       <c r="H3" s="60">
         <f ca="1">TODAY()</f>
-        <v>45783</v>
+        <v>45806</v>
       </c>
       <c r="K3" s="62" t="s">
         <v>7</v>
@@ -2497,11 +2505,11 @@
       </c>
       <c r="C6" s="63">
         <f>COUNTA([4]Main!$B$4:$B$1048576)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" s="64">
         <f>[4]Main!$AE$3</f>
-        <v>-0.23973616282793675</v>
+        <v>-0.33193217039371187</v>
       </c>
       <c r="E6" s="66">
         <f>[4]Main!$R$3</f>
@@ -2545,19 +2553,19 @@
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="C9" s="63">
         <f>SUM(C3:C8)</f>
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D9" s="64">
         <f>AVERAGE(D3:D8)</f>
-        <v>-0.33282167403068369</v>
+        <v>-0.35925511667233567</v>
       </c>
       <c r="E9" s="66">
         <f>AVERAGE(E3:E8)</f>
-        <v>23.161522967976676</v>
+        <v>23.562655802028576</v>
       </c>
       <c r="F9" s="67">
         <f>AVERAGE(F3:F8)</f>
-        <v>1.9167153540415338</v>
+        <v>1.9734128021542441</v>
       </c>
     </row>
   </sheetData>
@@ -2691,7 +2699,7 @@
     <row r="3" spans="2:20" x14ac:dyDescent="0.3">
       <c r="D3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45783</v>
+        <v>45806</v>
       </c>
       <c r="F3" s="33" t="s">
         <v>125</v>
@@ -2730,7 +2738,7 @@
       </c>
       <c r="Q3" s="29">
         <f t="shared" ref="Q3:Q10" ca="1" si="2">$D$3-I3</f>
-        <v>1652</v>
+        <v>1675</v>
       </c>
       <c r="R3" s="7">
         <f t="shared" ref="R3:R10" si="3">N3/M3-1</f>
@@ -2738,7 +2746,7 @@
       </c>
       <c r="S3" s="51">
         <f t="shared" ref="S3:S10" ca="1" si="4">R3*(12-(($D$3-I3)/30.44))</f>
-        <v>-256.21125018555927</v>
+        <v>-260.79100238826675</v>
       </c>
       <c r="T3" s="56" t="s">
         <v>124</v>
@@ -2782,7 +2790,7 @@
       </c>
       <c r="Q4" s="29">
         <f t="shared" ca="1" si="2"/>
-        <v>1611</v>
+        <v>1634</v>
       </c>
       <c r="R4" s="7">
         <f t="shared" si="3"/>
@@ -2790,7 +2798,7 @@
       </c>
       <c r="S4" s="51">
         <f t="shared" ca="1" si="4"/>
-        <v>-5.9900846437488964</v>
+        <v>-6.1006808827160999</v>
       </c>
       <c r="T4" t="s">
         <v>122</v>
@@ -2833,7 +2841,7 @@
       </c>
       <c r="Q5" s="29">
         <f t="shared" ca="1" si="2"/>
-        <v>1611</v>
+        <v>1634</v>
       </c>
       <c r="R5" s="7">
         <f t="shared" si="3"/>
@@ -2841,7 +2849,7 @@
       </c>
       <c r="S5" s="51">
         <f t="shared" ca="1" si="4"/>
-        <v>-2.6813068596390388</v>
+        <v>-2.7308124128706623</v>
       </c>
     </row>
     <row r="6" spans="2:20" x14ac:dyDescent="0.3">
@@ -2885,7 +2893,7 @@
       </c>
       <c r="Q6" s="29">
         <f t="shared" ca="1" si="2"/>
-        <v>1576</v>
+        <v>1599</v>
       </c>
       <c r="R6" s="7">
         <f t="shared" si="3"/>
@@ -2893,7 +2901,7 @@
       </c>
       <c r="S6" s="51">
         <f t="shared" ca="1" si="4"/>
-        <v>-43.031918662797729</v>
+        <v>-43.84939432128553</v>
       </c>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.3">
@@ -2939,7 +2947,7 @@
       </c>
       <c r="Q7" s="29">
         <f t="shared" ca="1" si="2"/>
-        <v>1576</v>
+        <v>1599</v>
       </c>
       <c r="R7" s="7">
         <f t="shared" si="3"/>
@@ -2947,7 +2955,7 @@
       </c>
       <c r="S7" s="51">
         <f t="shared" ca="1" si="4"/>
-        <v>-6.0530177373941232</v>
+        <v>-6.1680066761744072</v>
       </c>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.3">
@@ -2993,7 +3001,7 @@
       </c>
       <c r="Q8" s="29">
         <f t="shared" ca="1" si="2"/>
-        <v>1576</v>
+        <v>1599</v>
       </c>
       <c r="R8" s="7">
         <f t="shared" si="3"/>
@@ -3001,7 +3009,7 @@
       </c>
       <c r="S8" s="51">
         <f t="shared" ca="1" si="4"/>
-        <v>-29.285006943762895</v>
+        <v>-29.841333063515233</v>
       </c>
     </row>
     <row r="9" spans="2:20" x14ac:dyDescent="0.3">
@@ -3047,7 +3055,7 @@
       </c>
       <c r="Q9" s="29">
         <f t="shared" ca="1" si="2"/>
-        <v>1572</v>
+        <v>1595</v>
       </c>
       <c r="R9" s="7">
         <f t="shared" si="3"/>
@@ -3055,7 +3063,7 @@
       </c>
       <c r="S9" s="51">
         <f t="shared" ca="1" si="4"/>
-        <v>-12.511098186337207</v>
+        <v>-12.749558855163245</v>
       </c>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.3">
@@ -3102,7 +3110,7 @@
       </c>
       <c r="Q10" s="29">
         <f t="shared" ca="1" si="2"/>
-        <v>1517</v>
+        <v>1540</v>
       </c>
       <c r="R10" s="7">
         <f t="shared" si="3"/>
@@ -3110,7 +3118,7 @@
       </c>
       <c r="S10" s="51">
         <f t="shared" ca="1" si="4"/>
-        <v>-6.4319004805201097</v>
+        <v>-6.5603463797421098</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.3">
@@ -3194,7 +3202,7 @@
       </c>
       <c r="S13" s="42">
         <f ca="1">R13*(12-(($D$3-I13)/30.44))</f>
-        <v>-177.96385913272013</v>
+        <v>-181.14494651773984</v>
       </c>
       <c r="T13" s="26"/>
     </row>
@@ -3598,6 +3606,9 @@
       </c>
     </row>
     <row r="25" spans="2:42" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>133</v>
+      </c>
       <c r="F25" t="s">
         <v>84</v>
       </c>
@@ -4049,7 +4060,7 @@
       </c>
       <c r="Q36" s="23">
         <f ca="1">TODAY()-I36</f>
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="R36" s="22">
         <f>P36/N36-1</f>
@@ -4099,7 +4110,7 @@
       </c>
       <c r="Q37" s="21">
         <f ca="1">TODAY()-I37</f>
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="R37" s="7">
         <f>P37/N37-1</f>
@@ -4149,7 +4160,7 @@
       </c>
       <c r="Q38" s="21">
         <f ca="1">TODAY()-I38</f>
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="R38" s="7">
         <f>P38/N38-1</f>
@@ -4199,7 +4210,7 @@
       </c>
       <c r="Q39" s="21">
         <f ca="1">TODAY()-I39</f>
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="R39" s="7">
         <f>P39/N39-1</f>
@@ -5951,23 +5962,11 @@
       <c r="S91" s="7"/>
     </row>
     <row r="93" spans="6:19" x14ac:dyDescent="0.3">
-      <c r="N93" s="6">
-        <f>SUM(N85:N92)</f>
-        <v>2298.6892829606786</v>
-      </c>
-      <c r="O93" s="6">
-        <f>SUM(O85:O92)</f>
-        <v>1228.23</v>
-      </c>
-      <c r="P93" s="6">
-        <f>SUM(P85:P92)</f>
-        <v>0</v>
-      </c>
+      <c r="N93" s="6"/>
+      <c r="O93" s="6"/>
+      <c r="P93" s="6"/>
       <c r="Q93" s="4"/>
-      <c r="R93" s="5">
-        <f>P93/N93-1</f>
-        <v>-1</v>
-      </c>
+      <c r="R93" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Financial Analysis/Models.xlsx
+++ b/Financial Analysis/Models.xlsx
@@ -8,21 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0C76DDA-798A-4359-8E4C-D090E71A52C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C46595-D3E8-4AB3-B9B2-DD41C9C0656E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{40711DBD-7A53-4994-9FF1-9E754821B18D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{40711DBD-7A53-4994-9FF1-9E754821B18D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="Upgrades" sheetId="3" r:id="rId2"/>
+    <sheet name="Equity Bubbles" sheetId="5" r:id="rId3"/>
+    <sheet name="Market Bubbles" sheetId="6" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
-    <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,8 +35,248 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Anton Mniszek</author>
+  </authors>
+  <commentList>
+    <comment ref="B2" authorId="0" shapeId="0" xr:uid="{FDD54D56-CCF9-4CE7-9B21-9990BBE31B07}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+brackets means multiple bubbles (done already or tbd)
+COULD ALSO RESEARCH BOTTOMS, E.G. DOWNBEAT OR DEEP VALUE STOCKS</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{3BA14E04-B291-401D-8277-03AED154AFC5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+maybe go into more detail and then categorise averages for each reason</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{C9A059F8-94EC-49DF-BBC8-22BA2F5CE283}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+also may be the bottom or start of bullish run, not necessarily the first ever 10% day?</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{A8DF8E38-88AF-40CA-9F8E-2DCC904B1813}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+either &gt;4 days at a certain level, or &gt;5 days before next ATH? latter produces more
+orr &gt;10% drop
+for now it's just an estimate, but I think the sample data growing in abundance makes or will make the average accurate anyways</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{C14F6B2B-F9F5-4A58-982B-743C50CFCCBC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+also could do how many peaks (e.g. identifiable peaks of multiple days, how long they lasted), days of high vol/high % gain/loss, indicators at peaks or very peak, news affecting vol and peaks, and news at the peak
+then also maybe IONQ (1st time) then new row of new peak second time etc.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="0" shapeId="0" xr:uid="{9C9AF2E3-A825-426F-97FC-5549386E45C8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+usually assuming a take profit at 50%, sometimes intraday hits but often goes back up again and for a while</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R2" authorId="0" shapeId="0" xr:uid="{406B637C-6449-4F37-95D3-3376951ECFA9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+this would be interesting t model too, need t think through, maybe similar to no. of peaks? Or max rebound or something else</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{C387349A-F0CF-4164-A8DF-0AF8F89BCE90}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+outlier - &gt;9%</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Anton Mniszek</author>
+  </authors>
+  <commentList>
+    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{768F5D96-0354-4A42-9916-ECFE8FA5C786}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+5% for pre-2020 indices?</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="131">
   <si>
     <t>Tech</t>
   </si>
@@ -169,17 +411,276 @@
   </si>
   <si>
     <t>Last upgraded</t>
+  </si>
+  <si>
+    <t>KODK</t>
+  </si>
+  <si>
+    <t>BBBY</t>
+  </si>
+  <si>
+    <t>OSTK</t>
+  </si>
+  <si>
+    <t>Terra Luna</t>
+  </si>
+  <si>
+    <t>ZM</t>
+  </si>
+  <si>
+    <t>Fraud</t>
+  </si>
+  <si>
+    <t>italic = predicted</t>
+  </si>
+  <si>
+    <t>bold = ongoing</t>
+  </si>
+  <si>
+    <t>peak date + -50%</t>
+  </si>
+  <si>
+    <t>Hype</t>
+  </si>
+  <si>
+    <t>BYND</t>
+  </si>
+  <si>
+    <t>Squeeze</t>
+  </si>
+  <si>
+    <t>TLRY</t>
+  </si>
+  <si>
+    <t>Hype/fraud?</t>
+  </si>
+  <si>
+    <t>OKLO</t>
+  </si>
+  <si>
+    <t>IONQ (Q125)</t>
+  </si>
+  <si>
+    <t>RGTI (Q125)</t>
+  </si>
+  <si>
+    <t>RGTI (Q324)</t>
+  </si>
+  <si>
+    <t>IPO</t>
+  </si>
+  <si>
+    <t>RIVN</t>
+  </si>
+  <si>
+    <t>ACB (Q317)</t>
+  </si>
+  <si>
+    <t>FCEL (Q124)</t>
+  </si>
+  <si>
+    <t>Hype?</t>
+  </si>
+  <si>
+    <t>FCEL (Q114)</t>
+  </si>
+  <si>
+    <t>PLUG</t>
+  </si>
+  <si>
+    <t>SPCE (Q421)</t>
+  </si>
+  <si>
+    <t>SPCE (Q120)</t>
+  </si>
+  <si>
+    <t>AMC</t>
+  </si>
+  <si>
+    <t>PTON</t>
+  </si>
+  <si>
+    <t>LCID (Q121)</t>
+  </si>
+  <si>
+    <t>NKLA</t>
+  </si>
+  <si>
+    <t>Time to -90%</t>
+  </si>
+  <si>
+    <t>1st 90% DD Date</t>
+  </si>
+  <si>
+    <t>1st 90% DD</t>
+  </si>
+  <si>
+    <t>Max Rebound</t>
+  </si>
+  <si>
+    <t>Up Days</t>
+  </si>
+  <si>
+    <t>Period Days</t>
+  </si>
+  <si>
+    <t>Time to -75%</t>
+  </si>
+  <si>
+    <t>1st 75% DD Date</t>
+  </si>
+  <si>
+    <t>1st 75% DD</t>
+  </si>
+  <si>
+    <t>Drawdown</t>
+  </si>
+  <si>
+    <t>Trading Days</t>
+  </si>
+  <si>
+    <t>Time to -50%</t>
+  </si>
+  <si>
+    <t>1st 50% DD Date</t>
+  </si>
+  <si>
+    <t>50% DD</t>
+  </si>
+  <si>
+    <t>Time to -25%</t>
+  </si>
+  <si>
+    <t>1st 25% DD Date</t>
+  </si>
+  <si>
+    <t>25% DD</t>
+  </si>
+  <si>
+    <t>Peak Close</t>
+  </si>
+  <si>
+    <t>Time per Peak</t>
+  </si>
+  <si>
+    <t>Time to Peak</t>
+  </si>
+  <si>
+    <t>Peak Date</t>
+  </si>
+  <si>
+    <t>No. of Peaks</t>
+  </si>
+  <si>
+    <t>1st &gt;10% Day</t>
+  </si>
+  <si>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>Ticker</t>
+  </si>
+  <si>
+    <t>Main</t>
+  </si>
+  <si>
+    <t>IONQ (Q324)</t>
+  </si>
+  <si>
+    <t>Hype/IPO</t>
+  </si>
+  <si>
+    <t>BBAI (Q123)</t>
+  </si>
+  <si>
+    <t>BBAI (Q122)</t>
+  </si>
+  <si>
+    <t>BBAI (Q125)</t>
+  </si>
+  <si>
+    <t>VOW</t>
+  </si>
+  <si>
+    <t>GME (Q320)</t>
+  </si>
+  <si>
+    <t>KTOS</t>
+  </si>
+  <si>
+    <t>MSTR</t>
+  </si>
+  <si>
+    <t>JOBY</t>
+  </si>
+  <si>
+    <t>ACHR</t>
+  </si>
+  <si>
+    <t>DUOL</t>
+  </si>
+  <si>
+    <t>QBTS</t>
+  </si>
+  <si>
+    <t>QUBT</t>
+  </si>
+  <si>
+    <t>HOOD</t>
+  </si>
+  <si>
+    <t>SOUN</t>
+  </si>
+  <si>
+    <t>TEM</t>
+  </si>
+  <si>
+    <t>Hype/fraud</t>
+  </si>
+  <si>
+    <t>CRWV</t>
+  </si>
+  <si>
+    <t>CRCL</t>
+  </si>
+  <si>
+    <t>SYM</t>
+  </si>
+  <si>
+    <t>SPY (Q225)</t>
+  </si>
+  <si>
+    <t>QQQ (Q299)</t>
+  </si>
+  <si>
+    <t>SPY (Q108)</t>
+  </si>
+  <si>
+    <t>BTC</t>
+  </si>
+  <si>
+    <t>XAU/USD</t>
+  </si>
+  <si>
+    <t>PLTR</t>
+  </si>
+  <si>
+    <t>can take very long for large mcap stocks to peak? (PLTR, PTON, DUOL) perhaps cause of beta and passive investing</t>
+  </si>
+  <si>
+    <t>efficient to take profits at -25%? explore with more %'s</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="170" formatCode="0\x"/>
-    <numFmt numFmtId="171" formatCode="0.0\x"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0\x"/>
+    <numFmt numFmtId="165" formatCode="0.0\x"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,8 +757,100 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="5" tint="0.39997558519241921"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="5" tint="0.39997558519241921"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -309,8 +902,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -399,15 +998,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -443,19 +1059,101 @@
     <xf numFmtId="0" fontId="7" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="7" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="15" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="15" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="15" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="15" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="8" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="16" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="8" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="17" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="8" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="14" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="18" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="8" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="8" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="19" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="23" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="7">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Hyperlink" xfId="4" builtinId="8"/>
+    <cellStyle name="Hyperlink 2" xfId="6" xr:uid="{2D3C89F8-AEE2-48DC-8478-074498FD1787}"/>
     <cellStyle name="Neutral" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="5" xr:uid="{6BCB83A4-1E91-4648-82AA-D35DEF998E24}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -904,7 +1602,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1076,7 +1774,7 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="O3">
-            <v>29.924485010131235</v>
+            <v>30.068644764713405</v>
           </cell>
           <cell r="U3">
             <v>0.99923487105066666</v>
@@ -1355,66 +2053,71 @@
         </row>
         <row r="17">
           <cell r="B17" t="str">
-            <v>Dassault</v>
+            <v>Anduril</v>
           </cell>
         </row>
         <row r="18">
           <cell r="B18" t="str">
-            <v>Leonardo</v>
+            <v>Dassault</v>
           </cell>
         </row>
         <row r="19">
           <cell r="B19" t="str">
-            <v>Leidos</v>
+            <v>Leonardo</v>
           </cell>
         </row>
         <row r="20">
           <cell r="B20" t="str">
-            <v>Bombardier</v>
+            <v>Leidos</v>
           </cell>
         </row>
         <row r="21">
           <cell r="B21" t="str">
-            <v>Textron</v>
+            <v>Bombardier</v>
           </cell>
         </row>
         <row r="22">
           <cell r="B22" t="str">
-            <v>Embraer</v>
+            <v>Textron</v>
           </cell>
         </row>
         <row r="23">
           <cell r="B23" t="str">
-            <v>Hensoldt</v>
+            <v>Embraer</v>
           </cell>
         </row>
         <row r="24">
           <cell r="B24" t="str">
-            <v>Kratos</v>
+            <v>Hensoldt</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25" t="str">
-            <v>Norinco</v>
+            <v>Kratos</v>
           </cell>
         </row>
         <row r="26">
           <cell r="B26" t="str">
-            <v>Renk</v>
+            <v>Norinco</v>
           </cell>
         </row>
         <row r="27">
           <cell r="B27" t="str">
-            <v>Red Cat</v>
+            <v>Renk</v>
           </cell>
         </row>
         <row r="28">
           <cell r="B28" t="str">
+            <v>Red Cat</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29" t="str">
             <v>Unusual Machines</v>
           </cell>
         </row>
-        <row r="29">
-          <cell r="B29"/>
+        <row r="30">
+          <cell r="B30"/>
         </row>
       </sheetData>
     </sheetDataSet>
@@ -1479,8 +2182,8 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="AB3">
-            <v>-0.83979249526057242</v>
+          <cell r="AC3">
+            <v>-0.83830827653230344</v>
           </cell>
         </row>
         <row r="4">
@@ -1875,11 +2578,11 @@
         <v>4.1199516612244071</v>
       </c>
       <c r="G3" s="15">
-        <v>45771</v>
+        <v>45932</v>
       </c>
       <c r="H3" s="15">
         <f ca="1">TODAY()</f>
-        <v>45928</v>
+        <v>45932</v>
       </c>
       <c r="K3" s="17" t="s">
         <v>7</v>
@@ -1920,7 +2623,7 @@
       </c>
       <c r="E5" s="21">
         <f>[3]Main!$O$3</f>
-        <v>29.924485010131235</v>
+        <v>30.068644764713405</v>
       </c>
       <c r="F5" s="22">
         <f>[3]Main!$U$3</f>
@@ -1933,7 +2636,7 @@
       </c>
       <c r="C6" s="18">
         <f>COUNTA([4]Main!$B$4:$B$1048576)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="19">
         <f>[4]Main!$AE$3</f>
@@ -1985,8 +2688,8 @@
         <v>6</v>
       </c>
       <c r="D8" s="19">
-        <f>[6]Main!$AB$3</f>
-        <v>-0.83979249526057242</v>
+        <f>[6]Main!$AC$3</f>
+        <v>-0.83830827653230344</v>
       </c>
       <c r="E8" s="21"/>
       <c r="F8" s="20"/>
@@ -2003,15 +2706,15 @@
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C9" s="18">
         <f>SUM(C3:C8)</f>
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D9" s="19">
         <f>AVERAGE(D3:D8)</f>
-        <v>-0.44210349438283769</v>
+        <v>-0.4418561245947929</v>
       </c>
       <c r="E9" s="21">
         <f>AVERAGE(E3:E8)</f>
-        <v>27.120191910157992</v>
+        <v>27.156231848803536</v>
       </c>
       <c r="F9" s="22">
         <f>AVERAGE(F3:F8)</f>
@@ -2104,65 +2807,2631 @@
   <dimension ref="B3:B13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="105.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="42"/>
+    <col min="2" max="2" width="105.44140625" style="42" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="42"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="43" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="43" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="43" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
+      <c r="B7" s="42" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
+      <c r="B8" s="42" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="43" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="43" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
+      <c r="B11" s="42" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
+      <c r="B12" s="42" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
+      <c r="B13" s="42" t="s">
         <v>43</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04147068-271F-415A-A4EA-D0D6DE05E2E6}">
+  <dimension ref="A1:AC55"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.44140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" style="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" style="25" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.77734375" style="34" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.44140625" style="29" customWidth="1"/>
+    <col min="11" max="11" width="15.21875" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.44140625" style="34" customWidth="1"/>
+    <col min="13" max="13" width="10.44140625" style="29" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15" style="25" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.44140625" style="25" customWidth="1"/>
+    <col min="16" max="16" width="12" style="25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.109375" style="25" customWidth="1"/>
+    <col min="19" max="19" width="10.88671875" style="25" customWidth="1"/>
+    <col min="20" max="20" width="11.44140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11.44140625" style="24" customWidth="1"/>
+    <col min="22" max="22" width="11.44140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.44140625" style="24" customWidth="1"/>
+    <col min="26" max="26" width="8.88671875" style="24"/>
+    <col min="27" max="28" width="10.44140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" s="41">
+        <f>AVERAGE(E3:E103)</f>
+        <v>4.1212121212121211</v>
+      </c>
+      <c r="F1" s="40"/>
+      <c r="G1" s="39">
+        <f>AVERAGE(G3:G103)</f>
+        <v>116.81818181818181</v>
+      </c>
+      <c r="H1" s="39">
+        <f>AVERAGE(H3:H103)</f>
+        <v>27.084848484848486</v>
+      </c>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="39">
+        <f>AVERAGE(L3:L103)</f>
+        <v>11.178571428571429</v>
+      </c>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="39">
+        <f ca="1">AVERAGE(O3:O103)</f>
+        <v>43.25</v>
+      </c>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="V1" s="26">
+        <f>AVERAGE(V4:V41)</f>
+        <v>297.125</v>
+      </c>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="AB1" s="26">
+        <f>AVERAGE(AB4:AB41)</f>
+        <v>705.5</v>
+      </c>
+      <c r="AC1" s="26"/>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B2" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="J2" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="K2" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="L2" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="M2" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="N2" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="O2" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="P2" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q2" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="R2" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="S2" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="T2" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="U2" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="V2" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="W2" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="X2" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y2" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z2" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA2" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB2" s="25" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B3" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="27">
+        <v>39707</v>
+      </c>
+      <c r="E3" s="25">
+        <v>3</v>
+      </c>
+      <c r="F3" s="27">
+        <v>39749</v>
+      </c>
+      <c r="G3" s="25">
+        <f t="shared" ref="G3:G35" si="0">F3-D3</f>
+        <v>42</v>
+      </c>
+      <c r="H3" s="25">
+        <f t="shared" ref="H3:H35" si="1">G3/E3</f>
+        <v>14</v>
+      </c>
+      <c r="I3" s="29">
+        <v>945</v>
+      </c>
+      <c r="J3" s="29">
+        <f t="shared" ref="J3:J35" si="2">I3*0.75</f>
+        <v>708.75</v>
+      </c>
+      <c r="K3" s="27">
+        <v>39750</v>
+      </c>
+      <c r="L3" s="25">
+        <f t="shared" ref="L3:L26" si="3">K3-F3</f>
+        <v>1</v>
+      </c>
+      <c r="M3" s="29">
+        <f t="shared" ref="M3:M35" si="4">I3*0.5</f>
+        <v>472.5</v>
+      </c>
+      <c r="N3" s="27">
+        <v>39755</v>
+      </c>
+      <c r="O3" s="28">
+        <f t="shared" ref="O3:O26" si="5">+N3-F3</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B4" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4" s="27">
+        <v>41642</v>
+      </c>
+      <c r="E4" s="25">
+        <v>2</v>
+      </c>
+      <c r="F4" s="27">
+        <v>41708</v>
+      </c>
+      <c r="G4" s="25">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="H4" s="25">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="I4" s="29">
+        <v>16984.39</v>
+      </c>
+      <c r="J4" s="29">
+        <f t="shared" si="2"/>
+        <v>12738.2925</v>
+      </c>
+      <c r="K4" s="27">
+        <v>41715</v>
+      </c>
+      <c r="L4" s="25">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="M4" s="29">
+        <f t="shared" si="4"/>
+        <v>8492.1949999999997</v>
+      </c>
+      <c r="N4" s="27">
+        <v>41767</v>
+      </c>
+      <c r="O4" s="28">
+        <f t="shared" si="5"/>
+        <v>59</v>
+      </c>
+      <c r="S4" s="30">
+        <f t="shared" ref="S4:S11" si="6">+M4/I4-1</f>
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B5" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="27">
+        <v>43045</v>
+      </c>
+      <c r="E5" s="25">
+        <v>4</v>
+      </c>
+      <c r="F5" s="27">
+        <v>43123</v>
+      </c>
+      <c r="G5" s="25">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="H5" s="34">
+        <f t="shared" si="1"/>
+        <v>19.5</v>
+      </c>
+      <c r="I5" s="29">
+        <v>1774.8</v>
+      </c>
+      <c r="J5" s="29">
+        <f t="shared" si="2"/>
+        <v>1331.1</v>
+      </c>
+      <c r="K5" s="27">
+        <v>43132</v>
+      </c>
+      <c r="L5" s="25">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="M5" s="29">
+        <f t="shared" si="4"/>
+        <v>887.4</v>
+      </c>
+      <c r="N5" s="27">
+        <v>43136</v>
+      </c>
+      <c r="O5" s="25">
+        <f t="shared" si="5"/>
+        <v>13</v>
+      </c>
+      <c r="S5" s="25">
+        <f t="shared" si="6"/>
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B6" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="27">
+        <v>43327</v>
+      </c>
+      <c r="E6" s="25">
+        <v>2</v>
+      </c>
+      <c r="F6" s="27">
+        <v>43362</v>
+      </c>
+      <c r="G6" s="25">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="H6" s="34">
+        <f t="shared" si="1"/>
+        <v>17.5</v>
+      </c>
+      <c r="I6" s="29">
+        <v>214.06</v>
+      </c>
+      <c r="J6" s="29">
+        <f t="shared" si="2"/>
+        <v>160.54500000000002</v>
+      </c>
+      <c r="K6" s="27">
+        <v>43364</v>
+      </c>
+      <c r="L6" s="34">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="M6" s="29">
+        <f t="shared" si="4"/>
+        <v>107.03</v>
+      </c>
+      <c r="N6" s="27">
+        <v>43367</v>
+      </c>
+      <c r="O6" s="28">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="30">
+        <f t="shared" si="6"/>
+        <v>-0.5</v>
+      </c>
+      <c r="T6" s="31">
+        <v>53.52</v>
+      </c>
+      <c r="U6" s="32">
+        <v>43566</v>
+      </c>
+      <c r="V6" s="33">
+        <f t="shared" ref="V6:V11" si="7">+U6-F6</f>
+        <v>204</v>
+      </c>
+      <c r="W6" s="33"/>
+      <c r="X6" s="33"/>
+      <c r="Y6" s="33"/>
+      <c r="Z6" s="31">
+        <v>20.65</v>
+      </c>
+      <c r="AA6" s="32">
+        <v>43748</v>
+      </c>
+      <c r="AB6" s="33">
+        <f>+AA6-F6</f>
+        <v>386</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B7" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="27">
+        <v>43591</v>
+      </c>
+      <c r="E7" s="25">
+        <v>6</v>
+      </c>
+      <c r="F7" s="27">
+        <v>43642</v>
+      </c>
+      <c r="G7" s="25">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="H7" s="34">
+        <f t="shared" si="1"/>
+        <v>8.5</v>
+      </c>
+      <c r="I7" s="29">
+        <v>234.9</v>
+      </c>
+      <c r="J7" s="29">
+        <f t="shared" si="2"/>
+        <v>176.17500000000001</v>
+      </c>
+      <c r="K7" s="27">
+        <v>43678</v>
+      </c>
+      <c r="L7" s="34">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="M7" s="29">
+        <f t="shared" si="4"/>
+        <v>117.45</v>
+      </c>
+      <c r="N7" s="27">
+        <v>43755</v>
+      </c>
+      <c r="O7" s="28">
+        <f t="shared" si="5"/>
+        <v>113</v>
+      </c>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="30">
+        <f t="shared" si="6"/>
+        <v>-0.5</v>
+      </c>
+      <c r="T7" s="24">
+        <v>54.02</v>
+      </c>
+      <c r="U7" s="32">
+        <v>43908</v>
+      </c>
+      <c r="V7" s="33">
+        <f t="shared" si="7"/>
+        <v>266</v>
+      </c>
+      <c r="W7" s="33"/>
+      <c r="X7" s="33"/>
+      <c r="Y7" s="33"/>
+      <c r="Z7" s="24">
+        <v>22.86</v>
+      </c>
+      <c r="AA7" s="32">
+        <v>44721</v>
+      </c>
+      <c r="AB7" s="33">
+        <f>+AA7-F7</f>
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B8" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="27">
+        <v>43808</v>
+      </c>
+      <c r="E8" s="25">
+        <v>2</v>
+      </c>
+      <c r="F8" s="27">
+        <v>43880</v>
+      </c>
+      <c r="G8" s="28">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="H8" s="28">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="I8" s="29">
+        <v>747</v>
+      </c>
+      <c r="J8" s="29">
+        <f t="shared" si="2"/>
+        <v>560.25</v>
+      </c>
+      <c r="K8" s="27">
+        <v>43887</v>
+      </c>
+      <c r="L8" s="25">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="M8" s="29">
+        <f t="shared" si="4"/>
+        <v>373.5</v>
+      </c>
+      <c r="N8" s="27">
+        <v>43899</v>
+      </c>
+      <c r="O8" s="28">
+        <f t="shared" si="5"/>
+        <v>19</v>
+      </c>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="28"/>
+      <c r="S8" s="30">
+        <f t="shared" si="6"/>
+        <v>-0.5</v>
+      </c>
+      <c r="T8" s="31">
+        <v>267.60000000000002</v>
+      </c>
+      <c r="U8" s="32">
+        <v>44561</v>
+      </c>
+      <c r="V8" s="33">
+        <f t="shared" si="7"/>
+        <v>681</v>
+      </c>
+      <c r="W8" s="33"/>
+      <c r="X8" s="33"/>
+      <c r="Y8" s="33"/>
+      <c r="Z8" s="31">
+        <v>106.2</v>
+      </c>
+      <c r="AA8" s="32">
+        <v>44820</v>
+      </c>
+      <c r="AB8" s="33">
+        <f>+AA8-F8</f>
+        <v>940</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B9" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="27">
+        <v>43893</v>
+      </c>
+      <c r="E9" s="25">
+        <v>3</v>
+      </c>
+      <c r="F9" s="27">
+        <v>43991</v>
+      </c>
+      <c r="G9" s="28">
+        <f t="shared" si="0"/>
+        <v>98</v>
+      </c>
+      <c r="H9" s="28">
+        <f t="shared" si="1"/>
+        <v>32.666666666666664</v>
+      </c>
+      <c r="I9" s="29">
+        <v>2391.92</v>
+      </c>
+      <c r="J9" s="29">
+        <f t="shared" si="2"/>
+        <v>1793.94</v>
+      </c>
+      <c r="K9" s="27">
+        <v>43993</v>
+      </c>
+      <c r="L9" s="25">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="M9" s="29">
+        <f t="shared" si="4"/>
+        <v>1195.96</v>
+      </c>
+      <c r="N9" s="27">
+        <v>44032</v>
+      </c>
+      <c r="O9" s="28">
+        <f t="shared" si="5"/>
+        <v>41</v>
+      </c>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="30">
+        <f t="shared" si="6"/>
+        <v>-0.5</v>
+      </c>
+      <c r="T9" s="31">
+        <v>573.00570000000005</v>
+      </c>
+      <c r="U9" s="32">
+        <v>44098</v>
+      </c>
+      <c r="V9" s="33">
+        <f t="shared" si="7"/>
+        <v>107</v>
+      </c>
+      <c r="W9" s="33"/>
+      <c r="X9" s="33"/>
+      <c r="Y9" s="33"/>
+      <c r="Z9" s="31">
+        <f>+I9*0.1</f>
+        <v>239.19200000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B10" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="27">
+        <v>43906</v>
+      </c>
+      <c r="E10" s="25">
+        <v>6</v>
+      </c>
+      <c r="F10" s="27">
+        <v>44209</v>
+      </c>
+      <c r="G10" s="28">
+        <f t="shared" si="0"/>
+        <v>303</v>
+      </c>
+      <c r="H10" s="28">
+        <f t="shared" si="1"/>
+        <v>50.5</v>
+      </c>
+      <c r="I10" s="29">
+        <v>167.42</v>
+      </c>
+      <c r="J10" s="29">
+        <f t="shared" si="2"/>
+        <v>125.565</v>
+      </c>
+      <c r="K10" s="27">
+        <v>44249</v>
+      </c>
+      <c r="L10" s="25">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="M10" s="29">
+        <f t="shared" si="4"/>
+        <v>83.71</v>
+      </c>
+      <c r="N10" s="27">
+        <v>44321</v>
+      </c>
+      <c r="O10" s="28">
+        <f t="shared" si="5"/>
+        <v>112</v>
+      </c>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="28"/>
+      <c r="S10" s="30">
+        <f t="shared" si="6"/>
+        <v>-0.5</v>
+      </c>
+      <c r="T10" s="24">
+        <v>41.78</v>
+      </c>
+      <c r="U10" s="32">
+        <v>44537</v>
+      </c>
+      <c r="V10" s="33">
+        <f t="shared" si="7"/>
+        <v>328</v>
+      </c>
+      <c r="W10" s="33"/>
+      <c r="X10" s="33"/>
+      <c r="Y10" s="33"/>
+      <c r="Z10" s="31">
+        <v>15.7</v>
+      </c>
+      <c r="AA10" s="32">
+        <v>44687</v>
+      </c>
+      <c r="AB10" s="33">
+        <f>+AA10-F10</f>
+        <v>478</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B11" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="27">
+        <v>43986</v>
+      </c>
+      <c r="E11" s="25">
+        <v>5</v>
+      </c>
+      <c r="F11" s="27">
+        <v>44222</v>
+      </c>
+      <c r="G11" s="25">
+        <f t="shared" si="0"/>
+        <v>236</v>
+      </c>
+      <c r="H11" s="28">
+        <f t="shared" si="1"/>
+        <v>47.2</v>
+      </c>
+      <c r="I11" s="29">
+        <v>73.180000000000007</v>
+      </c>
+      <c r="J11" s="29">
+        <f t="shared" si="2"/>
+        <v>54.885000000000005</v>
+      </c>
+      <c r="K11" s="27">
+        <v>44243</v>
+      </c>
+      <c r="L11" s="25">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="M11" s="29">
+        <f t="shared" si="4"/>
+        <v>36.590000000000003</v>
+      </c>
+      <c r="N11" s="27">
+        <v>44260</v>
+      </c>
+      <c r="O11" s="28">
+        <f t="shared" si="5"/>
+        <v>38</v>
+      </c>
+      <c r="S11" s="30">
+        <f t="shared" si="6"/>
+        <v>-0.5</v>
+      </c>
+      <c r="U11" s="32">
+        <v>44327</v>
+      </c>
+      <c r="V11" s="33">
+        <f t="shared" si="7"/>
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B12" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="27">
+        <v>44074</v>
+      </c>
+      <c r="E12" s="25">
+        <v>6</v>
+      </c>
+      <c r="F12" s="27">
+        <v>44223</v>
+      </c>
+      <c r="G12" s="25">
+        <f t="shared" si="0"/>
+        <v>149</v>
+      </c>
+      <c r="H12" s="34">
+        <f t="shared" si="1"/>
+        <v>24.833333333333332</v>
+      </c>
+      <c r="I12" s="29">
+        <v>86.88</v>
+      </c>
+      <c r="J12" s="29">
+        <f t="shared" si="2"/>
+        <v>65.16</v>
+      </c>
+      <c r="K12" s="27">
+        <v>44229</v>
+      </c>
+      <c r="L12" s="34">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="M12" s="29">
+        <f t="shared" si="4"/>
+        <v>43.44</v>
+      </c>
+      <c r="N12" s="27">
+        <v>44229</v>
+      </c>
+      <c r="O12" s="28">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="V12" s="33"/>
+      <c r="W12" s="33"/>
+      <c r="X12" s="33"/>
+      <c r="Y12" s="33"/>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B13" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="27">
+        <v>44098</v>
+      </c>
+      <c r="E13" s="25">
+        <v>3</v>
+      </c>
+      <c r="F13" s="27">
+        <v>44238</v>
+      </c>
+      <c r="G13" s="28">
+        <f t="shared" si="0"/>
+        <v>140</v>
+      </c>
+      <c r="H13" s="28">
+        <f t="shared" si="1"/>
+        <v>46.666666666666664</v>
+      </c>
+      <c r="I13" s="29">
+        <v>1188.2</v>
+      </c>
+      <c r="J13" s="29">
+        <f t="shared" si="2"/>
+        <v>891.15000000000009</v>
+      </c>
+      <c r="K13" s="27">
+        <v>44250</v>
+      </c>
+      <c r="L13" s="25">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="M13" s="29">
+        <f t="shared" si="4"/>
+        <v>594.1</v>
+      </c>
+      <c r="N13" s="27">
+        <v>44260</v>
+      </c>
+      <c r="O13" s="28">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
+      <c r="P13" s="28"/>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="28"/>
+      <c r="S13" s="30"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="32"/>
+      <c r="V13" s="33"/>
+      <c r="W13" s="33"/>
+      <c r="X13" s="33"/>
+      <c r="Y13" s="33"/>
+      <c r="Z13" s="31"/>
+      <c r="AA13" s="32"/>
+      <c r="AB13" s="33"/>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B14" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="27">
+        <v>44111</v>
+      </c>
+      <c r="E14" s="25">
+        <v>4</v>
+      </c>
+      <c r="F14" s="27">
+        <v>44236</v>
+      </c>
+      <c r="G14" s="25">
+        <f t="shared" si="0"/>
+        <v>125</v>
+      </c>
+      <c r="H14" s="34">
+        <f t="shared" si="1"/>
+        <v>31.25</v>
+      </c>
+      <c r="I14" s="29">
+        <v>838.8</v>
+      </c>
+      <c r="J14" s="29">
+        <f t="shared" si="2"/>
+        <v>629.09999999999991</v>
+      </c>
+      <c r="K14" s="27">
+        <v>44245</v>
+      </c>
+      <c r="L14" s="25">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="M14" s="29">
+        <f t="shared" si="4"/>
+        <v>419.4</v>
+      </c>
+      <c r="N14" s="27">
+        <v>44250</v>
+      </c>
+      <c r="O14" s="28">
+        <f t="shared" si="5"/>
+        <v>14</v>
+      </c>
+      <c r="S14" s="30">
+        <f>+M14/I14-1</f>
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B15" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="27">
+        <v>44207</v>
+      </c>
+      <c r="E15" s="25">
+        <v>1</v>
+      </c>
+      <c r="F15" s="27">
+        <v>44245</v>
+      </c>
+      <c r="G15" s="28">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="H15" s="28">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="I15" s="29">
+        <v>580.5</v>
+      </c>
+      <c r="J15" s="29">
+        <f t="shared" si="2"/>
+        <v>435.375</v>
+      </c>
+      <c r="K15" s="27">
+        <v>44250</v>
+      </c>
+      <c r="L15" s="25">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="M15" s="29">
+        <f t="shared" si="4"/>
+        <v>290.25</v>
+      </c>
+      <c r="N15" s="27">
+        <v>44251</v>
+      </c>
+      <c r="O15" s="28">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="28"/>
+      <c r="R15" s="28"/>
+      <c r="S15" s="30">
+        <f>+M15/I15-1</f>
+        <v>-0.5</v>
+      </c>
+      <c r="T15" s="24">
+        <v>138.6</v>
+      </c>
+      <c r="U15" s="32">
+        <v>44692</v>
+      </c>
+      <c r="V15" s="33">
+        <f>+U15-F15</f>
+        <v>447</v>
+      </c>
+      <c r="W15" s="33"/>
+      <c r="X15" s="33"/>
+      <c r="Y15" s="33"/>
+      <c r="Z15" s="24">
+        <v>57.3</v>
+      </c>
+      <c r="AA15" s="32">
+        <v>45099</v>
+      </c>
+      <c r="AB15" s="33">
+        <f>+AA15-F15</f>
+        <v>854</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B16" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="27">
+        <v>44215</v>
+      </c>
+      <c r="E16" s="25">
+        <v>3</v>
+      </c>
+      <c r="F16" s="27">
+        <v>44349</v>
+      </c>
+      <c r="G16" s="28">
+        <f t="shared" si="0"/>
+        <v>134</v>
+      </c>
+      <c r="H16" s="28">
+        <f t="shared" si="1"/>
+        <v>44.666666666666664</v>
+      </c>
+      <c r="I16" s="29">
+        <v>339.05</v>
+      </c>
+      <c r="J16" s="29">
+        <f t="shared" si="2"/>
+        <v>254.28750000000002</v>
+      </c>
+      <c r="K16" s="27">
+        <v>44357</v>
+      </c>
+      <c r="L16" s="25">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="M16" s="29">
+        <f t="shared" si="4"/>
+        <v>169.52500000000001</v>
+      </c>
+      <c r="N16" s="27">
+        <v>44396</v>
+      </c>
+      <c r="O16" s="28">
+        <f t="shared" si="5"/>
+        <v>47</v>
+      </c>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="30">
+        <f>+M16/I16-1</f>
+        <v>-0.5</v>
+      </c>
+      <c r="T16" s="31">
+        <f>+I16*0.25</f>
+        <v>84.762500000000003</v>
+      </c>
+      <c r="U16" s="32">
+        <v>44588</v>
+      </c>
+      <c r="V16" s="33">
+        <f>+U16-F16</f>
+        <v>239</v>
+      </c>
+      <c r="W16" s="33"/>
+      <c r="X16" s="33"/>
+      <c r="Y16" s="33"/>
+      <c r="Z16" s="31">
+        <v>61.2</v>
+      </c>
+      <c r="AA16" s="32">
+        <v>44845</v>
+      </c>
+      <c r="AB16" s="33">
+        <f>+AA16-F16</f>
+        <v>496</v>
+      </c>
+    </row>
+    <row r="17" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B17" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="27">
+        <v>44510</v>
+      </c>
+      <c r="E17" s="25">
+        <v>1</v>
+      </c>
+      <c r="F17" s="27">
+        <v>44516</v>
+      </c>
+      <c r="G17" s="25">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="H17" s="34">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="I17" s="29">
+        <v>172.01</v>
+      </c>
+      <c r="J17" s="29">
+        <f t="shared" si="2"/>
+        <v>129.00749999999999</v>
+      </c>
+      <c r="K17" s="27">
+        <v>44518</v>
+      </c>
+      <c r="L17" s="25">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="M17" s="29">
+        <f t="shared" si="4"/>
+        <v>86.004999999999995</v>
+      </c>
+      <c r="N17" s="27">
+        <v>44567</v>
+      </c>
+      <c r="O17" s="28">
+        <f t="shared" si="5"/>
+        <v>51</v>
+      </c>
+      <c r="V17" s="33"/>
+      <c r="W17" s="33"/>
+      <c r="X17" s="33"/>
+      <c r="Y17" s="33"/>
+    </row>
+    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B18" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="27">
+        <v>44617</v>
+      </c>
+      <c r="E18" s="25">
+        <v>3</v>
+      </c>
+      <c r="F18" s="27">
+        <v>44664</v>
+      </c>
+      <c r="G18" s="25">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="H18" s="34">
+        <f t="shared" si="1"/>
+        <v>15.666666666666666</v>
+      </c>
+      <c r="I18" s="29">
+        <v>12.69</v>
+      </c>
+      <c r="J18" s="29">
+        <f t="shared" si="2"/>
+        <v>9.5175000000000001</v>
+      </c>
+      <c r="K18" s="27">
+        <v>44673</v>
+      </c>
+      <c r="L18" s="34">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="M18" s="29">
+        <f t="shared" si="4"/>
+        <v>6.3449999999999998</v>
+      </c>
+      <c r="N18" s="27">
+        <v>44705</v>
+      </c>
+      <c r="O18" s="28">
+        <f t="shared" si="5"/>
+        <v>41</v>
+      </c>
+      <c r="V18" s="33"/>
+      <c r="W18" s="33"/>
+      <c r="X18" s="33"/>
+      <c r="Y18" s="33"/>
+    </row>
+    <row r="19" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B19" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="27">
+        <v>44938</v>
+      </c>
+      <c r="E19" s="25">
+        <v>3</v>
+      </c>
+      <c r="F19" s="27">
+        <v>44963</v>
+      </c>
+      <c r="G19" s="25">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="H19" s="34">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333339</v>
+      </c>
+      <c r="I19" s="29">
+        <v>6.11</v>
+      </c>
+      <c r="J19" s="29">
+        <f t="shared" si="2"/>
+        <v>4.5825000000000005</v>
+      </c>
+      <c r="K19" s="27">
+        <v>44970</v>
+      </c>
+      <c r="L19" s="34">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="M19" s="29">
+        <f t="shared" si="4"/>
+        <v>3.0550000000000002</v>
+      </c>
+      <c r="N19" s="27">
+        <v>44985</v>
+      </c>
+      <c r="O19" s="28">
+        <f t="shared" si="5"/>
+        <v>22</v>
+      </c>
+      <c r="V19" s="33"/>
+      <c r="W19" s="33"/>
+      <c r="X19" s="33"/>
+      <c r="Y19" s="33"/>
+    </row>
+    <row r="20" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B20" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="27">
+        <v>45488</v>
+      </c>
+      <c r="E20" s="25">
+        <v>5</v>
+      </c>
+      <c r="F20" s="27">
+        <v>45616</v>
+      </c>
+      <c r="G20" s="25">
+        <f t="shared" si="0"/>
+        <v>128</v>
+      </c>
+      <c r="H20" s="34">
+        <f t="shared" si="1"/>
+        <v>25.6</v>
+      </c>
+      <c r="I20" s="29">
+        <v>473.83</v>
+      </c>
+      <c r="J20" s="29">
+        <f t="shared" si="2"/>
+        <v>355.3725</v>
+      </c>
+      <c r="K20" s="27">
+        <v>45622</v>
+      </c>
+      <c r="L20" s="34">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="M20" s="29">
+        <f t="shared" si="4"/>
+        <v>236.91499999999999</v>
+      </c>
+      <c r="N20" s="27">
+        <v>45716</v>
+      </c>
+      <c r="O20" s="25">
+        <f t="shared" si="5"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B21" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="27">
+        <v>45512</v>
+      </c>
+      <c r="E21" s="25">
+        <v>6</v>
+      </c>
+      <c r="F21" s="27">
+        <v>45791</v>
+      </c>
+      <c r="G21" s="25">
+        <f t="shared" si="0"/>
+        <v>279</v>
+      </c>
+      <c r="H21" s="34">
+        <f t="shared" si="1"/>
+        <v>46.5</v>
+      </c>
+      <c r="I21" s="29">
+        <v>540.67999999999995</v>
+      </c>
+      <c r="J21" s="29">
+        <f t="shared" si="2"/>
+        <v>405.51</v>
+      </c>
+      <c r="K21" s="27">
+        <v>45833</v>
+      </c>
+      <c r="L21" s="34">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="M21" s="29">
+        <f t="shared" si="4"/>
+        <v>270.33999999999997</v>
+      </c>
+      <c r="N21" s="27">
+        <v>45904</v>
+      </c>
+      <c r="O21" s="25">
+        <f t="shared" si="5"/>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B22" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22" s="27">
+        <v>45562</v>
+      </c>
+      <c r="E22" s="25">
+        <v>5</v>
+      </c>
+      <c r="F22" s="27">
+        <v>45663</v>
+      </c>
+      <c r="G22" s="25">
+        <f t="shared" si="0"/>
+        <v>101</v>
+      </c>
+      <c r="H22" s="34">
+        <f t="shared" si="1"/>
+        <v>20.2</v>
+      </c>
+      <c r="I22" s="29">
+        <v>51.07</v>
+      </c>
+      <c r="J22" s="29">
+        <f t="shared" si="2"/>
+        <v>38.302500000000002</v>
+      </c>
+      <c r="K22" s="27">
+        <v>45665</v>
+      </c>
+      <c r="L22" s="34">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="M22" s="29">
+        <f t="shared" si="4"/>
+        <v>25.535</v>
+      </c>
+      <c r="N22" s="27">
+        <v>45715</v>
+      </c>
+      <c r="O22" s="28">
+        <f t="shared" si="5"/>
+        <v>52</v>
+      </c>
+      <c r="T22" s="25"/>
+      <c r="U22" s="25"/>
+      <c r="V22" s="25"/>
+      <c r="W22" s="25"/>
+      <c r="X22" s="25"/>
+      <c r="Y22" s="25"/>
+      <c r="Z22" s="25"/>
+      <c r="AA22" s="25"/>
+      <c r="AB22" s="25"/>
+    </row>
+    <row r="23" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B23" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="27">
+        <v>45579</v>
+      </c>
+      <c r="E23" s="25">
+        <v>6</v>
+      </c>
+      <c r="F23" s="27">
+        <v>45701</v>
+      </c>
+      <c r="G23" s="25">
+        <f t="shared" si="0"/>
+        <v>122</v>
+      </c>
+      <c r="H23" s="34">
+        <f t="shared" si="1"/>
+        <v>20.333333333333332</v>
+      </c>
+      <c r="I23" s="29">
+        <v>9.7799999999999994</v>
+      </c>
+      <c r="J23" s="29">
+        <f t="shared" si="2"/>
+        <v>7.3349999999999991</v>
+      </c>
+      <c r="K23" s="27">
+        <v>45708</v>
+      </c>
+      <c r="L23" s="34">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="M23" s="29">
+        <f t="shared" si="4"/>
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="N23" s="27">
+        <v>45720</v>
+      </c>
+      <c r="O23" s="28">
+        <f t="shared" si="5"/>
+        <v>19</v>
+      </c>
+      <c r="V23" s="33"/>
+      <c r="W23" s="33"/>
+      <c r="X23" s="33"/>
+      <c r="Y23" s="33"/>
+    </row>
+    <row r="24" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B24" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="27">
+        <v>45581</v>
+      </c>
+      <c r="E24" s="25">
+        <v>4</v>
+      </c>
+      <c r="F24" s="27">
+        <v>45659</v>
+      </c>
+      <c r="G24" s="25">
+        <f t="shared" si="0"/>
+        <v>78</v>
+      </c>
+      <c r="H24" s="34">
+        <f t="shared" si="1"/>
+        <v>19.5</v>
+      </c>
+      <c r="I24" s="29">
+        <v>20</v>
+      </c>
+      <c r="J24" s="29">
+        <f t="shared" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="K24" s="27">
+        <v>45665</v>
+      </c>
+      <c r="L24" s="34">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="M24" s="29">
+        <f t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="N24" s="27">
+        <v>45665</v>
+      </c>
+      <c r="O24" s="28">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="T24" s="25"/>
+      <c r="U24" s="25"/>
+      <c r="V24" s="25"/>
+      <c r="W24" s="25"/>
+      <c r="X24" s="25"/>
+      <c r="Y24" s="25"/>
+      <c r="Z24" s="25"/>
+      <c r="AA24" s="25"/>
+      <c r="AB24" s="25"/>
+    </row>
+    <row r="25" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B25" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="27">
+        <v>45582</v>
+      </c>
+      <c r="E25" s="25">
+        <v>5</v>
+      </c>
+      <c r="F25" s="27">
+        <v>45644</v>
+      </c>
+      <c r="G25" s="25">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="H25" s="34">
+        <f t="shared" si="1"/>
+        <v>12.4</v>
+      </c>
+      <c r="I25" s="29">
+        <v>25.68</v>
+      </c>
+      <c r="J25" s="29">
+        <f t="shared" si="2"/>
+        <v>19.259999999999998</v>
+      </c>
+      <c r="K25" s="27">
+        <v>45645</v>
+      </c>
+      <c r="L25" s="34">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="M25" s="29">
+        <f t="shared" si="4"/>
+        <v>12.84</v>
+      </c>
+      <c r="N25" s="27">
+        <v>45665</v>
+      </c>
+      <c r="O25" s="25">
+        <f t="shared" si="5"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B26" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="27">
+        <v>45593</v>
+      </c>
+      <c r="E26" s="25">
+        <v>4</v>
+      </c>
+      <c r="F26" s="27">
+        <v>45652</v>
+      </c>
+      <c r="G26" s="25">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="H26" s="34">
+        <f t="shared" si="1"/>
+        <v>14.75</v>
+      </c>
+      <c r="I26" s="29">
+        <v>24.23</v>
+      </c>
+      <c r="J26" s="29">
+        <f t="shared" si="2"/>
+        <v>18.172499999999999</v>
+      </c>
+      <c r="K26" s="27">
+        <v>45664</v>
+      </c>
+      <c r="L26" s="34">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="M26" s="29">
+        <f t="shared" si="4"/>
+        <v>12.115</v>
+      </c>
+      <c r="N26" s="27">
+        <v>45702</v>
+      </c>
+      <c r="O26" s="25">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B27" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" s="27">
+        <v>45601</v>
+      </c>
+      <c r="E27" s="25">
+        <v>6</v>
+      </c>
+      <c r="F27" s="36">
+        <v>45881</v>
+      </c>
+      <c r="G27" s="25">
+        <f>F27-D27</f>
+        <v>280</v>
+      </c>
+      <c r="H27" s="34">
+        <f>G27/E27</f>
+        <v>46.666666666666664</v>
+      </c>
+      <c r="I27" s="29">
+        <v>186.97</v>
+      </c>
+      <c r="J27" s="29">
+        <f t="shared" si="2"/>
+        <v>140.22749999999999</v>
+      </c>
+      <c r="K27" s="55">
+        <f>F27+$L$1</f>
+        <v>45892.178571428572</v>
+      </c>
+      <c r="M27" s="29">
+        <f t="shared" si="4"/>
+        <v>93.484999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B28" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="27">
+        <v>45671</v>
+      </c>
+      <c r="E28" s="25">
+        <v>6</v>
+      </c>
+      <c r="F28" s="36">
+        <v>45932</v>
+      </c>
+      <c r="G28" s="25">
+        <f t="shared" si="0"/>
+        <v>261</v>
+      </c>
+      <c r="H28" s="34">
+        <f t="shared" si="1"/>
+        <v>43.5</v>
+      </c>
+      <c r="I28" s="38">
+        <v>32.1</v>
+      </c>
+      <c r="J28" s="29">
+        <f t="shared" si="2"/>
+        <v>24.075000000000003</v>
+      </c>
+      <c r="K28" s="36">
+        <f>F28+$L$1</f>
+        <v>45943.178571428572</v>
+      </c>
+      <c r="M28" s="29">
+        <f t="shared" si="4"/>
+        <v>16.05</v>
+      </c>
+      <c r="N28" s="36">
+        <f t="shared" ref="N28:N33" ca="1" si="8">F28+$O$1</f>
+        <v>45975.25</v>
+      </c>
+      <c r="O28" s="28"/>
+      <c r="T28" s="25"/>
+      <c r="U28" s="25"/>
+      <c r="V28" s="25"/>
+      <c r="W28" s="25"/>
+      <c r="X28" s="25"/>
+      <c r="Y28" s="25"/>
+      <c r="Z28" s="25"/>
+      <c r="AA28" s="25"/>
+      <c r="AB28" s="25"/>
+    </row>
+    <row r="29" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B29" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="D29" s="27">
+        <v>45728</v>
+      </c>
+      <c r="E29" s="25">
+        <v>5</v>
+      </c>
+      <c r="F29" s="36">
+        <v>45923</v>
+      </c>
+      <c r="G29" s="25">
+        <f t="shared" si="0"/>
+        <v>195</v>
+      </c>
+      <c r="H29" s="34">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="I29" s="38">
+        <v>75.14</v>
+      </c>
+      <c r="J29" s="29">
+        <f t="shared" si="2"/>
+        <v>56.355000000000004</v>
+      </c>
+      <c r="K29" s="36">
+        <f>F29+$L$1</f>
+        <v>45934.178571428572</v>
+      </c>
+      <c r="M29" s="29">
+        <f t="shared" si="4"/>
+        <v>37.57</v>
+      </c>
+      <c r="N29" s="36">
+        <f t="shared" ca="1" si="8"/>
+        <v>45966.25</v>
+      </c>
+      <c r="T29" s="25"/>
+      <c r="U29" s="25"/>
+      <c r="V29" s="25"/>
+      <c r="W29" s="25"/>
+      <c r="X29" s="25"/>
+      <c r="Y29" s="25"/>
+      <c r="Z29" s="25"/>
+      <c r="AA29" s="25"/>
+      <c r="AB29" s="25"/>
+    </row>
+    <row r="30" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B30" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="27">
+        <v>45754</v>
+      </c>
+      <c r="E30" s="25">
+        <v>6</v>
+      </c>
+      <c r="F30" s="36">
+        <v>45923</v>
+      </c>
+      <c r="G30" s="25">
+        <f t="shared" si="0"/>
+        <v>169</v>
+      </c>
+      <c r="H30" s="34">
+        <f t="shared" si="1"/>
+        <v>28.166666666666668</v>
+      </c>
+      <c r="I30" s="29">
+        <v>142.65</v>
+      </c>
+      <c r="J30" s="29">
+        <f t="shared" si="2"/>
+        <v>106.98750000000001</v>
+      </c>
+      <c r="K30" s="36">
+        <f>F30+$L$1</f>
+        <v>45934.178571428572</v>
+      </c>
+      <c r="M30" s="29">
+        <f t="shared" si="4"/>
+        <v>71.325000000000003</v>
+      </c>
+      <c r="N30" s="36">
+        <f t="shared" ca="1" si="8"/>
+        <v>45966.25</v>
+      </c>
+      <c r="T30" s="25"/>
+      <c r="U30" s="25"/>
+      <c r="V30" s="25"/>
+      <c r="W30" s="25"/>
+      <c r="X30" s="25"/>
+      <c r="Y30" s="25"/>
+      <c r="Z30" s="25"/>
+      <c r="AA30" s="25"/>
+      <c r="AB30" s="25"/>
+    </row>
+    <row r="31" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B31" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="27">
+        <v>45756</v>
+      </c>
+      <c r="E31" s="25">
+        <v>6</v>
+      </c>
+      <c r="F31" s="36">
+        <v>45874</v>
+      </c>
+      <c r="G31" s="25">
+        <f t="shared" si="0"/>
+        <v>118</v>
+      </c>
+      <c r="H31" s="34">
+        <f t="shared" si="1"/>
+        <v>19.666666666666668</v>
+      </c>
+      <c r="I31" s="29">
+        <v>63.21</v>
+      </c>
+      <c r="J31" s="29">
+        <f t="shared" si="2"/>
+        <v>47.407499999999999</v>
+      </c>
+      <c r="K31" s="27">
+        <v>45888</v>
+      </c>
+      <c r="L31" s="34">
+        <f>K31-F31</f>
+        <v>14</v>
+      </c>
+      <c r="M31" s="29">
+        <f t="shared" si="4"/>
+        <v>31.605</v>
+      </c>
+      <c r="N31" s="36">
+        <f t="shared" ca="1" si="8"/>
+        <v>45917.25</v>
+      </c>
+      <c r="O31" s="44">
+        <f ca="1">TODAY()-F31</f>
+        <v>58</v>
+      </c>
+      <c r="T31" s="25"/>
+      <c r="U31" s="25"/>
+      <c r="V31" s="25"/>
+      <c r="W31" s="25"/>
+      <c r="X31" s="25"/>
+      <c r="Y31" s="25"/>
+      <c r="Z31" s="25"/>
+      <c r="AA31" s="25"/>
+      <c r="AB31" s="25"/>
+    </row>
+    <row r="32" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B32" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32" s="27">
+        <v>45756</v>
+      </c>
+      <c r="E32" s="25">
+        <v>5</v>
+      </c>
+      <c r="F32" s="27">
+        <v>45873</v>
+      </c>
+      <c r="G32" s="25">
+        <f t="shared" si="0"/>
+        <v>117</v>
+      </c>
+      <c r="H32" s="34">
+        <f t="shared" si="1"/>
+        <v>23.4</v>
+      </c>
+      <c r="I32" s="29">
+        <v>20.39</v>
+      </c>
+      <c r="J32" s="29">
+        <f t="shared" si="2"/>
+        <v>15.2925</v>
+      </c>
+      <c r="K32" s="27">
+        <v>45888</v>
+      </c>
+      <c r="L32" s="34">
+        <f>K32-F32</f>
+        <v>15</v>
+      </c>
+      <c r="M32" s="29">
+        <f t="shared" si="4"/>
+        <v>10.195</v>
+      </c>
+      <c r="N32" s="36">
+        <f t="shared" ca="1" si="8"/>
+        <v>45916.25</v>
+      </c>
+      <c r="O32" s="44">
+        <f ca="1">TODAY()-F32</f>
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B33" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" s="27">
+        <v>45756</v>
+      </c>
+      <c r="E33" s="25">
+        <v>5</v>
+      </c>
+      <c r="F33" s="36">
+        <v>45931</v>
+      </c>
+      <c r="G33" s="25">
+        <f t="shared" si="0"/>
+        <v>175</v>
+      </c>
+      <c r="H33" s="34">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="I33" s="29">
+        <v>92.32</v>
+      </c>
+      <c r="J33" s="29">
+        <f t="shared" si="2"/>
+        <v>69.239999999999995</v>
+      </c>
+      <c r="K33" s="36">
+        <f>F33+$L$1</f>
+        <v>45942.178571428572</v>
+      </c>
+      <c r="M33" s="29">
+        <f t="shared" si="4"/>
+        <v>46.16</v>
+      </c>
+      <c r="N33" s="36">
+        <f t="shared" ca="1" si="8"/>
+        <v>45974.25</v>
+      </c>
+      <c r="T33" s="25"/>
+      <c r="U33" s="25"/>
+      <c r="V33" s="25"/>
+      <c r="W33" s="25"/>
+      <c r="X33" s="25"/>
+      <c r="Y33" s="25"/>
+      <c r="Z33" s="25"/>
+      <c r="AA33" s="25"/>
+      <c r="AB33" s="25"/>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B34" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="D34" s="27">
+        <v>45779</v>
+      </c>
+      <c r="E34" s="25">
+        <v>3</v>
+      </c>
+      <c r="F34" s="27">
+        <v>45828</v>
+      </c>
+      <c r="G34" s="25">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="H34" s="34">
+        <f t="shared" si="1"/>
+        <v>16.333333333333332</v>
+      </c>
+      <c r="I34" s="29">
+        <v>183.58</v>
+      </c>
+      <c r="J34" s="29">
+        <f t="shared" si="2"/>
+        <v>137.685</v>
+      </c>
+      <c r="K34" s="27">
+        <v>45849</v>
+      </c>
+      <c r="L34" s="34">
+        <f>K34-F34</f>
+        <v>21</v>
+      </c>
+      <c r="M34" s="29">
+        <f t="shared" si="4"/>
+        <v>91.79</v>
+      </c>
+      <c r="N34" s="27">
+        <v>45889</v>
+      </c>
+      <c r="O34" s="25">
+        <f>+N34-F34</f>
+        <v>61</v>
+      </c>
+      <c r="T34" s="25"/>
+      <c r="U34" s="25"/>
+      <c r="V34" s="25"/>
+      <c r="W34" s="25"/>
+      <c r="X34" s="25"/>
+      <c r="Y34" s="25"/>
+      <c r="Z34" s="25"/>
+      <c r="AA34" s="25"/>
+      <c r="AB34" s="25"/>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B35" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35" s="27">
+        <v>45814</v>
+      </c>
+      <c r="E35" s="25">
+        <v>2</v>
+      </c>
+      <c r="F35" s="27">
+        <v>45831</v>
+      </c>
+      <c r="G35" s="25">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="H35" s="34">
+        <f t="shared" si="1"/>
+        <v>8.5</v>
+      </c>
+      <c r="I35" s="29">
+        <v>263.45</v>
+      </c>
+      <c r="J35" s="29">
+        <f t="shared" si="2"/>
+        <v>197.58749999999998</v>
+      </c>
+      <c r="K35" s="27">
+        <v>45835</v>
+      </c>
+      <c r="L35" s="34">
+        <f>K35-F35</f>
+        <v>4</v>
+      </c>
+      <c r="M35" s="29">
+        <f t="shared" si="4"/>
+        <v>131.72499999999999</v>
+      </c>
+      <c r="N35" s="27">
+        <v>45888</v>
+      </c>
+      <c r="O35" s="25">
+        <f>+N35-F35</f>
+        <v>57</v>
+      </c>
+      <c r="T35" s="25"/>
+      <c r="U35" s="25"/>
+      <c r="V35" s="25"/>
+      <c r="W35" s="25"/>
+      <c r="X35" s="25"/>
+      <c r="Y35" s="25"/>
+      <c r="Z35" s="25"/>
+      <c r="AA35" s="25"/>
+      <c r="AB35" s="25"/>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B36" s="24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B37" s="24" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B38" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="N38" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="24"/>
+      <c r="B39" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+      <c r="H39" s="34"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="27"/>
+      <c r="L39" s="34"/>
+      <c r="M39" s="29"/>
+      <c r="N39" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="O39" s="37"/>
+      <c r="P39" s="37"/>
+      <c r="Q39" s="37"/>
+      <c r="R39" s="37"/>
+      <c r="S39" s="37"/>
+    </row>
+    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B40" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="N40" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="S40" s="30"/>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B41" s="24" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B42" s="24" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B43" s="24" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B44" s="24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="49" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I49" s="56" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I50" s="56" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="51" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I51" s="56" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="52" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I52" s="56"/>
+    </row>
+    <row r="53" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I53" s="56"/>
+    </row>
+    <row r="54" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I54" s="56"/>
+    </row>
+    <row r="55" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I55" s="56"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AB40">
+    <sortCondition ref="D3:D40"/>
+  </sortState>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{A9B13DF2-D48C-48B0-AA59-066687FD8A4D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3B95373-36E1-4041-B321-49E0FB572644}">
+  <dimension ref="A1:AC7"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.88671875" style="54" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="54" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" style="54" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" style="54" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" style="54" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.77734375" style="54" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.21875" style="54" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="54" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.21875" style="54" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.77734375" style="54" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.88671875" style="54" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.21875" style="54" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.77734375" style="54" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.88671875" style="54" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8" style="54" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12" style="54" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.44140625" style="54" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.77734375" style="54" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.21875" style="54" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.77734375" style="54" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.109375" style="54" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8" style="54" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12" style="54" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.77734375" style="54" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.21875" style="54" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.77734375" style="54" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="54"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:29" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="41">
+        <f>AVERAGE(E3:E106)</f>
+        <v>8</v>
+      </c>
+      <c r="F1" s="40"/>
+      <c r="G1" s="39">
+        <f ca="1">AVERAGE(G3:G106)</f>
+        <v>229</v>
+      </c>
+      <c r="H1" s="39">
+        <f ca="1">AVERAGE(H3:H106)</f>
+        <v>28.625</v>
+      </c>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="39">
+        <f>AVERAGE(L3:L106)</f>
+        <v>21</v>
+      </c>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="39">
+        <f>AVERAGE(O3:O106)</f>
+        <v>271</v>
+      </c>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="25"/>
+      <c r="V1" s="26" t="e">
+        <f>AVERAGE(V6:V43)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="26"/>
+      <c r="AB1" s="26" t="e">
+        <f>AVERAGE(AB6:AB43)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC1" s="26"/>
+    </row>
+    <row r="2" spans="1:29" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="I2" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="J2" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="K2" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="L2" s="25" t="s">
+        <v>90</v>
+      </c>
+      <c r="M2" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="N2" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="O2" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="P2" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q2" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="R2" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="S2" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="T2" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="U2" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="V2" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="W2" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="X2" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y2" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z2" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA2" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="AB2" s="25" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="50" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="52">
+        <v>45756</v>
+      </c>
+      <c r="E3" s="45">
+        <v>8</v>
+      </c>
+      <c r="F3" s="46">
+        <f>D3+'Equity Bubbles'!G1</f>
+        <v>45872.818181818184</v>
+      </c>
+      <c r="G3" s="47">
+        <f ca="1">TODAY()-D3</f>
+        <v>176</v>
+      </c>
+      <c r="H3" s="48">
+        <f ca="1">G3/E3</f>
+        <v>22</v>
+      </c>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="46"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="46"/>
+      <c r="O3" s="45"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="25"/>
+      <c r="V3" s="25"/>
+      <c r="W3" s="25"/>
+      <c r="X3" s="25"/>
+      <c r="Y3" s="25"/>
+      <c r="Z3" s="25"/>
+      <c r="AA3" s="25"/>
+      <c r="AB3" s="25"/>
+    </row>
+    <row r="4" spans="1:29" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="51" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="53">
+        <v>36327</v>
+      </c>
+      <c r="E4" s="25">
+        <v>8</v>
+      </c>
+      <c r="F4" s="27">
+        <v>36609</v>
+      </c>
+      <c r="G4" s="25">
+        <f>F4-D4</f>
+        <v>282</v>
+      </c>
+      <c r="H4" s="34">
+        <f>G4/E4</f>
+        <v>35.25</v>
+      </c>
+      <c r="I4" s="29">
+        <v>117.88</v>
+      </c>
+      <c r="J4" s="29">
+        <f>I4*0.75</f>
+        <v>88.41</v>
+      </c>
+      <c r="K4" s="27">
+        <v>36630</v>
+      </c>
+      <c r="L4" s="34">
+        <f>K4-F4</f>
+        <v>21</v>
+      </c>
+      <c r="M4" s="29">
+        <f>I4*0.5</f>
+        <v>58.94</v>
+      </c>
+      <c r="N4" s="27">
+        <v>36880</v>
+      </c>
+      <c r="O4" s="25">
+        <f>+N4-F4</f>
+        <v>271</v>
+      </c>
+      <c r="P4" s="25"/>
+      <c r="Q4" s="25"/>
+      <c r="R4" s="25"/>
+      <c r="S4" s="25"/>
+      <c r="T4" s="25"/>
+      <c r="U4" s="25"/>
+      <c r="V4" s="25"/>
+      <c r="W4" s="25"/>
+      <c r="X4" s="25"/>
+      <c r="Y4" s="25"/>
+      <c r="Z4" s="25"/>
+      <c r="AA4" s="25"/>
+      <c r="AB4" s="25"/>
+    </row>
+    <row r="5" spans="1:29" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="27"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="27"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="25"/>
+      <c r="Q5" s="25"/>
+      <c r="R5" s="25"/>
+      <c r="S5" s="25"/>
+      <c r="T5" s="25"/>
+      <c r="U5" s="25"/>
+      <c r="V5" s="25"/>
+      <c r="W5" s="25"/>
+      <c r="X5" s="25"/>
+      <c r="Y5" s="25"/>
+      <c r="Z5" s="25"/>
+      <c r="AA5" s="25"/>
+      <c r="AB5" s="25"/>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B6" s="54" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B7" s="54" t="s">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{A0A4EBEB-7FC1-46F7-A54D-9C6C97184B30}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Financial Analysis/Models.xlsx
+++ b/Financial Analysis/Models.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C46595-D3E8-4AB3-B9B2-DD41C9C0656E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF488D15-0378-488E-9F80-4723EA6C3670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{40711DBD-7A53-4994-9FF1-9E754821B18D}"/>
   </bookViews>

--- a/Financial Analysis/Models.xlsx
+++ b/Financial Analysis/Models.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF488D15-0378-488E-9F80-4723EA6C3670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80741E9F-D11D-4C89-9319-C59396820647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{40711DBD-7A53-4994-9FF1-9E754821B18D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{40711DBD-7A53-4994-9FF1-9E754821B18D}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -276,7 +276,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="134">
   <si>
     <t>Tech</t>
   </si>
@@ -669,6 +669,15 @@
   </si>
   <si>
     <t>efficient to take profits at -25%? explore with more %'s</t>
+  </si>
+  <si>
+    <t>UMAC</t>
+  </si>
+  <si>
+    <t>RCAT</t>
+  </si>
+  <si>
+    <t>Price Variance</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1032,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -1145,6 +1154,9 @@
     <xf numFmtId="4" fontId="15" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -1182,13 +1194,13 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="N3">
-            <v>27.722623235186219</v>
+            <v>27.58173814816303</v>
           </cell>
           <cell r="T3">
-            <v>4.1199516612244071</v>
+            <v>4.6317001586310811</v>
           </cell>
           <cell r="Z3">
-            <v>-0.28177309827873842</v>
+            <v>-0.29140664255030541</v>
           </cell>
         </row>
         <row r="5">
@@ -1363,241 +1375,246 @@
         </row>
         <row r="39">
           <cell r="B39" t="str">
-            <v>IonQ</v>
+            <v>Rigetti</v>
           </cell>
         </row>
         <row r="40">
           <cell r="B40" t="str">
-            <v>Roku</v>
+            <v>IonQ</v>
           </cell>
         </row>
         <row r="41">
           <cell r="B41" t="str">
-            <v>Shift4</v>
+            <v>Roku</v>
           </cell>
         </row>
         <row r="42">
           <cell r="B42" t="str">
-            <v>Life360</v>
+            <v>Shift4</v>
           </cell>
         </row>
         <row r="43">
           <cell r="B43" t="str">
-            <v>EPAM</v>
+            <v>Life360</v>
           </cell>
         </row>
         <row r="44">
           <cell r="B44" t="str">
-            <v>Novami</v>
+            <v>EPAM</v>
           </cell>
         </row>
         <row r="45">
           <cell r="B45" t="str">
-            <v>GameStop</v>
+            <v>Novami</v>
           </cell>
         </row>
         <row r="46">
           <cell r="B46" t="str">
-            <v>StoneCo</v>
+            <v>GameStop</v>
           </cell>
         </row>
         <row r="47">
           <cell r="B47" t="str">
-            <v>Stride</v>
+            <v>StoneCo</v>
           </cell>
         </row>
         <row r="48">
           <cell r="B48" t="str">
-            <v>Wise</v>
+            <v>Stride</v>
           </cell>
         </row>
         <row r="49">
           <cell r="B49" t="str">
-            <v>PagSeguro</v>
+            <v>Wise</v>
           </cell>
         </row>
         <row r="50">
           <cell r="B50" t="str">
-            <v>Paysafe</v>
+            <v>PagSeguro</v>
           </cell>
         </row>
         <row r="51">
           <cell r="B51" t="str">
-            <v>PlugPower</v>
+            <v>Paysafe</v>
           </cell>
         </row>
         <row r="52">
           <cell r="B52" t="str">
-            <v>Opera</v>
+            <v>PlugPower</v>
           </cell>
         </row>
         <row r="53">
           <cell r="B53" t="str">
-            <v>Sonos</v>
+            <v>Opera</v>
           </cell>
         </row>
         <row r="54">
           <cell r="B54" t="str">
-            <v>Coursera</v>
+            <v>Sonos</v>
           </cell>
         </row>
         <row r="55">
           <cell r="B55" t="str">
-            <v>Corsair Gaming</v>
+            <v>Coursera</v>
           </cell>
         </row>
         <row r="56">
           <cell r="B56" t="str">
-            <v>Fiverr</v>
+            <v>Corsair Gaming</v>
           </cell>
         </row>
         <row r="57">
           <cell r="B57" t="str">
-            <v>Bandwidth</v>
+            <v>Fiverr</v>
           </cell>
         </row>
         <row r="58">
           <cell r="B58" t="str">
-            <v>Ambiq Micro</v>
+            <v>Bandwidth</v>
           </cell>
         </row>
         <row r="59">
           <cell r="B59" t="str">
-            <v>Gambling.com</v>
+            <v>Ambiq Micro</v>
           </cell>
         </row>
         <row r="60">
           <cell r="B60" t="str">
-            <v>Inseego</v>
+            <v>Gambling.com</v>
           </cell>
         </row>
         <row r="61">
           <cell r="B61" t="str">
-            <v>Atari</v>
+            <v>Inseego</v>
           </cell>
         </row>
         <row r="62">
           <cell r="B62" t="str">
-            <v>Chegg</v>
+            <v>Atari</v>
           </cell>
         </row>
         <row r="63">
           <cell r="B63" t="str">
-            <v>Roadzen</v>
+            <v>Chegg</v>
           </cell>
         </row>
         <row r="64">
           <cell r="B64" t="str">
-            <v>FuelCell</v>
+            <v>Roadzen</v>
           </cell>
         </row>
         <row r="65">
           <cell r="B65" t="str">
-            <v>Koss</v>
+            <v>FuelCell</v>
           </cell>
         </row>
         <row r="66">
           <cell r="B66" t="str">
-            <v>MicroAlgo</v>
+            <v>Koss</v>
           </cell>
         </row>
         <row r="67">
           <cell r="B67" t="str">
-            <v>Skillz</v>
+            <v>MicroAlgo</v>
           </cell>
         </row>
         <row r="68">
           <cell r="B68" t="str">
-            <v>Arqit Quantum</v>
+            <v>Skillz</v>
           </cell>
         </row>
         <row r="69">
           <cell r="B69" t="str">
-            <v>Hewlett-Packard</v>
+            <v>Arqit Quantum</v>
           </cell>
         </row>
         <row r="70">
           <cell r="B70" t="str">
-            <v>HP Enterprise</v>
+            <v>Hewlett-Packard</v>
           </cell>
         </row>
         <row r="71">
           <cell r="B71" t="str">
-            <v>Dell</v>
+            <v>HP Enterprise</v>
           </cell>
         </row>
         <row r="72">
           <cell r="B72" t="str">
-            <v>Electronic Arts</v>
+            <v>Dell</v>
           </cell>
         </row>
         <row r="73">
           <cell r="B73" t="str">
-            <v>Shopify</v>
+            <v>Electronic Arts</v>
           </cell>
         </row>
         <row r="74">
           <cell r="B74" t="str">
-            <v>IBM</v>
+            <v>Shopify</v>
           </cell>
         </row>
         <row r="75">
           <cell r="B75" t="str">
-            <v>Xiaomi</v>
+            <v>IBM</v>
           </cell>
         </row>
         <row r="76">
           <cell r="B76" t="str">
-            <v>Uber</v>
+            <v>Xiaomi</v>
           </cell>
         </row>
         <row r="77">
           <cell r="B77" t="str">
-            <v>Disney</v>
+            <v>Uber</v>
           </cell>
         </row>
         <row r="78">
           <cell r="B78" t="str">
-            <v>Pinterest</v>
+            <v>Disney</v>
           </cell>
         </row>
         <row r="79">
           <cell r="B79" t="str">
-            <v>Freshworks</v>
+            <v>Pinterest</v>
           </cell>
         </row>
         <row r="80">
           <cell r="B80" t="str">
-            <v>eBay</v>
+            <v>Freshworks</v>
           </cell>
         </row>
         <row r="81">
           <cell r="B81" t="str">
-            <v>Xerox</v>
+            <v>eBay</v>
           </cell>
         </row>
         <row r="82">
           <cell r="B82" t="str">
+            <v>Xerox</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="B83" t="str">
             <v>Alibaba</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="B85" t="str">
-            <v>Taiwan Semiconductor</v>
           </cell>
         </row>
         <row r="86">
           <cell r="B86" t="str">
-            <v>ASML</v>
+            <v>Taiwan Semiconductor</v>
           </cell>
         </row>
         <row r="87">
           <cell r="B87" t="str">
-            <v>Broadcom</v>
+            <v>ASML</v>
           </cell>
         </row>
         <row r="88">
           <cell r="B88" t="str">
+            <v>Broadcom</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="B89" t="str">
             <v>Qualcomm</v>
           </cell>
         </row>
@@ -1972,18 +1989,21 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
+      <sheetName val="FY2026 DoD Budget Materials"/>
+      <sheetName val="DoD Products"/>
+      <sheetName val="Future Products"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
           <cell r="R3">
-            <v>34.421156571947499</v>
-          </cell>
-          <cell r="Y3">
-            <v>2.8329303433229946</v>
+            <v>37.145030304683814</v>
           </cell>
           <cell r="AE3">
-            <v>-0.45499566684070913</v>
+            <v>2.9293484226775894</v>
+          </cell>
+          <cell r="AL3">
+            <v>-0.46900509315888117</v>
           </cell>
         </row>
         <row r="4">
@@ -2116,10 +2136,15 @@
             <v>Unusual Machines</v>
           </cell>
         </row>
-        <row r="30">
-          <cell r="B30"/>
+        <row r="31">
+          <cell r="B31" t="str">
+            <v>SAAB</v>
+          </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2563,26 +2588,26 @@
       </c>
       <c r="C3" s="18">
         <f>COUNTA([1]Models!$B$5:$B$1048576)</f>
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D3" s="19">
         <f>[1]Models!$Z$3</f>
-        <v>-0.28177309827873842</v>
+        <v>-0.29140664255030541</v>
       </c>
       <c r="E3" s="21">
         <f>[1]Models!$N$3</f>
-        <v>27.722623235186219</v>
+        <v>27.58173814816303</v>
       </c>
       <c r="F3" s="22">
         <f>[1]Models!$T$3</f>
-        <v>4.1199516612244071</v>
+        <v>4.6317001586310811</v>
       </c>
       <c r="G3" s="15">
         <v>45932</v>
       </c>
       <c r="H3" s="15">
         <f ca="1">TODAY()</f>
-        <v>45932</v>
+        <v>45939</v>
       </c>
       <c r="K3" s="17" t="s">
         <v>7</v>
@@ -2608,6 +2633,9 @@
         <f>[2]Main!$U$3</f>
         <v>0.96851754398012357</v>
       </c>
+      <c r="K4" s="57" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B5" s="17" t="s">
@@ -2636,19 +2664,19 @@
       </c>
       <c r="C6" s="18">
         <f>COUNTA([4]Main!$B$4:$B$1048576)</f>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="19">
-        <f>[4]Main!$AE$3</f>
-        <v>-0.45499566684070913</v>
+        <f>[4]Main!$AL$3</f>
+        <v>-0.46900509315888117</v>
       </c>
       <c r="E6" s="21">
         <f>[4]Main!$R$3</f>
-        <v>34.421156571947499</v>
+        <v>37.145030304683814</v>
       </c>
       <c r="F6" s="22">
-        <f>[4]Main!$Y$3</f>
-        <v>2.8329303433229946</v>
+        <f>[4]Main!$AE$3</f>
+        <v>2.9293484226775894</v>
       </c>
       <c r="K6" s="12" t="s">
         <v>36</v>
@@ -2706,19 +2734,19 @@
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C9" s="18">
         <f>SUM(C3:C8)</f>
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D9" s="19">
         <f>AVERAGE(D3:D8)</f>
-        <v>-0.4418561245947929</v>
+        <v>-0.44579661969308271</v>
       </c>
       <c r="E9" s="21">
         <f>AVERAGE(E3:E8)</f>
-        <v>27.156231848803536</v>
+        <v>27.801979010231811</v>
       </c>
       <c r="F9" s="22">
         <f>AVERAGE(F3:F8)</f>
-        <v>7.5291707435647606</v>
+        <v>7.6508040589170152</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>33</v>
@@ -2742,6 +2770,7 @@
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B11" s="20"/>
       <c r="K11" s="1" t="s">
         <v>30</v>
       </c>
@@ -2797,6 +2826,7 @@
     <hyperlink ref="B7" r:id="rId5" xr:uid="{A17DCD71-EE89-4DC1-A07D-05642306D744}"/>
     <hyperlink ref="B8" r:id="rId6" xr:uid="{8B455401-3CF0-478F-90EE-4BCE8AFD4668}"/>
     <hyperlink ref="K3" r:id="rId7" xr:uid="{119BFD1D-40CB-4E53-88E7-0B54106196A1}"/>
+    <hyperlink ref="K4" r:id="rId8" xr:uid="{96C3EF73-BFB4-4813-A0FA-B46F9F5E5121}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2874,7 +2904,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04147068-271F-415A-A4EA-D0D6DE05E2E6}">
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.44140625" style="24" bestFit="1" customWidth="1"/>
@@ -2911,43 +2941,43 @@
         <v>101</v>
       </c>
       <c r="E1" s="41">
-        <f>AVERAGE(E3:E103)</f>
-        <v>4.1212121212121211</v>
+        <f>AVERAGE(E3:E105)</f>
+        <v>4.1428571428571432</v>
       </c>
       <c r="F1" s="40"/>
       <c r="G1" s="39">
-        <f>AVERAGE(G3:G103)</f>
-        <v>116.81818181818181</v>
+        <f>AVERAGE(G3:G105)</f>
+        <v>116.25714285714285</v>
       </c>
       <c r="H1" s="39">
-        <f>AVERAGE(H3:H103)</f>
-        <v>27.084848484848486</v>
+        <f>AVERAGE(H3:H105)</f>
+        <v>26.695102040816327</v>
       </c>
       <c r="I1" s="40"/>
       <c r="J1" s="40"/>
       <c r="K1" s="40"/>
       <c r="L1" s="39">
-        <f>AVERAGE(L3:L103)</f>
-        <v>11.178571428571429</v>
+        <f>AVERAGE(L3:L105)</f>
+        <v>10.7</v>
       </c>
       <c r="M1" s="40"/>
       <c r="N1" s="40"/>
       <c r="O1" s="39">
-        <f ca="1">AVERAGE(O3:O103)</f>
-        <v>43.25</v>
+        <f ca="1">AVERAGE(O3:O105)</f>
+        <v>43.12903225806452</v>
       </c>
       <c r="P1" s="26"/>
       <c r="Q1" s="26"/>
       <c r="R1" s="26"/>
       <c r="V1" s="26">
-        <f>AVERAGE(V4:V41)</f>
+        <f>AVERAGE(V4:V43)</f>
         <v>297.125</v>
       </c>
       <c r="W1" s="26"/>
       <c r="X1" s="26"/>
       <c r="Y1" s="26"/>
       <c r="AB1" s="26">
-        <f>AVERAGE(AB4:AB41)</f>
+        <f>AVERAGE(AB4:AB43)</f>
         <v>705.5</v>
       </c>
       <c r="AC1" s="26"/>
@@ -3052,36 +3082,36 @@
         <v>39749</v>
       </c>
       <c r="G3" s="25">
-        <f t="shared" ref="G3:G35" si="0">F3-D3</f>
+        <f t="shared" ref="G3:G37" si="0">F3-D3</f>
         <v>42</v>
       </c>
       <c r="H3" s="25">
-        <f t="shared" ref="H3:H35" si="1">G3/E3</f>
+        <f t="shared" ref="H3:H37" si="1">G3/E3</f>
         <v>14</v>
       </c>
       <c r="I3" s="29">
         <v>945</v>
       </c>
       <c r="J3" s="29">
-        <f t="shared" ref="J3:J35" si="2">I3*0.75</f>
+        <f t="shared" ref="J3:J37" si="2">I3*0.75</f>
         <v>708.75</v>
       </c>
       <c r="K3" s="27">
         <v>39750</v>
       </c>
       <c r="L3" s="25">
-        <f t="shared" ref="L3:L26" si="3">K3-F3</f>
+        <f t="shared" ref="L3:L28" si="3">K3-F3</f>
         <v>1</v>
       </c>
       <c r="M3" s="29">
-        <f t="shared" ref="M3:M35" si="4">I3*0.5</f>
+        <f t="shared" ref="M3:M37" si="4">I3*0.5</f>
         <v>472.5</v>
       </c>
       <c r="N3" s="27">
         <v>39755</v>
       </c>
       <c r="O3" s="28">
-        <f t="shared" ref="O3:O26" si="5">+N3-F3</f>
+        <f t="shared" ref="O3:O28" si="5">+N3-F3</f>
         <v>6</v>
       </c>
     </row>
@@ -4144,566 +4174,572 @@
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B20" s="24" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="C20" s="25" t="s">
         <v>54</v>
       </c>
       <c r="D20" s="27">
-        <v>45488</v>
+        <v>45482</v>
       </c>
       <c r="E20" s="25">
         <v>5</v>
       </c>
       <c r="F20" s="27">
-        <v>45616</v>
+        <v>45663</v>
       </c>
       <c r="G20" s="25">
         <f t="shared" si="0"/>
-        <v>128</v>
+        <v>181</v>
       </c>
       <c r="H20" s="34">
         <f t="shared" si="1"/>
-        <v>25.6</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="I20" s="29">
-        <v>473.83</v>
+        <v>14.19</v>
       </c>
       <c r="J20" s="29">
         <f t="shared" si="2"/>
-        <v>355.3725</v>
+        <v>10.6425</v>
       </c>
       <c r="K20" s="27">
-        <v>45622</v>
+        <v>45667</v>
       </c>
       <c r="L20" s="34">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M20" s="29">
         <f t="shared" si="4"/>
+        <v>7.0949999999999998</v>
+      </c>
+      <c r="N20" s="27">
+        <v>45712</v>
+      </c>
+      <c r="O20" s="28">
+        <f t="shared" si="5"/>
+        <v>49</v>
+      </c>
+      <c r="V20" s="33"/>
+      <c r="W20" s="33"/>
+      <c r="X20" s="33"/>
+      <c r="Y20" s="33"/>
+    </row>
+    <row r="21" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B21" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="27">
+        <v>45488</v>
+      </c>
+      <c r="E21" s="25">
+        <v>5</v>
+      </c>
+      <c r="F21" s="27">
+        <v>45616</v>
+      </c>
+      <c r="G21" s="25">
+        <f t="shared" si="0"/>
+        <v>128</v>
+      </c>
+      <c r="H21" s="34">
+        <f t="shared" si="1"/>
+        <v>25.6</v>
+      </c>
+      <c r="I21" s="29">
+        <v>473.83</v>
+      </c>
+      <c r="J21" s="29">
+        <f t="shared" si="2"/>
+        <v>355.3725</v>
+      </c>
+      <c r="K21" s="27">
+        <v>45622</v>
+      </c>
+      <c r="L21" s="34">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="M21" s="29">
+        <f t="shared" si="4"/>
         <v>236.91499999999999</v>
       </c>
-      <c r="N20" s="27">
+      <c r="N21" s="27">
         <v>45716</v>
       </c>
-      <c r="O20" s="25">
+      <c r="O21" s="25">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B21" s="24" t="s">
+    <row r="22" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B22" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C22" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D22" s="27">
         <v>45512</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E22" s="25">
         <v>6</v>
       </c>
-      <c r="F21" s="27">
+      <c r="F22" s="27">
         <v>45791</v>
       </c>
-      <c r="G21" s="25">
+      <c r="G22" s="25">
         <f t="shared" si="0"/>
         <v>279</v>
       </c>
-      <c r="H21" s="34">
+      <c r="H22" s="34">
         <f t="shared" si="1"/>
         <v>46.5</v>
       </c>
-      <c r="I21" s="29">
+      <c r="I22" s="29">
         <v>540.67999999999995</v>
       </c>
-      <c r="J21" s="29">
+      <c r="J22" s="29">
         <f t="shared" si="2"/>
         <v>405.51</v>
       </c>
-      <c r="K21" s="27">
+      <c r="K22" s="27">
         <v>45833</v>
       </c>
-      <c r="L21" s="34">
+      <c r="L22" s="34">
         <f t="shared" si="3"/>
         <v>42</v>
       </c>
-      <c r="M21" s="29">
+      <c r="M22" s="29">
         <f t="shared" si="4"/>
         <v>270.33999999999997</v>
       </c>
-      <c r="N21" s="27">
+      <c r="N22" s="27">
         <v>45904</v>
       </c>
-      <c r="O21" s="25">
+      <c r="O22" s="25">
         <f t="shared" si="5"/>
         <v>113</v>
       </c>
     </row>
-    <row r="22" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B22" s="24" t="s">
+    <row r="23" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B23" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C23" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D23" s="27">
         <v>45562</v>
       </c>
-      <c r="E22" s="25">
+      <c r="E23" s="25">
         <v>5</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F23" s="27">
         <v>45663</v>
       </c>
-      <c r="G22" s="25">
+      <c r="G23" s="25">
         <f t="shared" si="0"/>
         <v>101</v>
       </c>
-      <c r="H22" s="34">
+      <c r="H23" s="34">
         <f t="shared" si="1"/>
         <v>20.2</v>
       </c>
-      <c r="I22" s="29">
+      <c r="I23" s="29">
         <v>51.07</v>
       </c>
-      <c r="J22" s="29">
+      <c r="J23" s="29">
         <f t="shared" si="2"/>
         <v>38.302500000000002</v>
       </c>
-      <c r="K22" s="27">
+      <c r="K23" s="27">
         <v>45665</v>
       </c>
-      <c r="L22" s="34">
+      <c r="L23" s="34">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="M22" s="29">
+      <c r="M23" s="29">
         <f t="shared" si="4"/>
         <v>25.535</v>
       </c>
-      <c r="N22" s="27">
+      <c r="N23" s="27">
         <v>45715</v>
       </c>
-      <c r="O22" s="28">
+      <c r="O23" s="28">
         <f t="shared" si="5"/>
         <v>52</v>
       </c>
-      <c r="T22" s="25"/>
-      <c r="U22" s="25"/>
-      <c r="V22" s="25"/>
-      <c r="W22" s="25"/>
-      <c r="X22" s="25"/>
-      <c r="Y22" s="25"/>
-      <c r="Z22" s="25"/>
-      <c r="AA22" s="25"/>
-      <c r="AB22" s="25"/>
-    </row>
-    <row r="23" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B23" s="24" t="s">
+      <c r="T23" s="25"/>
+      <c r="U23" s="25"/>
+      <c r="V23" s="25"/>
+      <c r="W23" s="25"/>
+      <c r="X23" s="25"/>
+      <c r="Y23" s="25"/>
+      <c r="Z23" s="25"/>
+      <c r="AA23" s="25"/>
+      <c r="AB23" s="25"/>
+    </row>
+    <row r="24" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B24" s="24" t="s">
         <v>106</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C24" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D24" s="27">
         <v>45579</v>
       </c>
-      <c r="E23" s="25">
+      <c r="E24" s="25">
         <v>6</v>
       </c>
-      <c r="F23" s="27">
+      <c r="F24" s="27">
         <v>45701</v>
       </c>
-      <c r="G23" s="25">
+      <c r="G24" s="25">
         <f t="shared" si="0"/>
         <v>122</v>
       </c>
-      <c r="H23" s="34">
+      <c r="H24" s="34">
         <f t="shared" si="1"/>
         <v>20.333333333333332</v>
       </c>
-      <c r="I23" s="29">
+      <c r="I24" s="29">
         <v>9.7799999999999994</v>
       </c>
-      <c r="J23" s="29">
+      <c r="J24" s="29">
         <f t="shared" si="2"/>
         <v>7.3349999999999991</v>
       </c>
-      <c r="K23" s="27">
+      <c r="K24" s="27">
         <v>45708</v>
       </c>
-      <c r="L23" s="34">
+      <c r="L24" s="34">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="M23" s="29">
+      <c r="M24" s="29">
         <f t="shared" si="4"/>
         <v>4.8899999999999997</v>
       </c>
-      <c r="N23" s="27">
+      <c r="N24" s="27">
         <v>45720</v>
       </c>
-      <c r="O23" s="28">
+      <c r="O24" s="28">
         <f t="shared" si="5"/>
         <v>19</v>
       </c>
-      <c r="V23" s="33"/>
-      <c r="W23" s="33"/>
-      <c r="X23" s="33"/>
-      <c r="Y23" s="33"/>
-    </row>
-    <row r="24" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B24" s="24" t="s">
+      <c r="V24" s="33"/>
+      <c r="W24" s="33"/>
+      <c r="X24" s="33"/>
+      <c r="Y24" s="33"/>
+    </row>
+    <row r="25" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B25" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C25" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="27">
+      <c r="D25" s="27">
         <v>45581</v>
       </c>
-      <c r="E24" s="25">
+      <c r="E25" s="25">
         <v>4</v>
       </c>
-      <c r="F24" s="27">
+      <c r="F25" s="27">
         <v>45659</v>
       </c>
-      <c r="G24" s="25">
+      <c r="G25" s="25">
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="H24" s="34">
+      <c r="H25" s="34">
         <f t="shared" si="1"/>
         <v>19.5</v>
       </c>
-      <c r="I24" s="29">
+      <c r="I25" s="29">
         <v>20</v>
       </c>
-      <c r="J24" s="29">
+      <c r="J25" s="29">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="K24" s="27">
+      <c r="K25" s="27">
         <v>45665</v>
       </c>
-      <c r="L24" s="34">
+      <c r="L25" s="34">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="M24" s="29">
+      <c r="M25" s="29">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N24" s="27">
+      <c r="N25" s="27">
         <v>45665</v>
       </c>
-      <c r="O24" s="28">
+      <c r="O25" s="28">
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="T24" s="25"/>
-      <c r="U24" s="25"/>
-      <c r="V24" s="25"/>
-      <c r="W24" s="25"/>
-      <c r="X24" s="25"/>
-      <c r="Y24" s="25"/>
-      <c r="Z24" s="25"/>
-      <c r="AA24" s="25"/>
-      <c r="AB24" s="25"/>
-    </row>
-    <row r="25" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B25" s="24" t="s">
+      <c r="T25" s="25"/>
+      <c r="U25" s="25"/>
+      <c r="V25" s="25"/>
+      <c r="W25" s="25"/>
+      <c r="X25" s="25"/>
+      <c r="Y25" s="25"/>
+      <c r="Z25" s="25"/>
+      <c r="AA25" s="25"/>
+      <c r="AB25" s="25"/>
+    </row>
+    <row r="26" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B26" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="C25" s="25" t="s">
+      <c r="C26" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D26" s="27">
         <v>45582</v>
       </c>
-      <c r="E25" s="25">
+      <c r="E26" s="25">
         <v>5</v>
       </c>
-      <c r="F25" s="27">
+      <c r="F26" s="27">
         <v>45644</v>
       </c>
-      <c r="G25" s="25">
+      <c r="G26" s="25">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="H25" s="34">
+      <c r="H26" s="34">
         <f t="shared" si="1"/>
         <v>12.4</v>
       </c>
-      <c r="I25" s="29">
+      <c r="I26" s="29">
         <v>25.68</v>
       </c>
-      <c r="J25" s="29">
+      <c r="J26" s="29">
         <f t="shared" si="2"/>
         <v>19.259999999999998</v>
       </c>
-      <c r="K25" s="27">
+      <c r="K26" s="27">
         <v>45645</v>
       </c>
-      <c r="L25" s="34">
+      <c r="L26" s="34">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="M25" s="29">
+      <c r="M26" s="29">
         <f t="shared" si="4"/>
         <v>12.84</v>
       </c>
-      <c r="N25" s="27">
+      <c r="N26" s="27">
         <v>45665</v>
       </c>
-      <c r="O25" s="25">
+      <c r="O26" s="25">
         <f t="shared" si="5"/>
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B26" s="24" t="s">
+    <row r="27" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B27" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="C26" s="25" t="s">
+      <c r="C27" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="D26" s="27">
+      <c r="D27" s="27">
         <v>45593</v>
       </c>
-      <c r="E26" s="25">
+      <c r="E27" s="25">
         <v>4</v>
       </c>
-      <c r="F26" s="27">
+      <c r="F27" s="27">
         <v>45652</v>
       </c>
-      <c r="G26" s="25">
+      <c r="G27" s="25">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="H26" s="34">
+      <c r="H27" s="34">
         <f t="shared" si="1"/>
         <v>14.75</v>
       </c>
-      <c r="I26" s="29">
+      <c r="I27" s="29">
         <v>24.23</v>
       </c>
-      <c r="J26" s="29">
+      <c r="J27" s="29">
         <f t="shared" si="2"/>
         <v>18.172499999999999</v>
       </c>
-      <c r="K26" s="27">
+      <c r="K27" s="27">
         <v>45664</v>
       </c>
-      <c r="L26" s="34">
+      <c r="L27" s="34">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="M26" s="29">
+      <c r="M27" s="29">
         <f t="shared" si="4"/>
         <v>12.115</v>
       </c>
-      <c r="N26" s="27">
+      <c r="N27" s="27">
         <v>45702</v>
       </c>
-      <c r="O26" s="25">
+      <c r="O27" s="25">
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B27" s="35" t="s">
+    <row r="28" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B28" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="27">
+        <v>45595</v>
+      </c>
+      <c r="E28" s="25">
+        <v>3</v>
+      </c>
+      <c r="F28" s="27">
+        <v>45625</v>
+      </c>
+      <c r="G28" s="25">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="H28" s="34">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="I28" s="29">
+        <v>18.73</v>
+      </c>
+      <c r="J28" s="29">
+        <f t="shared" si="2"/>
+        <v>14.047499999999999</v>
+      </c>
+      <c r="K28" s="27">
+        <v>45629</v>
+      </c>
+      <c r="L28" s="34">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="M28" s="29">
+        <f t="shared" si="4"/>
+        <v>9.3650000000000002</v>
+      </c>
+      <c r="N28" s="27">
+        <v>45630</v>
+      </c>
+      <c r="O28" s="25">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="B29" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="C29" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="27">
+      <c r="D29" s="27">
         <v>45601</v>
       </c>
-      <c r="E27" s="25">
+      <c r="E29" s="25">
         <v>6</v>
       </c>
-      <c r="F27" s="36">
+      <c r="F29" s="36">
         <v>45881</v>
       </c>
-      <c r="G27" s="25">
-        <f>F27-D27</f>
+      <c r="G29" s="25">
+        <f>F29-D29</f>
         <v>280</v>
       </c>
-      <c r="H27" s="34">
-        <f>G27/E27</f>
+      <c r="H29" s="34">
+        <f>G29/E29</f>
         <v>46.666666666666664</v>
       </c>
-      <c r="I27" s="29">
+      <c r="I29" s="29">
         <v>186.97</v>
       </c>
-      <c r="J27" s="29">
+      <c r="J29" s="29">
         <f t="shared" si="2"/>
         <v>140.22749999999999</v>
       </c>
-      <c r="K27" s="55">
-        <f>F27+$L$1</f>
-        <v>45892.178571428572</v>
-      </c>
-      <c r="M27" s="29">
+      <c r="K29" s="55">
+        <f>F29+$L$1</f>
+        <v>45891.7</v>
+      </c>
+      <c r="M29" s="29">
         <f t="shared" si="4"/>
         <v>93.484999999999999</v>
       </c>
-    </row>
-    <row r="28" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B28" s="35" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="D28" s="27">
-        <v>45671</v>
-      </c>
-      <c r="E28" s="25">
-        <v>6</v>
-      </c>
-      <c r="F28" s="36">
-        <v>45932</v>
-      </c>
-      <c r="G28" s="25">
-        <f t="shared" si="0"/>
-        <v>261</v>
-      </c>
-      <c r="H28" s="34">
-        <f t="shared" si="1"/>
-        <v>43.5</v>
-      </c>
-      <c r="I28" s="38">
-        <v>32.1</v>
-      </c>
-      <c r="J28" s="29">
-        <f t="shared" si="2"/>
-        <v>24.075000000000003</v>
-      </c>
-      <c r="K28" s="36">
-        <f>F28+$L$1</f>
-        <v>45943.178571428572</v>
-      </c>
-      <c r="M28" s="29">
-        <f t="shared" si="4"/>
-        <v>16.05</v>
-      </c>
-      <c r="N28" s="36">
-        <f t="shared" ref="N28:N33" ca="1" si="8">F28+$O$1</f>
-        <v>45975.25</v>
-      </c>
-      <c r="O28" s="28"/>
-      <c r="T28" s="25"/>
-      <c r="U28" s="25"/>
-      <c r="V28" s="25"/>
-      <c r="W28" s="25"/>
-      <c r="X28" s="25"/>
-      <c r="Y28" s="25"/>
-      <c r="Z28" s="25"/>
-      <c r="AA28" s="25"/>
-      <c r="AB28" s="25"/>
-    </row>
-    <row r="29" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B29" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="D29" s="27">
-        <v>45728</v>
-      </c>
-      <c r="E29" s="25">
-        <v>5</v>
-      </c>
-      <c r="F29" s="36">
-        <v>45923</v>
-      </c>
-      <c r="G29" s="25">
-        <f t="shared" si="0"/>
-        <v>195</v>
-      </c>
-      <c r="H29" s="34">
-        <f t="shared" si="1"/>
-        <v>39</v>
-      </c>
-      <c r="I29" s="38">
-        <v>75.14</v>
-      </c>
-      <c r="J29" s="29">
-        <f t="shared" si="2"/>
-        <v>56.355000000000004</v>
-      </c>
-      <c r="K29" s="36">
-        <f>F29+$L$1</f>
-        <v>45934.178571428572</v>
-      </c>
-      <c r="M29" s="29">
-        <f t="shared" si="4"/>
-        <v>37.57</v>
-      </c>
       <c r="N29" s="36">
-        <f t="shared" ca="1" si="8"/>
-        <v>45966.25</v>
-      </c>
-      <c r="T29" s="25"/>
-      <c r="U29" s="25"/>
-      <c r="V29" s="25"/>
-      <c r="W29" s="25"/>
-      <c r="X29" s="25"/>
-      <c r="Y29" s="25"/>
-      <c r="Z29" s="25"/>
-      <c r="AA29" s="25"/>
-      <c r="AB29" s="25"/>
+        <f t="shared" ref="N29:N35" ca="1" si="8">F29+$O$1</f>
+        <v>45924.129032258068</v>
+      </c>
+      <c r="O29" s="44">
+        <f ca="1">TODAY()-F29</f>
+        <v>58</v>
+      </c>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B30" s="35" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D30" s="27">
-        <v>45754</v>
+        <v>45671</v>
       </c>
       <c r="E30" s="25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F30" s="36">
-        <v>45923</v>
+        <v>45933</v>
       </c>
       <c r="G30" s="25">
         <f t="shared" si="0"/>
-        <v>169</v>
+        <v>262</v>
       </c>
       <c r="H30" s="34">
         <f t="shared" si="1"/>
-        <v>28.166666666666668</v>
-      </c>
-      <c r="I30" s="29">
-        <v>142.65</v>
+        <v>37.428571428571431</v>
+      </c>
+      <c r="I30" s="38">
+        <v>37.57</v>
       </c>
       <c r="J30" s="29">
         <f t="shared" si="2"/>
-        <v>106.98750000000001</v>
+        <v>28.177500000000002</v>
       </c>
       <c r="K30" s="36">
         <f>F30+$L$1</f>
-        <v>45934.178571428572</v>
+        <v>45943.7</v>
       </c>
       <c r="M30" s="29">
         <f t="shared" si="4"/>
-        <v>71.325000000000003</v>
+        <v>18.785</v>
       </c>
       <c r="N30" s="36">
         <f t="shared" ca="1" si="8"/>
-        <v>45966.25</v>
-      </c>
+        <v>45976.129032258068</v>
+      </c>
+      <c r="O30" s="28"/>
       <c r="T30" s="25"/>
       <c r="U30" s="25"/>
       <c r="V30" s="25"/>
@@ -4716,53 +4752,46 @@
     </row>
     <row r="31" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B31" s="35" t="s">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="D31" s="27">
-        <v>45756</v>
+        <v>45728</v>
       </c>
       <c r="E31" s="25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F31" s="36">
-        <v>45874</v>
+        <v>45923</v>
       </c>
       <c r="G31" s="25">
         <f t="shared" si="0"/>
-        <v>118</v>
+        <v>195</v>
       </c>
       <c r="H31" s="34">
         <f t="shared" si="1"/>
-        <v>19.666666666666668</v>
-      </c>
-      <c r="I31" s="29">
-        <v>63.21</v>
+        <v>39</v>
+      </c>
+      <c r="I31" s="38">
+        <v>75.14</v>
       </c>
       <c r="J31" s="29">
         <f t="shared" si="2"/>
-        <v>47.407499999999999</v>
-      </c>
-      <c r="K31" s="27">
-        <v>45888</v>
-      </c>
-      <c r="L31" s="34">
-        <f>K31-F31</f>
-        <v>14</v>
+        <v>56.355000000000004</v>
+      </c>
+      <c r="K31" s="36">
+        <f>F31+$L$1</f>
+        <v>45933.7</v>
       </c>
       <c r="M31" s="29">
         <f t="shared" si="4"/>
-        <v>31.605</v>
+        <v>37.57</v>
       </c>
       <c r="N31" s="36">
         <f t="shared" ca="1" si="8"/>
-        <v>45917.25</v>
-      </c>
-      <c r="O31" s="44">
-        <f ca="1">TODAY()-F31</f>
-        <v>58</v>
+        <v>45966.129032258068</v>
       </c>
       <c r="T31" s="25"/>
       <c r="U31" s="25"/>
@@ -4776,58 +4805,60 @@
     </row>
     <row r="32" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B32" s="35" t="s">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="C32" s="25" t="s">
         <v>58</v>
       </c>
       <c r="D32" s="27">
-        <v>45756</v>
+        <v>45754</v>
       </c>
       <c r="E32" s="25">
-        <v>5</v>
-      </c>
-      <c r="F32" s="27">
-        <v>45873</v>
+        <v>6</v>
+      </c>
+      <c r="F32" s="36">
+        <v>45923</v>
       </c>
       <c r="G32" s="25">
         <f t="shared" si="0"/>
-        <v>117</v>
+        <v>169</v>
       </c>
       <c r="H32" s="34">
         <f t="shared" si="1"/>
-        <v>23.4</v>
+        <v>28.166666666666668</v>
       </c>
       <c r="I32" s="29">
-        <v>20.39</v>
+        <v>142.65</v>
       </c>
       <c r="J32" s="29">
         <f t="shared" si="2"/>
-        <v>15.2925</v>
-      </c>
-      <c r="K32" s="27">
-        <v>45888</v>
-      </c>
-      <c r="L32" s="34">
-        <f>K32-F32</f>
-        <v>15</v>
+        <v>106.98750000000001</v>
+      </c>
+      <c r="K32" s="36">
+        <f>F32+$L$1</f>
+        <v>45933.7</v>
       </c>
       <c r="M32" s="29">
         <f t="shared" si="4"/>
-        <v>10.195</v>
+        <v>71.325000000000003</v>
       </c>
       <c r="N32" s="36">
         <f t="shared" ca="1" si="8"/>
-        <v>45916.25</v>
-      </c>
-      <c r="O32" s="44">
-        <f ca="1">TODAY()-F32</f>
-        <v>59</v>
-      </c>
+        <v>45966.129032258068</v>
+      </c>
+      <c r="T32" s="25"/>
+      <c r="U32" s="25"/>
+      <c r="V32" s="25"/>
+      <c r="W32" s="25"/>
+      <c r="X32" s="25"/>
+      <c r="Y32" s="25"/>
+      <c r="Z32" s="25"/>
+      <c r="AA32" s="25"/>
+      <c r="AB32" s="25"/>
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B33" s="35" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="C33" s="25" t="s">
         <v>54</v>
@@ -4836,37 +4867,44 @@
         <v>45756</v>
       </c>
       <c r="E33" s="25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F33" s="36">
-        <v>45931</v>
+        <v>45874</v>
       </c>
       <c r="G33" s="25">
         <f t="shared" si="0"/>
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="H33" s="34">
         <f t="shared" si="1"/>
-        <v>35</v>
+        <v>19.666666666666668</v>
       </c>
       <c r="I33" s="29">
-        <v>92.32</v>
+        <v>63.21</v>
       </c>
       <c r="J33" s="29">
         <f t="shared" si="2"/>
-        <v>69.239999999999995</v>
-      </c>
-      <c r="K33" s="36">
-        <f>F33+$L$1</f>
-        <v>45942.178571428572</v>
+        <v>47.407499999999999</v>
+      </c>
+      <c r="K33" s="27">
+        <v>45888</v>
+      </c>
+      <c r="L33" s="34">
+        <f>K33-F33</f>
+        <v>14</v>
       </c>
       <c r="M33" s="29">
         <f t="shared" si="4"/>
-        <v>46.16</v>
+        <v>31.605</v>
       </c>
       <c r="N33" s="36">
         <f t="shared" ca="1" si="8"/>
-        <v>45974.25</v>
+        <v>45917.129032258068</v>
+      </c>
+      <c r="O33" s="44">
+        <f ca="1">TODAY()-F33</f>
+        <v>65</v>
       </c>
       <c r="T33" s="25"/>
       <c r="U33" s="25"/>
@@ -4879,112 +4917,98 @@
       <c r="AB33" s="25"/>
     </row>
     <row r="34" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B34" s="24" t="s">
-        <v>120</v>
+      <c r="B34" s="35" t="s">
+        <v>111</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="D34" s="27">
-        <v>45779</v>
+        <v>45756</v>
       </c>
       <c r="E34" s="25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F34" s="27">
-        <v>45828</v>
+        <v>45873</v>
       </c>
       <c r="G34" s="25">
         <f t="shared" si="0"/>
-        <v>49</v>
+        <v>117</v>
       </c>
       <c r="H34" s="34">
         <f t="shared" si="1"/>
-        <v>16.333333333333332</v>
+        <v>23.4</v>
       </c>
       <c r="I34" s="29">
-        <v>183.58</v>
+        <v>20.39</v>
       </c>
       <c r="J34" s="29">
         <f t="shared" si="2"/>
-        <v>137.685</v>
+        <v>15.2925</v>
       </c>
       <c r="K34" s="27">
-        <v>45849</v>
+        <v>45888</v>
       </c>
       <c r="L34" s="34">
         <f>K34-F34</f>
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="M34" s="29">
         <f t="shared" si="4"/>
-        <v>91.79</v>
-      </c>
-      <c r="N34" s="27">
-        <v>45889</v>
-      </c>
-      <c r="O34" s="25">
-        <f>+N34-F34</f>
-        <v>61</v>
-      </c>
-      <c r="T34" s="25"/>
-      <c r="U34" s="25"/>
-      <c r="V34" s="25"/>
-      <c r="W34" s="25"/>
-      <c r="X34" s="25"/>
-      <c r="Y34" s="25"/>
-      <c r="Z34" s="25"/>
-      <c r="AA34" s="25"/>
-      <c r="AB34" s="25"/>
+        <v>10.195</v>
+      </c>
+      <c r="N34" s="36">
+        <f t="shared" ca="1" si="8"/>
+        <v>45916.129032258068</v>
+      </c>
+      <c r="O34" s="44">
+        <f ca="1">TODAY()-F34</f>
+        <v>66</v>
+      </c>
     </row>
     <row r="35" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B35" s="24" t="s">
-        <v>121</v>
+      <c r="B35" s="35" t="s">
+        <v>109</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="D35" s="27">
-        <v>45814</v>
+        <v>45756</v>
       </c>
       <c r="E35" s="25">
-        <v>2</v>
-      </c>
-      <c r="F35" s="27">
-        <v>45831</v>
+        <v>5</v>
+      </c>
+      <c r="F35" s="36">
+        <v>45933</v>
       </c>
       <c r="G35" s="25">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>177</v>
       </c>
       <c r="H35" s="34">
         <f t="shared" si="1"/>
-        <v>8.5</v>
+        <v>35.4</v>
       </c>
       <c r="I35" s="29">
-        <v>263.45</v>
+        <v>92.32</v>
       </c>
       <c r="J35" s="29">
         <f t="shared" si="2"/>
-        <v>197.58749999999998</v>
-      </c>
-      <c r="K35" s="27">
-        <v>45835</v>
-      </c>
-      <c r="L35" s="34">
-        <f>K35-F35</f>
-        <v>4</v>
+        <v>69.239999999999995</v>
+      </c>
+      <c r="K35" s="36">
+        <f>F35+$L$1</f>
+        <v>45943.7</v>
       </c>
       <c r="M35" s="29">
         <f t="shared" si="4"/>
-        <v>131.72499999999999</v>
-      </c>
-      <c r="N35" s="27">
-        <v>45888</v>
-      </c>
-      <c r="O35" s="25">
-        <f>+N35-F35</f>
-        <v>57</v>
+        <v>46.16</v>
+      </c>
+      <c r="N35" s="36">
+        <f t="shared" ca="1" si="8"/>
+        <v>45976.129032258068</v>
       </c>
       <c r="T35" s="25"/>
       <c r="U35" s="25"/>
@@ -4998,96 +5022,208 @@
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B36" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="D36" s="27">
+        <v>45779</v>
+      </c>
+      <c r="E36" s="25">
+        <v>3</v>
+      </c>
+      <c r="F36" s="27">
+        <v>45828</v>
+      </c>
+      <c r="G36" s="25">
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
+      <c r="H36" s="34">
+        <f t="shared" si="1"/>
+        <v>16.333333333333332</v>
+      </c>
+      <c r="I36" s="29">
+        <v>183.58</v>
+      </c>
+      <c r="J36" s="29">
+        <f t="shared" si="2"/>
+        <v>137.685</v>
+      </c>
+      <c r="K36" s="27">
+        <v>45849</v>
+      </c>
+      <c r="L36" s="34">
+        <f>K36-F36</f>
+        <v>21</v>
+      </c>
+      <c r="M36" s="29">
+        <f t="shared" si="4"/>
+        <v>91.79</v>
+      </c>
+      <c r="N36" s="27">
+        <v>45889</v>
+      </c>
+      <c r="O36" s="25">
+        <f>+N36-F36</f>
+        <v>61</v>
+      </c>
+      <c r="T36" s="25"/>
+      <c r="U36" s="25"/>
+      <c r="V36" s="25"/>
+      <c r="W36" s="25"/>
+      <c r="X36" s="25"/>
+      <c r="Y36" s="25"/>
+      <c r="Z36" s="25"/>
+      <c r="AA36" s="25"/>
+      <c r="AB36" s="25"/>
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B37" s="24" t="s">
-        <v>48</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="D37" s="27">
+        <v>45814</v>
+      </c>
+      <c r="E37" s="25">
+        <v>2</v>
+      </c>
+      <c r="F37" s="27">
+        <v>45831</v>
+      </c>
+      <c r="G37" s="25">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="H37" s="34">
+        <f t="shared" si="1"/>
+        <v>8.5</v>
+      </c>
+      <c r="I37" s="29">
+        <v>263.45</v>
+      </c>
+      <c r="J37" s="29">
+        <f t="shared" si="2"/>
+        <v>197.58749999999998</v>
+      </c>
+      <c r="K37" s="27">
+        <v>45835</v>
+      </c>
+      <c r="L37" s="34">
+        <f>K37-F37</f>
+        <v>4</v>
+      </c>
+      <c r="M37" s="29">
+        <f t="shared" si="4"/>
+        <v>131.72499999999999</v>
+      </c>
+      <c r="N37" s="27">
+        <v>45888</v>
+      </c>
+      <c r="O37" s="25">
+        <f>+N37-F37</f>
+        <v>57</v>
+      </c>
+      <c r="T37" s="25"/>
+      <c r="U37" s="25"/>
+      <c r="V37" s="25"/>
+      <c r="W37" s="25"/>
+      <c r="X37" s="25"/>
+      <c r="Y37" s="25"/>
+      <c r="Z37" s="25"/>
+      <c r="AA37" s="25"/>
+      <c r="AB37" s="25"/>
     </row>
     <row r="38" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B38" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="N38" s="25" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:28" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B39" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="C39" s="25"/>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="34"/>
-      <c r="I39" s="29"/>
-      <c r="J39" s="29"/>
-      <c r="K39" s="27"/>
-      <c r="L39" s="34"/>
-      <c r="M39" s="29"/>
-      <c r="N39" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="O39" s="37"/>
-      <c r="P39" s="37"/>
-      <c r="Q39" s="37"/>
-      <c r="R39" s="37"/>
-      <c r="S39" s="37"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="40" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B40" s="24" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N40" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="S40" s="30"/>
-    </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="24"/>
       <c r="B41" s="24" t="s">
-        <v>112</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="34"/>
+      <c r="I41" s="29"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="27"/>
+      <c r="L41" s="34"/>
+      <c r="M41" s="29"/>
+      <c r="N41" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="O41" s="37"/>
+      <c r="P41" s="37"/>
+      <c r="Q41" s="37"/>
+      <c r="R41" s="37"/>
+      <c r="S41" s="37"/>
     </row>
     <row r="42" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B42" s="24" t="s">
-        <v>114</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="N42" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="S42" s="30"/>
     </row>
     <row r="43" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B43" s="24" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B44" s="24" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B45" s="24" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B46" s="24" t="s">
         <v>118</v>
-      </c>
-    </row>
-    <row r="49" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I49" s="56" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I50" s="56" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="51" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I51" s="56" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I52" s="56" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="53" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I53" s="56" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="52" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I52" s="56"/>
-    </row>
-    <row r="53" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I53" s="56"/>
     </row>
     <row r="54" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I54" s="56"/>
@@ -5095,9 +5231,15 @@
     <row r="55" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I55" s="56"/>
     </row>
+    <row r="56" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I56" s="56"/>
+    </row>
+    <row r="57" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I57" s="56"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AB40">
-    <sortCondition ref="D3:D40"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AB42">
+    <sortCondition ref="D3:D42"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{A9B13DF2-D48C-48B0-AA59-066687FD8A4D}"/>
@@ -5156,11 +5298,11 @@
       <c r="F1" s="40"/>
       <c r="G1" s="39">
         <f ca="1">AVERAGE(G3:G106)</f>
-        <v>229</v>
+        <v>232.5</v>
       </c>
       <c r="H1" s="39">
         <f ca="1">AVERAGE(H3:H106)</f>
-        <v>28.625</v>
+        <v>29.0625</v>
       </c>
       <c r="I1" s="40"/>
       <c r="J1" s="40"/>
@@ -5290,15 +5432,15 @@
       </c>
       <c r="F3" s="46">
         <f>D3+'Equity Bubbles'!G1</f>
-        <v>45872.818181818184</v>
+        <v>45872.257142857146</v>
       </c>
       <c r="G3" s="47">
         <f ca="1">TODAY()-D3</f>
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="H3" s="48">
         <f ca="1">G3/E3</f>
-        <v>22</v>
+        <v>22.875</v>
       </c>
       <c r="I3" s="49"/>
       <c r="J3" s="49"/>

--- a/Financial Analysis/Models.xlsx
+++ b/Financial Analysis/Models.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80741E9F-D11D-4C89-9319-C59396820647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FDE143-B341-4D6D-9343-061F919DD4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{40711DBD-7A53-4994-9FF1-9E754821B18D}"/>
   </bookViews>
@@ -1992,6 +1992,7 @@
       <sheetName val="FY2026 DoD Budget Materials"/>
       <sheetName val="DoD Products"/>
       <sheetName val="Future Products"/>
+      <sheetName val="Global Revenue"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -2141,10 +2142,31 @@
             <v>SAAB</v>
           </cell>
         </row>
+        <row r="32">
+          <cell r="B32" t="str">
+            <v>General Atomics</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="B33" t="str">
+            <v>AeroVironment</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="B34" t="str">
+            <v>Archer Aviation</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="B35" t="str">
+            <v>Sierra Nevada</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2" refreshError="1"/>
       <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2607,7 +2629,7 @@
       </c>
       <c r="H3" s="15">
         <f ca="1">TODAY()</f>
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="K3" s="17" t="s">
         <v>7</v>
@@ -2664,7 +2686,7 @@
       </c>
       <c r="C6" s="18">
         <f>COUNTA([4]Main!$B$4:$B$1048576)</f>
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D6" s="19">
         <f>[4]Main!$AL$3</f>
@@ -2734,7 +2756,7 @@
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C9" s="18">
         <f>SUM(C3:C8)</f>
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D9" s="19">
         <f>AVERAGE(D3:D8)</f>
@@ -2964,7 +2986,7 @@
       <c r="N1" s="40"/>
       <c r="O1" s="39">
         <f ca="1">AVERAGE(O3:O105)</f>
-        <v>43.12903225806452</v>
+        <v>43.225806451612904</v>
       </c>
       <c r="P1" s="26"/>
       <c r="Q1" s="26"/>
@@ -4689,11 +4711,11 @@
       </c>
       <c r="N29" s="36">
         <f t="shared" ref="N29:N35" ca="1" si="8">F29+$O$1</f>
-        <v>45924.129032258068</v>
+        <v>45924.225806451614</v>
       </c>
       <c r="O29" s="44">
         <f ca="1">TODAY()-F29</f>
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.25">
@@ -4737,7 +4759,7 @@
       </c>
       <c r="N30" s="36">
         <f t="shared" ca="1" si="8"/>
-        <v>45976.129032258068</v>
+        <v>45976.225806451614</v>
       </c>
       <c r="O30" s="28"/>
       <c r="T30" s="25"/>
@@ -4791,7 +4813,7 @@
       </c>
       <c r="N31" s="36">
         <f t="shared" ca="1" si="8"/>
-        <v>45966.129032258068</v>
+        <v>45966.225806451614</v>
       </c>
       <c r="T31" s="25"/>
       <c r="U31" s="25"/>
@@ -4844,7 +4866,7 @@
       </c>
       <c r="N32" s="36">
         <f t="shared" ca="1" si="8"/>
-        <v>45966.129032258068</v>
+        <v>45966.225806451614</v>
       </c>
       <c r="T32" s="25"/>
       <c r="U32" s="25"/>
@@ -4900,11 +4922,11 @@
       </c>
       <c r="N33" s="36">
         <f t="shared" ca="1" si="8"/>
-        <v>45917.129032258068</v>
+        <v>45917.225806451614</v>
       </c>
       <c r="O33" s="44">
         <f ca="1">TODAY()-F33</f>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T33" s="25"/>
       <c r="U33" s="25"/>
@@ -4960,11 +4982,11 @@
       </c>
       <c r="N34" s="36">
         <f t="shared" ca="1" si="8"/>
-        <v>45916.129032258068</v>
+        <v>45916.225806451614</v>
       </c>
       <c r="O34" s="44">
         <f ca="1">TODAY()-F34</f>
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:28" x14ac:dyDescent="0.25">
@@ -5008,7 +5030,7 @@
       </c>
       <c r="N35" s="36">
         <f t="shared" ca="1" si="8"/>
-        <v>45976.129032258068</v>
+        <v>45976.225806451614</v>
       </c>
       <c r="T35" s="25"/>
       <c r="U35" s="25"/>
@@ -5298,11 +5320,11 @@
       <c r="F1" s="40"/>
       <c r="G1" s="39">
         <f ca="1">AVERAGE(G3:G106)</f>
-        <v>232.5</v>
+        <v>233</v>
       </c>
       <c r="H1" s="39">
         <f ca="1">AVERAGE(H3:H106)</f>
-        <v>29.0625</v>
+        <v>29.125</v>
       </c>
       <c r="I1" s="40"/>
       <c r="J1" s="40"/>
@@ -5436,11 +5458,11 @@
       </c>
       <c r="G3" s="47">
         <f ca="1">TODAY()-D3</f>
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H3" s="48">
         <f ca="1">G3/E3</f>
-        <v>22.875</v>
+        <v>23</v>
       </c>
       <c r="I3" s="49"/>
       <c r="J3" s="49"/>

--- a/Financial Analysis/Models.xlsx
+++ b/Financial Analysis/Models.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FDE143-B341-4D6D-9343-061F919DD4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4ABF243-B016-4595-AB0E-2BA1F129E14E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{40711DBD-7A53-4994-9FF1-9E754821B18D}"/>
   </bookViews>
@@ -197,7 +197,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Anton Mniszek:</t>
         </r>
@@ -206,7 +206,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 this would be interesting t model too, need t think through, maybe similar to no. of peaks? Or max rebound or something else</t>
@@ -276,7 +276,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="137">
   <si>
     <t>Tech</t>
   </si>
@@ -434,9 +434,6 @@
     <t>italic = predicted</t>
   </si>
   <si>
-    <t>bold = ongoing</t>
-  </si>
-  <si>
     <t>peak date + -50%</t>
   </si>
   <si>
@@ -485,9 +482,6 @@
     <t>FCEL (Q114)</t>
   </si>
   <si>
-    <t>PLUG</t>
-  </si>
-  <si>
     <t>SPCE (Q421)</t>
   </si>
   <si>
@@ -587,9 +581,6 @@
     <t>IONQ (Q324)</t>
   </si>
   <si>
-    <t>Hype/IPO</t>
-  </si>
-  <si>
     <t>BBAI (Q123)</t>
   </si>
   <si>
@@ -626,15 +617,9 @@
     <t>QUBT</t>
   </si>
   <si>
-    <t>HOOD</t>
-  </si>
-  <si>
     <t>SOUN</t>
   </si>
   <si>
-    <t>TEM</t>
-  </si>
-  <si>
     <t>Hype/fraud</t>
   </si>
   <si>
@@ -678,6 +663,30 @@
   </si>
   <si>
     <t>Price Variance</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>PLUG (Q220)</t>
+  </si>
+  <si>
+    <t>PLUG (Q225)</t>
+  </si>
+  <si>
+    <t>LIF</t>
+  </si>
+  <si>
+    <t>if missed -25%, wait for rebound after -25% then short to -50%?</t>
+  </si>
+  <si>
+    <t>bold/underline = ongoing</t>
+  </si>
+  <si>
+    <t>consider -22.5% instead of -25%, however weigh because this might be for short-term bubbles not for the very peak</t>
+  </si>
+  <si>
+    <t>time to -25% usually either up to two weeks, incorrect peak, or about 35-40 days</t>
   </si>
 </sst>
 </file>
@@ -689,7 +698,7 @@
     <numFmt numFmtId="165" formatCode="0.0\x"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -837,19 +846,6 @@
       <color theme="5" tint="0.39997558519241921"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -1032,7 +1028,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -1148,7 +1144,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="23" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="21" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="4" fontId="15" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1156,6 +1152,10 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="18" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -1194,13 +1194,13 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="N3">
-            <v>27.58173814816303</v>
+            <v>27.169241995324199</v>
           </cell>
           <cell r="T3">
-            <v>4.6317001586310811</v>
-          </cell>
-          <cell r="Z3">
-            <v>-0.29140664255030541</v>
+            <v>4.4621323257125018</v>
+          </cell>
+          <cell r="AA3">
+            <v>-0.27093209566711646</v>
           </cell>
         </row>
         <row r="5">
@@ -1300,22 +1300,22 @@
         </row>
         <row r="24">
           <cell r="B24" t="str">
-            <v>Fiserv</v>
+            <v>Roblox</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25" t="str">
-            <v>Roblox</v>
+            <v>Snowflake</v>
           </cell>
         </row>
         <row r="26">
           <cell r="B26" t="str">
-            <v>Snowflake</v>
+            <v>Coinbase</v>
           </cell>
         </row>
         <row r="27">
           <cell r="B27" t="str">
-            <v>Coinbase</v>
+            <v>Fiserv</v>
           </cell>
         </row>
         <row r="28">
@@ -1355,12 +1355,12 @@
         </row>
         <row r="35">
           <cell r="B35" t="str">
-            <v>Zoom Video</v>
+            <v>IonQ</v>
           </cell>
         </row>
         <row r="36">
           <cell r="B36" t="str">
-            <v>Snap Inc</v>
+            <v>Zoom Video</v>
           </cell>
         </row>
         <row r="37">
@@ -1370,17 +1370,17 @@
         </row>
         <row r="38">
           <cell r="B38" t="str">
-            <v>Duolingo</v>
+            <v>Snap Inc</v>
           </cell>
         </row>
         <row r="39">
           <cell r="B39" t="str">
-            <v>Rigetti</v>
+            <v>Duolingo</v>
           </cell>
         </row>
         <row r="40">
           <cell r="B40" t="str">
-            <v>IonQ</v>
+            <v>Rigetti</v>
           </cell>
         </row>
         <row r="41">
@@ -1420,22 +1420,22 @@
         </row>
         <row r="48">
           <cell r="B48" t="str">
-            <v>Stride</v>
+            <v>Wise</v>
           </cell>
         </row>
         <row r="49">
           <cell r="B49" t="str">
-            <v>Wise</v>
+            <v>PagSeguro</v>
           </cell>
         </row>
         <row r="50">
           <cell r="B50" t="str">
-            <v>PagSeguro</v>
+            <v>Paysafe</v>
           </cell>
         </row>
         <row r="51">
           <cell r="B51" t="str">
-            <v>Paysafe</v>
+            <v>Stride</v>
           </cell>
         </row>
         <row r="52">
@@ -1455,27 +1455,27 @@
         </row>
         <row r="55">
           <cell r="B55" t="str">
-            <v>Coursera</v>
+            <v>Corsair Gaming</v>
           </cell>
         </row>
         <row r="56">
           <cell r="B56" t="str">
-            <v>Corsair Gaming</v>
+            <v>Coursera</v>
           </cell>
         </row>
         <row r="57">
           <cell r="B57" t="str">
-            <v>Fiverr</v>
+            <v>Bandwidth</v>
           </cell>
         </row>
         <row r="58">
           <cell r="B58" t="str">
-            <v>Bandwidth</v>
+            <v>Ambiq Micro</v>
           </cell>
         </row>
         <row r="59">
           <cell r="B59" t="str">
-            <v>Ambiq Micro</v>
+            <v>Fiverr</v>
           </cell>
         </row>
         <row r="60">
@@ -1515,106 +1515,101 @@
         </row>
         <row r="67">
           <cell r="B67" t="str">
-            <v>MicroAlgo</v>
+            <v>Skillz</v>
           </cell>
         </row>
         <row r="68">
           <cell r="B68" t="str">
-            <v>Skillz</v>
+            <v>Arqit Quantum</v>
           </cell>
         </row>
         <row r="69">
           <cell r="B69" t="str">
-            <v>Arqit Quantum</v>
+            <v>Hewlett-Packard</v>
           </cell>
         </row>
         <row r="70">
           <cell r="B70" t="str">
-            <v>Hewlett-Packard</v>
+            <v>HP Enterprise</v>
           </cell>
         </row>
         <row r="71">
           <cell r="B71" t="str">
-            <v>HP Enterprise</v>
+            <v>Dell</v>
           </cell>
         </row>
         <row r="72">
           <cell r="B72" t="str">
-            <v>Dell</v>
+            <v>Electronic Arts</v>
           </cell>
         </row>
         <row r="73">
           <cell r="B73" t="str">
-            <v>Electronic Arts</v>
+            <v>Shopify</v>
           </cell>
         </row>
         <row r="74">
           <cell r="B74" t="str">
-            <v>Shopify</v>
+            <v>IBM</v>
           </cell>
         </row>
         <row r="75">
           <cell r="B75" t="str">
-            <v>IBM</v>
+            <v>Xiaomi</v>
           </cell>
         </row>
         <row r="76">
           <cell r="B76" t="str">
-            <v>Xiaomi</v>
+            <v>Uber</v>
           </cell>
         </row>
         <row r="77">
           <cell r="B77" t="str">
-            <v>Uber</v>
+            <v>Disney</v>
           </cell>
         </row>
         <row r="78">
           <cell r="B78" t="str">
-            <v>Disney</v>
+            <v>Pinterest</v>
           </cell>
         </row>
         <row r="79">
           <cell r="B79" t="str">
-            <v>Pinterest</v>
+            <v>Freshworks</v>
           </cell>
         </row>
         <row r="80">
           <cell r="B80" t="str">
-            <v>Freshworks</v>
+            <v>eBay</v>
           </cell>
         </row>
         <row r="81">
           <cell r="B81" t="str">
-            <v>eBay</v>
+            <v>Xerox</v>
           </cell>
         </row>
         <row r="82">
           <cell r="B82" t="str">
-            <v>Xerox</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="B83" t="str">
             <v>Alibaba</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="B85" t="str">
+            <v>Taiwan Semiconductor</v>
           </cell>
         </row>
         <row r="86">
           <cell r="B86" t="str">
-            <v>Taiwan Semiconductor</v>
+            <v>ASML</v>
           </cell>
         </row>
         <row r="87">
           <cell r="B87" t="str">
-            <v>ASML</v>
+            <v>Broadcom</v>
           </cell>
         </row>
         <row r="88">
           <cell r="B88" t="str">
-            <v>Broadcom</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="B89" t="str">
             <v>Qualcomm</v>
           </cell>
         </row>
@@ -1641,10 +1636,10 @@
             <v>16.412502823367006</v>
           </cell>
           <cell r="U3">
-            <v>0.96851754398012357</v>
+            <v>1.0405324209773694</v>
           </cell>
           <cell r="AA3">
-            <v>-0.19797272187116063</v>
+            <v>-0.24824550873827725</v>
           </cell>
         </row>
         <row r="4">
@@ -1781,23 +1776,21 @@
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
+      <sheetName val="Models (Retail)"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
           <cell r="O3">
-            <v>30.068644764713405</v>
+            <v>29.266571548241291</v>
           </cell>
           <cell r="U3">
-            <v>0.99923487105066666</v>
-          </cell>
-          <cell r="AA3">
-            <v>-0.22397093414271882</v>
+            <v>1.3971942342652697</v>
+          </cell>
+          <cell r="AB3">
+            <v>-0.21162257953759367</v>
           </cell>
         </row>
         <row r="4">
@@ -1812,22 +1805,22 @@
         </row>
         <row r="6">
           <cell r="B6" t="str">
-            <v>TKMaxx</v>
+            <v>Hermès</v>
           </cell>
         </row>
         <row r="7">
           <cell r="B7" t="str">
-            <v>Nike</v>
+            <v>TKMaxx</v>
           </cell>
         </row>
         <row r="8">
           <cell r="B8" t="str">
-            <v>Hermès</v>
+            <v>Inditex</v>
           </cell>
         </row>
         <row r="9">
           <cell r="B9" t="str">
-            <v>Inditex</v>
+            <v>Nike</v>
           </cell>
         </row>
         <row r="10">
@@ -1852,7 +1845,7 @@
         </row>
         <row r="14">
           <cell r="B14" t="str">
-            <v>Farfetch</v>
+            <v>Lululemon</v>
           </cell>
         </row>
         <row r="15">
@@ -1976,6 +1969,7 @@
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1992,19 +1986,23 @@
       <sheetName val="FY2026 DoD Budget Materials"/>
       <sheetName val="DoD Products"/>
       <sheetName val="Future Products"/>
-      <sheetName val="Global Revenue"/>
+      <sheetName val="RawData"/>
+      <sheetName val="PivotTable"/>
+      <sheetName val="Subsidiaries"/>
+      <sheetName val="ProgramBreakdown"/>
+      <sheetName val="Wargaming"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
           <cell r="R3">
-            <v>37.145030304683814</v>
+            <v>37.082954294919055</v>
           </cell>
           <cell r="AE3">
-            <v>2.9293484226775894</v>
+            <v>3.0547812365039473</v>
           </cell>
           <cell r="AL3">
-            <v>-0.46900509315888117</v>
+            <v>-0.47586149868430783</v>
           </cell>
         </row>
         <row r="4">
@@ -2049,12 +2047,12 @@
         </row>
         <row r="12">
           <cell r="B12" t="str">
-            <v>Rheinmetall</v>
+            <v>Rolls Royce</v>
           </cell>
         </row>
         <row r="13">
           <cell r="B13" t="str">
-            <v>Rolls Royce</v>
+            <v>Rheinmetall</v>
           </cell>
         </row>
         <row r="14">
@@ -2074,17 +2072,17 @@
         </row>
         <row r="17">
           <cell r="B17" t="str">
-            <v>Anduril</v>
+            <v>Dassault</v>
           </cell>
         </row>
         <row r="18">
           <cell r="B18" t="str">
-            <v>Dassault</v>
+            <v>Leonardo</v>
           </cell>
         </row>
         <row r="19">
           <cell r="B19" t="str">
-            <v>Leonardo</v>
+            <v>Anduril</v>
           </cell>
         </row>
         <row r="20">
@@ -2137,6 +2135,9 @@
             <v>Unusual Machines</v>
           </cell>
         </row>
+        <row r="30">
+          <cell r="B30"/>
+        </row>
         <row r="31">
           <cell r="B31" t="str">
             <v>SAAB</v>
@@ -2162,11 +2163,65 @@
             <v>Sierra Nevada</v>
           </cell>
         </row>
+        <row r="36">
+          <cell r="B36" t="str">
+            <v>General Electric</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="B37" t="str">
+            <v>National Presto</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="B38" t="str">
+            <v>Patria</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="B39" t="str">
+            <v>Kongsberg</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="B40" t="str">
+            <v>Oshkosh</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="B41" t="str">
+            <v>Babcock?</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="B42" t="str">
+            <v>GKN</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="B43" t="str">
+            <v>Avio</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="B44" t="str">
+            <v>QinetiQ</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="B45" t="str">
+            <v>KNDS</v>
+          </cell>
+        </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2230,7 +2285,7 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="AC3">
-            <v>-0.83830827653230344</v>
+            <v>-0.7852827016272812</v>
           </cell>
         </row>
         <row r="4">
@@ -2610,26 +2665,26 @@
       </c>
       <c r="C3" s="18">
         <f>COUNTA([1]Models!$B$5:$B$1048576)</f>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D3" s="19">
-        <f>[1]Models!$Z$3</f>
-        <v>-0.29140664255030541</v>
+        <f>[1]Models!$AA$3</f>
+        <v>-0.27093209566711646</v>
       </c>
       <c r="E3" s="21">
         <f>[1]Models!$N$3</f>
-        <v>27.58173814816303</v>
+        <v>27.169241995324199</v>
       </c>
       <c r="F3" s="22">
         <f>[1]Models!$T$3</f>
-        <v>4.6317001586310811</v>
+        <v>4.4621323257125018</v>
       </c>
       <c r="G3" s="15">
         <v>45932</v>
       </c>
       <c r="H3" s="15">
         <f ca="1">TODAY()</f>
-        <v>45940</v>
+        <v>45968</v>
       </c>
       <c r="K3" s="17" t="s">
         <v>7</v>
@@ -2645,7 +2700,7 @@
       </c>
       <c r="D4" s="19">
         <f>[2]Main!$AA$3</f>
-        <v>-0.19797272187116063</v>
+        <v>-0.24824550873827725</v>
       </c>
       <c r="E4" s="21">
         <f>[2]Main!$O$3</f>
@@ -2653,14 +2708,14 @@
       </c>
       <c r="F4" s="22">
         <f>[2]Main!$U$3</f>
-        <v>0.96851754398012357</v>
+        <v>1.0405324209773694</v>
       </c>
       <c r="K4" s="57" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="57" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="18">
@@ -2668,16 +2723,16 @@
         <v>35</v>
       </c>
       <c r="D5" s="19">
-        <f>[3]Main!$AA$3</f>
-        <v>-0.22397093414271882</v>
+        <f>[3]Main!$AB$3</f>
+        <v>-0.21162257953759367</v>
       </c>
       <c r="E5" s="21">
         <f>[3]Main!$O$3</f>
-        <v>30.068644764713405</v>
+        <v>29.266571548241291</v>
       </c>
       <c r="F5" s="22">
         <f>[3]Main!$U$3</f>
-        <v>0.99923487105066666</v>
+        <v>1.3971942342652697</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
@@ -2686,19 +2741,19 @@
       </c>
       <c r="C6" s="18">
         <f>COUNTA([4]Main!$B$4:$B$1048576)</f>
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D6" s="19">
         <f>[4]Main!$AL$3</f>
-        <v>-0.46900509315888117</v>
+        <v>-0.47586149868430783</v>
       </c>
       <c r="E6" s="21">
         <f>[4]Main!$R$3</f>
-        <v>37.145030304683814</v>
+        <v>37.082954294919055</v>
       </c>
       <c r="F6" s="22">
         <f>[4]Main!$AE$3</f>
-        <v>2.9293484226775894</v>
+        <v>3.0547812365039473</v>
       </c>
       <c r="K6" s="12" t="s">
         <v>36</v>
@@ -2739,7 +2794,7 @@
       </c>
       <c r="D8" s="19">
         <f>[6]Main!$AC$3</f>
-        <v>-0.83830827653230344</v>
+        <v>-0.7852827016272812</v>
       </c>
       <c r="E8" s="21"/>
       <c r="F8" s="20"/>
@@ -2756,19 +2811,19 @@
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C9" s="18">
         <f>SUM(C3:C8)</f>
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="D9" s="19">
         <f>AVERAGE(D3:D8)</f>
-        <v>-0.44579661969308271</v>
+        <v>-0.44101007235961714</v>
       </c>
       <c r="E9" s="21">
         <f>AVERAGE(E3:E8)</f>
-        <v>27.801979010231811</v>
+        <v>27.482817665462889</v>
       </c>
       <c r="F9" s="22">
         <f>AVERAGE(F3:F8)</f>
-        <v>7.6508040589170152</v>
+        <v>7.73597190314094</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>33</v>
@@ -2960,139 +3015,139 @@
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E1" s="41">
         <f>AVERAGE(E3:E105)</f>
-        <v>4.1428571428571432</v>
+        <v>4.4594594594594597</v>
       </c>
       <c r="F1" s="40"/>
       <c r="G1" s="39">
         <f>AVERAGE(G3:G105)</f>
-        <v>116.25714285714285</v>
+        <v>124.43243243243244</v>
       </c>
       <c r="H1" s="39">
         <f>AVERAGE(H3:H105)</f>
-        <v>26.695102040816327</v>
+        <v>26.578217503217505</v>
       </c>
       <c r="I1" s="40"/>
       <c r="J1" s="40"/>
       <c r="K1" s="40"/>
       <c r="L1" s="39">
-        <f>AVERAGE(L3:L105)</f>
-        <v>10.7</v>
+        <f ca="1">AVERAGE(L3:L105)</f>
+        <v>11.058823529411764</v>
       </c>
       <c r="M1" s="40"/>
       <c r="N1" s="40"/>
       <c r="O1" s="39">
         <f ca="1">AVERAGE(O3:O105)</f>
-        <v>43.225806451612904</v>
+        <v>42.862068965517238</v>
       </c>
       <c r="P1" s="26"/>
       <c r="Q1" s="26"/>
       <c r="R1" s="26"/>
       <c r="V1" s="26">
-        <f>AVERAGE(V4:V43)</f>
+        <f>AVERAGE(V4:V45)</f>
         <v>297.125</v>
       </c>
       <c r="W1" s="26"/>
       <c r="X1" s="26"/>
       <c r="Y1" s="26"/>
       <c r="AB1" s="26">
-        <f>AVERAGE(AB4:AB43)</f>
+        <f>AVERAGE(AB4:AB45)</f>
         <v>705.5</v>
       </c>
       <c r="AC1" s="26"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B2" s="24" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J2" s="25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K2" s="25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L2" s="25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M2" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="N2" s="25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="O2" s="25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P2" s="25" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Q2" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="R2" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="S2" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="T2" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="U2" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="V2" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="R2" s="25" t="s">
+      <c r="W2" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="S2" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="T2" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="U2" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="V2" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="W2" s="25" t="s">
-        <v>81</v>
-      </c>
       <c r="X2" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="Y2" s="25" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Z2" s="25" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AA2" s="25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AB2" s="25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B3" s="24" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D3" s="27">
         <v>39707</v>
@@ -3104,29 +3159,29 @@
         <v>39749</v>
       </c>
       <c r="G3" s="25">
-        <f t="shared" ref="G3:G37" si="0">F3-D3</f>
+        <f t="shared" ref="G3:G39" si="0">F3-D3</f>
         <v>42</v>
       </c>
       <c r="H3" s="25">
-        <f t="shared" ref="H3:H37" si="1">G3/E3</f>
+        <f t="shared" ref="H3:H39" si="1">G3/E3</f>
         <v>14</v>
       </c>
       <c r="I3" s="29">
         <v>945</v>
       </c>
       <c r="J3" s="29">
-        <f t="shared" ref="J3:J37" si="2">I3*0.75</f>
+        <f t="shared" ref="J3:J39" si="2">I3*0.75</f>
         <v>708.75</v>
       </c>
       <c r="K3" s="27">
         <v>39750</v>
       </c>
       <c r="L3" s="25">
-        <f t="shared" ref="L3:L28" si="3">K3-F3</f>
+        <f t="shared" ref="L3:L32" si="3">K3-F3</f>
         <v>1</v>
       </c>
       <c r="M3" s="29">
-        <f t="shared" ref="M3:M37" si="4">I3*0.5</f>
+        <f t="shared" ref="M3:M39" si="4">I3*0.5</f>
         <v>472.5</v>
       </c>
       <c r="N3" s="27">
@@ -3139,10 +3194,10 @@
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B4" s="24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D4" s="27">
         <v>41642</v>
@@ -3193,10 +3248,10 @@
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D5" s="27">
         <v>43045</v>
@@ -3247,10 +3302,10 @@
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B6" s="24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="D6" s="27">
         <v>43327</v>
@@ -3327,10 +3382,10 @@
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B7" s="24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="D7" s="27">
         <v>43591</v>
@@ -3407,10 +3462,10 @@
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B8" s="24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D8" s="27">
         <v>43808</v>
@@ -3487,7 +3542,7 @@
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B9" s="24" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C9" s="25" t="s">
         <v>50</v>
@@ -3561,10 +3616,10 @@
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B10" s="24" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D10" s="27">
         <v>43906</v>
@@ -3641,10 +3696,10 @@
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B11" s="24" t="s">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D11" s="27">
         <v>43986</v>
@@ -3702,10 +3757,10 @@
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B12" s="24" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D12" s="27">
         <v>44074</v>
@@ -3756,10 +3811,10 @@
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B13" s="24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" s="27">
         <v>44098</v>
@@ -3819,10 +3874,10 @@
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B14" s="24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" s="27">
         <v>44111</v>
@@ -3873,10 +3928,10 @@
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B15" s="24" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" s="27">
         <v>44207</v>
@@ -3953,10 +4008,10 @@
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B16" s="24" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D16" s="27">
         <v>44215</v>
@@ -4034,10 +4089,10 @@
     </row>
     <row r="17" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B17" s="24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" s="27">
         <v>44510</v>
@@ -4088,10 +4143,10 @@
     </row>
     <row r="18" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B18" s="24" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D18" s="27">
         <v>44617</v>
@@ -4142,10 +4197,10 @@
     </row>
     <row r="19" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B19" s="24" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D19" s="27">
         <v>44938</v>
@@ -4196,10 +4251,10 @@
     </row>
     <row r="20" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B20" s="24" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D20" s="27">
         <v>45482</v>
@@ -4250,10 +4305,10 @@
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B21" s="24" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D21" s="27">
         <v>45488</v>
@@ -4300,10 +4355,10 @@
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B22" s="24" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D22" s="27">
         <v>45512</v>
@@ -4350,10 +4405,10 @@
     </row>
     <row r="23" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B23" s="24" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D23" s="27">
         <v>45562</v>
@@ -4409,10 +4464,10 @@
     </row>
     <row r="24" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B24" s="24" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D24" s="27">
         <v>45579</v>
@@ -4463,10 +4518,10 @@
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B25" s="24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D25" s="27">
         <v>45581</v>
@@ -4522,7 +4577,7 @@
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B26" s="24" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C26" s="25" t="s">
         <v>50</v>
@@ -4572,10 +4627,10 @@
     </row>
     <row r="27" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B27" s="24" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D27" s="27">
         <v>45593</v>
@@ -4622,10 +4677,10 @@
     </row>
     <row r="28" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B28" s="24" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D28" s="27">
         <v>45595</v>
@@ -4672,58 +4727,56 @@
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B29" s="35" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D29" s="27">
         <v>45601</v>
       </c>
-      <c r="E29" s="25">
-        <v>6</v>
+      <c r="E29" s="37">
+        <v>8</v>
       </c>
       <c r="F29" s="36">
-        <v>45881</v>
+        <v>45964</v>
       </c>
       <c r="G29" s="25">
-        <f>F29-D29</f>
-        <v>280</v>
+        <f t="shared" si="0"/>
+        <v>363</v>
       </c>
       <c r="H29" s="34">
-        <f>G29/E29</f>
-        <v>46.666666666666664</v>
-      </c>
-      <c r="I29" s="29">
-        <v>186.97</v>
+        <f t="shared" si="1"/>
+        <v>45.375</v>
+      </c>
+      <c r="I29" s="38">
+        <v>207.18</v>
       </c>
       <c r="J29" s="29">
         <f t="shared" si="2"/>
-        <v>140.22749999999999</v>
-      </c>
-      <c r="K29" s="55">
-        <f>F29+$L$1</f>
-        <v>45891.7</v>
-      </c>
+        <v>155.38499999999999</v>
+      </c>
+      <c r="K29" s="36">
+        <f t="shared" ref="K29:K34" ca="1" si="8">F29+$L$1</f>
+        <v>45975.058823529413</v>
+      </c>
+      <c r="L29" s="44"/>
       <c r="M29" s="29">
         <f t="shared" si="4"/>
-        <v>93.484999999999999</v>
+        <v>103.59</v>
       </c>
       <c r="N29" s="36">
-        <f t="shared" ref="N29:N35" ca="1" si="8">F29+$O$1</f>
-        <v>45924.225806451614</v>
-      </c>
-      <c r="O29" s="44">
-        <f ca="1">TODAY()-F29</f>
-        <v>59</v>
-      </c>
+        <f t="shared" ref="N29:N36" ca="1" si="9">F29+$O$1</f>
+        <v>46006.862068965514</v>
+      </c>
+      <c r="O29" s="44"/>
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B30" s="35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D30" s="27">
         <v>45671</v>
@@ -4731,35 +4784,38 @@
       <c r="E30" s="25">
         <v>7</v>
       </c>
-      <c r="F30" s="36">
-        <v>45933</v>
+      <c r="F30" s="27">
+        <v>45945</v>
       </c>
       <c r="G30" s="25">
         <f t="shared" si="0"/>
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="H30" s="34">
         <f t="shared" si="1"/>
-        <v>37.428571428571431</v>
-      </c>
-      <c r="I30" s="38">
-        <v>37.57</v>
+        <v>39.142857142857146</v>
+      </c>
+      <c r="I30" s="29">
+        <v>56.34</v>
       </c>
       <c r="J30" s="29">
         <f t="shared" si="2"/>
-        <v>28.177500000000002</v>
-      </c>
-      <c r="K30" s="36">
-        <f>F30+$L$1</f>
-        <v>45943.7</v>
+        <v>42.255000000000003</v>
+      </c>
+      <c r="K30" s="27">
+        <v>45951</v>
+      </c>
+      <c r="L30" s="34">
+        <f t="shared" si="3"/>
+        <v>6</v>
       </c>
       <c r="M30" s="29">
         <f t="shared" si="4"/>
-        <v>18.785</v>
+        <v>28.17</v>
       </c>
       <c r="N30" s="36">
-        <f t="shared" ca="1" si="8"/>
-        <v>45976.225806451614</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>45987.862068965514</v>
       </c>
       <c r="O30" s="28"/>
       <c r="T30" s="25"/>
@@ -4774,46 +4830,49 @@
     </row>
     <row r="31" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B31" s="35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D31" s="27">
         <v>45728</v>
       </c>
       <c r="E31" s="25">
-        <v>5</v>
-      </c>
-      <c r="F31" s="36">
-        <v>45923</v>
+        <v>6</v>
+      </c>
+      <c r="F31" s="27">
+        <v>45943</v>
       </c>
       <c r="G31" s="25">
         <f t="shared" si="0"/>
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="H31" s="34">
         <f t="shared" si="1"/>
-        <v>39</v>
-      </c>
-      <c r="I31" s="38">
-        <v>75.14</v>
+        <v>35.833333333333336</v>
+      </c>
+      <c r="I31" s="29">
+        <v>82.09</v>
       </c>
       <c r="J31" s="29">
         <f t="shared" si="2"/>
-        <v>56.355000000000004</v>
-      </c>
-      <c r="K31" s="36">
-        <f>F31+$L$1</f>
-        <v>45933.7</v>
+        <v>61.567500000000003</v>
+      </c>
+      <c r="K31" s="27">
+        <v>45950</v>
+      </c>
+      <c r="L31" s="34">
+        <f t="shared" si="3"/>
+        <v>7</v>
       </c>
       <c r="M31" s="29">
         <f t="shared" si="4"/>
-        <v>37.57</v>
+        <v>41.045000000000002</v>
       </c>
       <c r="N31" s="36">
-        <f t="shared" ca="1" si="8"/>
-        <v>45966.225806451614</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>45985.862068965514</v>
       </c>
       <c r="T31" s="25"/>
       <c r="U31" s="25"/>
@@ -4827,46 +4886,49 @@
     </row>
     <row r="32" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B32" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D32" s="27">
         <v>45754</v>
       </c>
       <c r="E32" s="25">
-        <v>6</v>
-      </c>
-      <c r="F32" s="36">
-        <v>45923</v>
+        <v>7</v>
+      </c>
+      <c r="F32" s="27">
+        <v>45944</v>
       </c>
       <c r="G32" s="25">
         <f t="shared" si="0"/>
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="H32" s="34">
         <f t="shared" si="1"/>
-        <v>28.166666666666668</v>
+        <v>27.142857142857142</v>
       </c>
       <c r="I32" s="29">
-        <v>142.65</v>
+        <v>174.14</v>
       </c>
       <c r="J32" s="29">
         <f t="shared" si="2"/>
-        <v>106.98750000000001</v>
-      </c>
-      <c r="K32" s="36">
-        <f>F32+$L$1</f>
-        <v>45933.7</v>
+        <v>130.60499999999999</v>
+      </c>
+      <c r="K32" s="27">
+        <v>45952</v>
+      </c>
+      <c r="L32" s="34">
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="M32" s="29">
         <f t="shared" si="4"/>
-        <v>71.325000000000003</v>
+        <v>87.07</v>
       </c>
       <c r="N32" s="36">
-        <f t="shared" ca="1" si="8"/>
-        <v>45966.225806451614</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>45986.862068965514</v>
       </c>
       <c r="T32" s="25"/>
       <c r="U32" s="25"/>
@@ -4880,53 +4942,50 @@
     </row>
     <row r="33" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B33" s="35" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D33" s="27">
         <v>45756</v>
       </c>
-      <c r="E33" s="25">
+      <c r="E33" s="37">
         <v>6</v>
       </c>
       <c r="F33" s="36">
-        <v>45874</v>
+        <v>45936</v>
       </c>
       <c r="G33" s="25">
         <f t="shared" si="0"/>
-        <v>118</v>
+        <v>180</v>
       </c>
       <c r="H33" s="34">
         <f t="shared" si="1"/>
-        <v>19.666666666666668</v>
-      </c>
-      <c r="I33" s="29">
-        <v>63.21</v>
+        <v>30</v>
+      </c>
+      <c r="I33" s="38">
+        <v>110.89</v>
       </c>
       <c r="J33" s="29">
         <f t="shared" si="2"/>
-        <v>47.407499999999999</v>
-      </c>
-      <c r="K33" s="27">
-        <v>45888</v>
-      </c>
-      <c r="L33" s="34">
-        <f>K33-F33</f>
-        <v>14</v>
+        <v>83.167500000000004</v>
+      </c>
+      <c r="K33" s="55">
+        <f t="shared" ca="1" si="8"/>
+        <v>45947.058823529413</v>
+      </c>
+      <c r="L33" s="44">
+        <f ca="1">TODAY()-F33</f>
+        <v>32</v>
       </c>
       <c r="M33" s="29">
         <f t="shared" si="4"/>
-        <v>31.605</v>
+        <v>55.445</v>
       </c>
       <c r="N33" s="36">
-        <f t="shared" ca="1" si="8"/>
-        <v>45917.225806451614</v>
-      </c>
-      <c r="O33" s="44">
-        <f ca="1">TODAY()-F33</f>
-        <v>66</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>45978.862068965514</v>
       </c>
       <c r="T33" s="25"/>
       <c r="U33" s="25"/>
@@ -4940,61 +4999,64 @@
     </row>
     <row r="34" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B34" s="35" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D34" s="27">
         <v>45756</v>
       </c>
-      <c r="E34" s="25">
-        <v>5</v>
-      </c>
-      <c r="F34" s="27">
-        <v>45873</v>
+      <c r="E34" s="37">
+        <v>8</v>
+      </c>
+      <c r="F34" s="36">
+        <v>45945</v>
       </c>
       <c r="G34" s="25">
         <f t="shared" si="0"/>
-        <v>117</v>
+        <v>189</v>
       </c>
       <c r="H34" s="34">
         <f t="shared" si="1"/>
-        <v>23.4</v>
-      </c>
-      <c r="I34" s="29">
-        <v>20.39</v>
+        <v>23.625</v>
+      </c>
+      <c r="I34" s="38">
+        <v>75.36</v>
       </c>
       <c r="J34" s="29">
         <f t="shared" si="2"/>
-        <v>15.2925</v>
-      </c>
-      <c r="K34" s="27">
-        <v>45888</v>
-      </c>
-      <c r="L34" s="34">
-        <f>K34-F34</f>
-        <v>15</v>
+        <v>56.519999999999996</v>
+      </c>
+      <c r="K34" s="36">
+        <f t="shared" ca="1" si="8"/>
+        <v>45956.058823529413</v>
       </c>
       <c r="M34" s="29">
         <f t="shared" si="4"/>
-        <v>10.195</v>
+        <v>37.68</v>
       </c>
       <c r="N34" s="36">
-        <f t="shared" ca="1" si="8"/>
-        <v>45916.225806451614</v>
-      </c>
-      <c r="O34" s="44">
-        <f ca="1">TODAY()-F34</f>
-        <v>67</v>
-      </c>
+        <f t="shared" ca="1" si="9"/>
+        <v>45987.862068965514</v>
+      </c>
+      <c r="O34" s="44"/>
+      <c r="T34" s="25"/>
+      <c r="U34" s="25"/>
+      <c r="V34" s="25"/>
+      <c r="W34" s="25"/>
+      <c r="X34" s="25"/>
+      <c r="Y34" s="25"/>
+      <c r="Z34" s="25"/>
+      <c r="AA34" s="25"/>
+      <c r="AB34" s="25"/>
     </row>
     <row r="35" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B35" s="35" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D35" s="27">
         <v>45756</v>
@@ -5002,94 +5064,86 @@
       <c r="E35" s="25">
         <v>5</v>
       </c>
-      <c r="F35" s="36">
-        <v>45933</v>
+      <c r="F35" s="27">
+        <v>45873</v>
       </c>
       <c r="G35" s="25">
         <f t="shared" si="0"/>
-        <v>177</v>
+        <v>117</v>
       </c>
       <c r="H35" s="34">
         <f t="shared" si="1"/>
-        <v>35.4</v>
+        <v>23.4</v>
       </c>
       <c r="I35" s="29">
-        <v>92.32</v>
+        <v>20.39</v>
       </c>
       <c r="J35" s="29">
         <f t="shared" si="2"/>
-        <v>69.239999999999995</v>
-      </c>
-      <c r="K35" s="36">
-        <f>F35+$L$1</f>
-        <v>45943.7</v>
+        <v>15.2925</v>
+      </c>
+      <c r="K35" s="27">
+        <v>45888</v>
+      </c>
+      <c r="L35" s="34">
+        <f>K35-F35</f>
+        <v>15</v>
       </c>
       <c r="M35" s="29">
         <f t="shared" si="4"/>
-        <v>46.16</v>
-      </c>
-      <c r="N35" s="36">
-        <f t="shared" ca="1" si="8"/>
-        <v>45976.225806451614</v>
-      </c>
-      <c r="T35" s="25"/>
-      <c r="U35" s="25"/>
-      <c r="V35" s="25"/>
-      <c r="W35" s="25"/>
-      <c r="X35" s="25"/>
-      <c r="Y35" s="25"/>
-      <c r="Z35" s="25"/>
-      <c r="AA35" s="25"/>
-      <c r="AB35" s="25"/>
+        <v>10.195</v>
+      </c>
+      <c r="N35" s="55">
+        <f t="shared" ca="1" si="9"/>
+        <v>45915.862068965514</v>
+      </c>
+      <c r="O35" s="44">
+        <f ca="1">TODAY()-F35</f>
+        <v>95</v>
+      </c>
     </row>
     <row r="36" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B36" s="24" t="s">
-        <v>120</v>
+      <c r="B36" s="35" t="s">
+        <v>106</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="D36" s="27">
-        <v>45779</v>
-      </c>
-      <c r="E36" s="25">
-        <v>3</v>
-      </c>
-      <c r="F36" s="27">
-        <v>45828</v>
+        <v>45756</v>
+      </c>
+      <c r="E36" s="37">
+        <v>5</v>
+      </c>
+      <c r="F36" s="36">
+        <v>45938</v>
       </c>
       <c r="G36" s="25">
         <f t="shared" si="0"/>
-        <v>49</v>
+        <v>182</v>
       </c>
       <c r="H36" s="34">
         <f t="shared" si="1"/>
-        <v>16.333333333333332</v>
-      </c>
-      <c r="I36" s="29">
-        <v>183.58</v>
+        <v>36.4</v>
+      </c>
+      <c r="I36" s="38">
+        <v>105.67</v>
       </c>
       <c r="J36" s="29">
         <f t="shared" si="2"/>
-        <v>137.685</v>
-      </c>
-      <c r="K36" s="27">
-        <v>45849</v>
-      </c>
-      <c r="L36" s="34">
-        <f>K36-F36</f>
-        <v>21</v>
+        <v>79.252499999999998</v>
+      </c>
+      <c r="K36" s="36">
+        <f ca="1">F36+$L$1</f>
+        <v>45949.058823529413</v>
       </c>
       <c r="M36" s="29">
         <f t="shared" si="4"/>
-        <v>91.79</v>
-      </c>
-      <c r="N36" s="27">
-        <v>45889</v>
-      </c>
-      <c r="O36" s="25">
-        <f>+N36-F36</f>
-        <v>61</v>
+        <v>52.835000000000001</v>
+      </c>
+      <c r="N36" s="36">
+        <f t="shared" ca="1" si="9"/>
+        <v>45980.862068965514</v>
       </c>
       <c r="T36" s="25"/>
       <c r="U36" s="25"/>
@@ -5103,52 +5157,52 @@
     </row>
     <row r="37" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B37" s="24" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="D37" s="27">
-        <v>45814</v>
+        <v>45779</v>
       </c>
       <c r="E37" s="25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" s="27">
-        <v>45831</v>
+        <v>45828</v>
       </c>
       <c r="G37" s="25">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="H37" s="34">
         <f t="shared" si="1"/>
-        <v>8.5</v>
+        <v>16.333333333333332</v>
       </c>
       <c r="I37" s="29">
-        <v>263.45</v>
+        <v>183.58</v>
       </c>
       <c r="J37" s="29">
         <f t="shared" si="2"/>
-        <v>197.58749999999998</v>
+        <v>137.685</v>
       </c>
       <c r="K37" s="27">
-        <v>45835</v>
+        <v>45849</v>
       </c>
       <c r="L37" s="34">
         <f>K37-F37</f>
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="M37" s="29">
         <f t="shared" si="4"/>
-        <v>131.72499999999999</v>
+        <v>91.79</v>
       </c>
       <c r="N37" s="27">
-        <v>45888</v>
+        <v>45889</v>
       </c>
       <c r="O37" s="25">
         <f>+N37-F37</f>
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="T37" s="25"/>
       <c r="U37" s="25"/>
@@ -5161,75 +5215,185 @@
       <c r="AB37" s="25"/>
     </row>
     <row r="38" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B38" s="24" t="s">
-        <v>49</v>
-      </c>
+      <c r="B38" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38" s="27">
+        <v>45793</v>
+      </c>
+      <c r="E38" s="25">
+        <v>8</v>
+      </c>
+      <c r="F38" s="27">
+        <v>45936</v>
+      </c>
+      <c r="G38" s="25">
+        <f t="shared" si="0"/>
+        <v>143</v>
+      </c>
+      <c r="H38" s="34">
+        <f t="shared" si="1"/>
+        <v>17.875</v>
+      </c>
+      <c r="I38" s="29">
+        <v>4.13</v>
+      </c>
+      <c r="J38" s="29">
+        <f t="shared" si="2"/>
+        <v>3.0975000000000001</v>
+      </c>
+      <c r="K38" s="27">
+        <v>45952</v>
+      </c>
+      <c r="L38" s="34">
+        <f>K38-F38</f>
+        <v>16</v>
+      </c>
+      <c r="M38" s="29">
+        <f t="shared" si="4"/>
+        <v>2.0649999999999999</v>
+      </c>
+      <c r="N38" s="36">
+        <f ca="1">F38+$O$1</f>
+        <v>45978.862068965514</v>
+      </c>
+      <c r="T38" s="25"/>
+      <c r="U38" s="25"/>
+      <c r="V38" s="25"/>
+      <c r="W38" s="25"/>
+      <c r="X38" s="25"/>
+      <c r="Y38" s="25"/>
+      <c r="Z38" s="25"/>
+      <c r="AA38" s="25"/>
+      <c r="AB38" s="25"/>
     </row>
     <row r="39" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B39" s="24" t="s">
-        <v>48</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="D39" s="27">
+        <v>45814</v>
+      </c>
+      <c r="E39" s="25">
+        <v>2</v>
+      </c>
+      <c r="F39" s="27">
+        <v>45831</v>
+      </c>
+      <c r="G39" s="25">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="H39" s="34">
+        <f t="shared" si="1"/>
+        <v>8.5</v>
+      </c>
+      <c r="I39" s="29">
+        <v>263.45</v>
+      </c>
+      <c r="J39" s="29">
+        <f t="shared" si="2"/>
+        <v>197.58749999999998</v>
+      </c>
+      <c r="K39" s="27">
+        <v>45835</v>
+      </c>
+      <c r="L39" s="34">
+        <f>K39-F39</f>
+        <v>4</v>
+      </c>
+      <c r="M39" s="29">
+        <f t="shared" si="4"/>
+        <v>131.72499999999999</v>
+      </c>
+      <c r="N39" s="27">
+        <v>45888</v>
+      </c>
+      <c r="O39" s="25">
+        <f>+N39-F39</f>
+        <v>57</v>
+      </c>
+      <c r="T39" s="25"/>
+      <c r="U39" s="25"/>
+      <c r="V39" s="25"/>
+      <c r="W39" s="25"/>
+      <c r="X39" s="25"/>
+      <c r="Y39" s="25"/>
+      <c r="Z39" s="25"/>
+      <c r="AA39" s="25"/>
+      <c r="AB39" s="25"/>
     </row>
     <row r="40" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B40" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="N40" s="25" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="41" spans="1:28" s="35" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="24"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B41" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" s="25"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="34"/>
-      <c r="I41" s="29"/>
-      <c r="J41" s="29"/>
-      <c r="K41" s="27"/>
-      <c r="L41" s="34"/>
-      <c r="M41" s="29"/>
-      <c r="N41" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="O41" s="37"/>
-      <c r="P41" s="37"/>
-      <c r="Q41" s="37"/>
-      <c r="R41" s="37"/>
-      <c r="S41" s="37"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="42" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B42" s="24" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N42" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="S42" s="30"/>
-    </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43" spans="1:28" s="35" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="24"/>
       <c r="B43" s="24" t="s">
-        <v>112</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="C43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="25"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="27"/>
+      <c r="L43" s="34"/>
+      <c r="M43" s="29"/>
+      <c r="N43" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="O43" s="37"/>
+      <c r="P43" s="37"/>
+      <c r="Q43" s="37"/>
+      <c r="R43" s="37"/>
+      <c r="S43" s="37"/>
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B44" s="24" t="s">
-        <v>114</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="N44" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="S44" s="30"/>
     </row>
     <row r="45" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B45" s="24" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="46" spans="1:28" x14ac:dyDescent="0.25">
       <c r="B46" s="24" t="s">
-        <v>118</v>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B48" s="58" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="9:9" x14ac:dyDescent="0.25">
@@ -5239,35 +5403,42 @@
     </row>
     <row r="52" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I52" s="56" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I53" s="56" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="54" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I54" s="56"/>
+      <c r="I54" s="56" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="55" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I55" s="56"/>
+      <c r="I55" s="59" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="56" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I56" s="56"/>
+      <c r="I56" s="56" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="57" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I57" s="56"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AB42">
-    <sortCondition ref="D3:D42"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AB46">
+    <sortCondition ref="D3:D46"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{A9B13DF2-D48C-48B0-AA59-066687FD8A4D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5309,7 +5480,7 @@
   <sheetData>
     <row r="1" spans="1:29" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
@@ -5320,11 +5491,11 @@
       <c r="F1" s="40"/>
       <c r="G1" s="39">
         <f ca="1">AVERAGE(G3:G106)</f>
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="H1" s="39">
         <f ca="1">AVERAGE(H3:H106)</f>
-        <v>29.125</v>
+        <v>30.875</v>
       </c>
       <c r="I1" s="40"/>
       <c r="J1" s="40"/>
@@ -5358,93 +5529,93 @@
     </row>
     <row r="2" spans="1:29" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B2" s="24" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J2" s="25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K2" s="25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L2" s="25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="M2" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="N2" s="25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="O2" s="25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P2" s="25" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Q2" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="R2" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="S2" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="T2" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="U2" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="V2" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="R2" s="25" t="s">
+      <c r="W2" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="S2" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="T2" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="U2" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="V2" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="W2" s="25" t="s">
-        <v>81</v>
-      </c>
       <c r="X2" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="Y2" s="25" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Z2" s="25" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AA2" s="25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AB2" s="25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:29" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="50" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C3" s="45" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D3" s="52">
         <v>45756</v>
@@ -5454,15 +5625,15 @@
       </c>
       <c r="F3" s="46">
         <f>D3+'Equity Bubbles'!G1</f>
-        <v>45872.257142857146</v>
+        <v>45880.432432432433</v>
       </c>
       <c r="G3" s="47">
         <f ca="1">TODAY()-D3</f>
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="H3" s="48">
         <f ca="1">G3/E3</f>
-        <v>23</v>
+        <v>26.5</v>
       </c>
       <c r="I3" s="49"/>
       <c r="J3" s="49"/>
@@ -5487,10 +5658,10 @@
     </row>
     <row r="4" spans="1:29" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="51" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D4" s="53">
         <v>36327</v>
@@ -5550,7 +5721,7 @@
     </row>
     <row r="5" spans="1:29" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="51" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C5" s="25" t="s">
         <v>50</v>
@@ -5583,12 +5754,12 @@
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B6" s="54" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B7" s="54" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/Models.xlsx
+++ b/Financial Analysis/Models.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4ABF243-B016-4595-AB0E-2BA1F129E14E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7AF0A32-B77E-41EA-A8E0-E5EDE5AFEDD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{40711DBD-7A53-4994-9FF1-9E754821B18D}"/>
   </bookViews>
@@ -17,14 +17,15 @@
     <sheet name="Upgrades" sheetId="3" r:id="rId2"/>
     <sheet name="Equity Bubbles" sheetId="5" r:id="rId3"/>
     <sheet name="Market Bubbles" sheetId="6" r:id="rId4"/>
+    <sheet name="Graham Criteria" sheetId="7" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
     <externalReference r:id="rId9"/>
     <externalReference r:id="rId10"/>
+    <externalReference r:id="rId11"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -189,7 +190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R2" authorId="0" shapeId="0" xr:uid="{406B637C-6449-4F37-95D3-3376951ECFA9}">
+    <comment ref="S2" authorId="0" shapeId="0" xr:uid="{406B637C-6449-4F37-95D3-3376951ECFA9}">
       <text>
         <r>
           <rPr>
@@ -276,7 +277,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="182">
   <si>
     <t>Tech</t>
   </si>
@@ -389,12 +390,6 @@
     <t>Ratings</t>
   </si>
   <si>
-    <t>EV/E</t>
-  </si>
-  <si>
-    <t>EV/R</t>
-  </si>
-  <si>
     <t>Do not short good companies! (maybe only at &gt;-70% and a short period of time)</t>
   </si>
   <si>
@@ -665,9 +660,6 @@
     <t>Price Variance</t>
   </si>
   <si>
-    <t>Average</t>
-  </si>
-  <si>
     <t>PLUG (Q220)</t>
   </si>
   <si>
@@ -680,13 +672,157 @@
     <t>if missed -25%, wait for rebound after -25% then short to -50%?</t>
   </si>
   <si>
-    <t>bold/underline = ongoing</t>
-  </si>
-  <si>
     <t>consider -22.5% instead of -25%, however weigh because this might be for short-term bubbles not for the very peak</t>
   </si>
   <si>
-    <t>time to -25% usually either up to two weeks, incorrect peak, or about 35-40 days</t>
+    <t>25% to 50%</t>
+  </si>
+  <si>
+    <t>the later the economic cycle, the more peaks?</t>
+  </si>
+  <si>
+    <t>62.5% DD</t>
+  </si>
+  <si>
+    <t>1st 62.5% DD Date</t>
+  </si>
+  <si>
+    <t>Time to -62.5%</t>
+  </si>
+  <si>
+    <t>50% to 62.5%</t>
+  </si>
+  <si>
+    <t>bold/underline = ongoing (less than -50%)</t>
+  </si>
+  <si>
+    <t>Defensive Investor</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>Financial Condition</t>
+  </si>
+  <si>
+    <t>Earnings Stability</t>
+  </si>
+  <si>
+    <t>Dividend Record</t>
+  </si>
+  <si>
+    <t>Earnings Growth</t>
+  </si>
+  <si>
+    <t>Moderate Price/Earnings</t>
+  </si>
+  <si>
+    <t>Moderate Price/Assets</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Exclude small companies</t>
+  </si>
+  <si>
+    <t>Numerical description</t>
+  </si>
+  <si>
+    <t>Earnings for past 10 years</t>
+  </si>
+  <si>
+    <t>Uninterrupted payments</t>
+  </si>
+  <si>
+    <t>More assets than liabilities</t>
+  </si>
+  <si>
+    <t>Positive earnings &gt; 10 years</t>
+  </si>
+  <si>
+    <t>Dividends &gt; 20 years</t>
+  </si>
+  <si>
+    <t>&gt; 100m in sales, &gt; 50m total assets (utilities)</t>
+  </si>
+  <si>
+    <t>Average earnings increase</t>
+  </si>
+  <si>
+    <t>Inexpensive price/earnings</t>
+  </si>
+  <si>
+    <t>1.33 x average EPS past 3 years &gt; average EPS last 3 years of past 10</t>
+  </si>
+  <si>
+    <t>&gt; 2x current ratio (industrials), working capital &gt; long-term debt, debt-to-equity &lt; 2 (utilities)</t>
+  </si>
+  <si>
+    <t>Price &lt; 15 x average EPS past 3 years (adjustable metric with price/assets below)</t>
+  </si>
+  <si>
+    <t>Inexpensive price/assets</t>
+  </si>
+  <si>
+    <t>Price &lt; 1.5 x book value</t>
+  </si>
+  <si>
+    <t>Price/Assets, Price/Earnings</t>
+  </si>
+  <si>
+    <t>Product of above ratios</t>
+  </si>
+  <si>
+    <t>Price/earnings x price/assets &lt; 22.5 (i.e. 15 x earnings &amp; 1.5 x book value)</t>
+  </si>
+  <si>
+    <t>Portfolio earnings yield</t>
+  </si>
+  <si>
+    <t>Price/earnings reversed</t>
+  </si>
+  <si>
+    <t>Average portfolio earnings yield &gt; current high-grade bond yield</t>
+  </si>
+  <si>
+    <t>P/S</t>
+  </si>
+  <si>
+    <t>P/E</t>
+  </si>
+  <si>
+    <t>Diversification encouraged</t>
+  </si>
+  <si>
+    <t>Multiple stock portfolio</t>
+  </si>
+  <si>
+    <t>Enterprising Investor</t>
+  </si>
+  <si>
+    <t>&gt; 1.5x current ratio, debt &lt; 110% of net current assets (industrials)</t>
+  </si>
+  <si>
+    <t>Earnings for past 5 years</t>
+  </si>
+  <si>
+    <t>Positive earnings &gt; 5 years</t>
+  </si>
+  <si>
+    <t>Some current dividend</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Price &lt; 120% of net tangible assets</t>
+  </si>
+  <si>
+    <t>time to -50% also seems to have some more or less specific day counts</t>
+  </si>
+  <si>
+    <t>time to -25% usually either up to two weeks, incorrect peak (sell after two weeks and before time per peak average?), or about 36-42 days</t>
   </si>
 </sst>
 </file>
@@ -698,7 +834,7 @@
     <numFmt numFmtId="165" formatCode="0.0\x"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -854,8 +990,17 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -910,6 +1055,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1028,7 +1179,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -1103,9 +1254,6 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="8" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="16" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="3" fontId="17" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1157,6 +1305,10 @@
     <xf numFmtId="4" fontId="18" fillId="9" borderId="8" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -1194,28 +1346,18 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="N3">
-            <v>27.169241995324199</v>
+            <v>26.62062128663548</v>
           </cell>
           <cell r="T3">
-            <v>4.4621323257125018</v>
+            <v>3.687787857781355</v>
           </cell>
           <cell r="AA3">
-            <v>-0.27093209566711646</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5" t="str">
-            <v>Microsoft</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6" t="str">
-            <v>Apple</v>
+            <v>-0.16118420686945295</v>
           </cell>
         </row>
         <row r="7">
           <cell r="B7" t="str">
-            <v>Alphabet</v>
+            <v>Microsoft</v>
           </cell>
         </row>
         <row r="8">
@@ -1235,32 +1377,32 @@
         </row>
         <row r="11">
           <cell r="B11" t="str">
-            <v>Oracle</v>
+            <v>Tencent</v>
           </cell>
         </row>
         <row r="12">
           <cell r="B12" t="str">
-            <v>Tencent</v>
+            <v>Visa</v>
           </cell>
         </row>
         <row r="13">
           <cell r="B13" t="str">
-            <v>Visa</v>
+            <v>Oracle</v>
           </cell>
         </row>
         <row r="14">
           <cell r="B14" t="str">
-            <v>Netflix</v>
+            <v>Mastercard</v>
           </cell>
         </row>
         <row r="15">
           <cell r="B15" t="str">
-            <v>Mastercard</v>
+            <v>Palantir</v>
           </cell>
         </row>
         <row r="16">
           <cell r="B16" t="str">
-            <v>Palantir</v>
+            <v>Netflix</v>
           </cell>
         </row>
         <row r="17">
@@ -1275,7 +1417,7 @@
         </row>
         <row r="19">
           <cell r="B19" t="str">
-            <v>Salesforce</v>
+            <v>Intel</v>
           </cell>
         </row>
         <row r="20">
@@ -1285,7 +1427,7 @@
         </row>
         <row r="21">
           <cell r="B21" t="str">
-            <v>Intel</v>
+            <v>Salesforce</v>
           </cell>
         </row>
         <row r="22">
@@ -1300,52 +1442,52 @@
         </row>
         <row r="24">
           <cell r="B24" t="str">
-            <v>Roblox</v>
+            <v>Coinbase</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25" t="str">
-            <v>Snowflake</v>
+            <v>Fiserv</v>
           </cell>
         </row>
         <row r="26">
           <cell r="B26" t="str">
-            <v>Coinbase</v>
+            <v>Snowflake</v>
           </cell>
         </row>
         <row r="27">
           <cell r="B27" t="str">
-            <v>Fiserv</v>
+            <v>Roblox</v>
           </cell>
         </row>
         <row r="28">
           <cell r="B28" t="str">
-            <v>Paypal</v>
+            <v>TakeTwo</v>
           </cell>
         </row>
         <row r="29">
           <cell r="B29" t="str">
-            <v>TakeTwo</v>
+            <v>Block</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30" t="str">
-            <v>Reddit</v>
+            <v>Paypal</v>
           </cell>
         </row>
         <row r="31">
           <cell r="B31" t="str">
-            <v>Block</v>
+            <v>Global Payments</v>
           </cell>
         </row>
         <row r="32">
           <cell r="B32" t="str">
-            <v>Global Payments</v>
+            <v>Symbotic</v>
           </cell>
         </row>
         <row r="33">
           <cell r="B33" t="str">
-            <v>Symbotic</v>
+            <v>Reddit</v>
           </cell>
         </row>
         <row r="34">
@@ -1365,57 +1507,57 @@
         </row>
         <row r="37">
           <cell r="B37" t="str">
-            <v>Logitech</v>
+            <v>Rigetti</v>
           </cell>
         </row>
         <row r="38">
           <cell r="B38" t="str">
-            <v>Snap Inc</v>
+            <v>Roku</v>
           </cell>
         </row>
         <row r="39">
           <cell r="B39" t="str">
-            <v>Duolingo</v>
+            <v>Logitech</v>
           </cell>
         </row>
         <row r="40">
           <cell r="B40" t="str">
-            <v>Rigetti</v>
+            <v>Snap Inc</v>
           </cell>
         </row>
         <row r="41">
           <cell r="B41" t="str">
-            <v>Roku</v>
+            <v>Shift4</v>
           </cell>
         </row>
         <row r="42">
           <cell r="B42" t="str">
-            <v>Shift4</v>
+            <v>EPAM</v>
           </cell>
         </row>
         <row r="43">
           <cell r="B43" t="str">
-            <v>Life360</v>
+            <v>Novami</v>
           </cell>
         </row>
         <row r="44">
           <cell r="B44" t="str">
-            <v>EPAM</v>
+            <v>StoneCo</v>
           </cell>
         </row>
         <row r="45">
           <cell r="B45" t="str">
-            <v>Novami</v>
+            <v>GameStop</v>
           </cell>
         </row>
         <row r="46">
           <cell r="B46" t="str">
-            <v>GameStop</v>
+            <v>Life360</v>
           </cell>
         </row>
         <row r="47">
           <cell r="B47" t="str">
-            <v>StoneCo</v>
+            <v>Duolingo</v>
           </cell>
         </row>
         <row r="48">
@@ -1425,47 +1567,47 @@
         </row>
         <row r="49">
           <cell r="B49" t="str">
-            <v>PagSeguro</v>
+            <v>Stride</v>
           </cell>
         </row>
         <row r="50">
           <cell r="B50" t="str">
-            <v>Paysafe</v>
+            <v>PlugPower</v>
           </cell>
         </row>
         <row r="51">
           <cell r="B51" t="str">
-            <v>Stride</v>
+            <v>PagSeguro</v>
           </cell>
         </row>
         <row r="52">
           <cell r="B52" t="str">
-            <v>PlugPower</v>
+            <v>Paysafe</v>
           </cell>
         </row>
         <row r="53">
           <cell r="B53" t="str">
-            <v>Opera</v>
+            <v>Sonos</v>
           </cell>
         </row>
         <row r="54">
           <cell r="B54" t="str">
-            <v>Sonos</v>
+            <v>Opera</v>
           </cell>
         </row>
         <row r="55">
           <cell r="B55" t="str">
-            <v>Corsair Gaming</v>
+            <v>Bandwidth</v>
           </cell>
         </row>
         <row r="56">
           <cell r="B56" t="str">
-            <v>Coursera</v>
+            <v>Corsair Gaming</v>
           </cell>
         </row>
         <row r="57">
           <cell r="B57" t="str">
-            <v>Bandwidth</v>
+            <v>Fiverr</v>
           </cell>
         </row>
         <row r="58">
@@ -1475,12 +1617,12 @@
         </row>
         <row r="59">
           <cell r="B59" t="str">
-            <v>Fiverr</v>
+            <v>Gambling.com</v>
           </cell>
         </row>
         <row r="60">
           <cell r="B60" t="str">
-            <v>Gambling.com</v>
+            <v>Coursera</v>
           </cell>
         </row>
         <row r="61">
@@ -1495,7 +1637,7 @@
         </row>
         <row r="63">
           <cell r="B63" t="str">
-            <v>Chegg</v>
+            <v>FuelCell</v>
           </cell>
         </row>
         <row r="64">
@@ -1505,7 +1647,7 @@
         </row>
         <row r="65">
           <cell r="B65" t="str">
-            <v>FuelCell</v>
+            <v>Chegg</v>
           </cell>
         </row>
         <row r="66">
@@ -1639,7 +1781,7 @@
             <v>1.0405324209773694</v>
           </cell>
           <cell r="AA3">
-            <v>-0.24824550873827725</v>
+            <v>-0.30225003994070132</v>
           </cell>
         </row>
         <row r="4">
@@ -1776,9 +1918,11 @@
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
-      <sheetName val="Models (Retail)"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
@@ -1969,7 +2113,6 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1983,26 +2126,27 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
+      <sheetName val="Subsidiaries"/>
       <sheetName val="FY2026 DoD Budget Materials"/>
       <sheetName val="DoD Products"/>
-      <sheetName val="Future Products"/>
       <sheetName val="RawData"/>
       <sheetName val="PivotTable"/>
-      <sheetName val="Subsidiaries"/>
       <sheetName val="ProgramBreakdown"/>
       <sheetName val="Wargaming"/>
+      <sheetName val="Product Catalogue"/>
+      <sheetName val="Future Products"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="R3">
-            <v>37.082954294919055</v>
+          <cell r="S3">
+            <v>30.621705228448555</v>
           </cell>
           <cell r="AE3">
-            <v>3.0547812365039473</v>
+            <v>2.9141040899024544</v>
           </cell>
           <cell r="AL3">
-            <v>-0.47586149868430783</v>
+            <v>-0.35905903268240191</v>
           </cell>
         </row>
         <row r="4">
@@ -2012,12 +2156,12 @@
         </row>
         <row r="5">
           <cell r="B5" t="str">
-            <v>Boeing</v>
+            <v>General Electric</v>
           </cell>
         </row>
         <row r="6">
           <cell r="B6" t="str">
-            <v>Honeywell</v>
+            <v>Boeing</v>
           </cell>
         </row>
         <row r="7">
@@ -2027,37 +2171,37 @@
         </row>
         <row r="8">
           <cell r="B8" t="str">
-            <v>Lockheed Martin</v>
+            <v>Honeywell</v>
           </cell>
         </row>
         <row r="9">
           <cell r="B9" t="str">
-            <v>Safran</v>
+            <v>Lockheed Martin</v>
           </cell>
         </row>
         <row r="10">
           <cell r="B10" t="str">
-            <v>Northrop Grumman</v>
+            <v>Safran</v>
           </cell>
         </row>
         <row r="11">
           <cell r="B11" t="str">
-            <v>General Dynamics</v>
+            <v>Northrop Grumman</v>
           </cell>
         </row>
         <row r="12">
           <cell r="B12" t="str">
-            <v>Rolls Royce</v>
+            <v>General Dynamics</v>
           </cell>
         </row>
         <row r="13">
           <cell r="B13" t="str">
-            <v>Rheinmetall</v>
+            <v>Rolls Royce</v>
           </cell>
         </row>
         <row r="14">
           <cell r="B14" t="str">
-            <v>BAE</v>
+            <v>Rheinmetall</v>
           </cell>
         </row>
         <row r="15">
@@ -2067,161 +2211,219 @@
         </row>
         <row r="16">
           <cell r="B16" t="str">
-            <v>Thales</v>
+            <v>BAE</v>
           </cell>
         </row>
         <row r="17">
           <cell r="B17" t="str">
-            <v>Dassault</v>
+            <v>Anduril*</v>
           </cell>
         </row>
         <row r="18">
           <cell r="B18" t="str">
-            <v>Leonardo</v>
+            <v>Thales</v>
           </cell>
         </row>
         <row r="19">
           <cell r="B19" t="str">
-            <v>Anduril</v>
+            <v>Dassault</v>
           </cell>
         </row>
         <row r="20">
           <cell r="B20" t="str">
-            <v>Leidos</v>
+            <v>Leonardo</v>
           </cell>
         </row>
         <row r="21">
           <cell r="B21" t="str">
-            <v>Bombardier</v>
+            <v>Leidos</v>
           </cell>
         </row>
         <row r="22">
           <cell r="B22" t="str">
-            <v>Textron</v>
+            <v>Bombardier</v>
           </cell>
         </row>
         <row r="23">
           <cell r="B23" t="str">
-            <v>Embraer</v>
+            <v>Textron</v>
           </cell>
         </row>
         <row r="24">
           <cell r="B24" t="str">
-            <v>Hensoldt</v>
+            <v>AeroVironment</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25" t="str">
-            <v>Kratos</v>
+            <v>Embraer</v>
           </cell>
         </row>
         <row r="26">
           <cell r="B26" t="str">
-            <v>Norinco</v>
+            <v>Kratos</v>
           </cell>
         </row>
         <row r="27">
           <cell r="B27" t="str">
-            <v>Renk</v>
+            <v>Oshkosh</v>
           </cell>
         </row>
         <row r="28">
           <cell r="B28" t="str">
-            <v>Red Cat</v>
+            <v>Hensoldt</v>
           </cell>
         </row>
         <row r="29">
           <cell r="B29" t="str">
-            <v>Unusual Machines</v>
+            <v>Renk</v>
           </cell>
         </row>
         <row r="30">
-          <cell r="B30"/>
+          <cell r="B30" t="str">
+            <v>National Presto</v>
+          </cell>
         </row>
         <row r="31">
           <cell r="B31" t="str">
-            <v>SAAB</v>
+            <v>Red Cat</v>
           </cell>
         </row>
         <row r="32">
           <cell r="B32" t="str">
-            <v>General Atomics</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="B33" t="str">
-            <v>AeroVironment</v>
+            <v>Unusual Machines</v>
           </cell>
         </row>
         <row r="34">
           <cell r="B34" t="str">
-            <v>Archer Aviation</v>
+            <v>Norinco</v>
           </cell>
         </row>
         <row r="35">
           <cell r="B35" t="str">
-            <v>Sierra Nevada</v>
+            <v>SAAB</v>
           </cell>
         </row>
         <row r="36">
           <cell r="B36" t="str">
-            <v>General Electric</v>
+            <v>General Atomics*</v>
           </cell>
         </row>
         <row r="37">
           <cell r="B37" t="str">
-            <v>National Presto</v>
+            <v>Archer Aviation</v>
           </cell>
         </row>
         <row r="38">
           <cell r="B38" t="str">
-            <v>Patria</v>
+            <v>Sierra Nevada*</v>
           </cell>
         </row>
         <row r="39">
           <cell r="B39" t="str">
-            <v>Kongsberg</v>
+            <v>Patria*</v>
           </cell>
         </row>
         <row r="40">
           <cell r="B40" t="str">
-            <v>Oshkosh</v>
+            <v>Kongsberg</v>
           </cell>
         </row>
         <row r="41">
           <cell r="B41" t="str">
-            <v>Babcock?</v>
+            <v>Babcock</v>
           </cell>
         </row>
         <row r="42">
           <cell r="B42" t="str">
-            <v>GKN</v>
+            <v>GKN*</v>
           </cell>
         </row>
         <row r="43">
           <cell r="B43" t="str">
-            <v>Avio</v>
+            <v>Melrose</v>
           </cell>
         </row>
         <row r="44">
           <cell r="B44" t="str">
-            <v>QinetiQ</v>
+            <v>Avio</v>
           </cell>
         </row>
         <row r="45">
           <cell r="B45" t="str">
-            <v>KNDS</v>
+            <v>QinetiQ</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="B46" t="str">
+            <v>KNDS*</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="B47" t="str">
+            <v>Indra</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="B48" t="str">
+            <v>InQTel*</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="B49" t="str">
+            <v>Teledyne</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="B50" t="str">
+            <v>Jenoptics</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="B51" t="str">
+            <v>TransDigm</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="B52" t="str">
+            <v>Heico</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="B53" t="str">
+            <v>Elbit Systems</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="B54" t="str">
+            <v>Hyundai WIA</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="B55" t="str">
+            <v>SNT Dynamics</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="B56" t="str">
+            <v>Samyang Comtech</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="B57" t="str">
+            <v>ST Engineering</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2622,7 +2824,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB1DBC02-9223-4C08-9E62-C64832103121}">
   <dimension ref="B2:O19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="13"/>
     <col min="2" max="2" width="10.5546875" style="13" bestFit="1" customWidth="1"/>
@@ -2647,13 +2849,13 @@
         <v>18</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>37</v>
+        <v>170</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>38</v>
+        <v>169</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H2" s="14" t="s">
         <v>16</v>
@@ -2664,27 +2866,27 @@
         <v>0</v>
       </c>
       <c r="C3" s="18">
-        <f>COUNTA([1]Models!$B$5:$B$1048576)</f>
-        <v>82</v>
+        <f>COUNTA([1]Models!$B$7:$B$1048576)</f>
+        <v>80</v>
       </c>
       <c r="D3" s="19">
         <f>[1]Models!$AA$3</f>
-        <v>-0.27093209566711646</v>
+        <v>-0.16118420686945295</v>
       </c>
       <c r="E3" s="21">
         <f>[1]Models!$N$3</f>
-        <v>27.169241995324199</v>
+        <v>26.62062128663548</v>
       </c>
       <c r="F3" s="22">
         <f>[1]Models!$T$3</f>
-        <v>4.4621323257125018</v>
+        <v>3.687787857781355</v>
       </c>
       <c r="G3" s="15">
         <v>45932</v>
       </c>
       <c r="H3" s="15">
         <f ca="1">TODAY()</f>
-        <v>45968</v>
+        <v>46066</v>
       </c>
       <c r="K3" s="17" t="s">
         <v>7</v>
@@ -2700,7 +2902,7 @@
       </c>
       <c r="D4" s="19">
         <f>[2]Main!$AA$3</f>
-        <v>-0.24824550873827725</v>
+        <v>-0.30225003994070132</v>
       </c>
       <c r="E4" s="21">
         <f>[2]Main!$O$3</f>
@@ -2710,12 +2912,12 @@
         <f>[2]Main!$U$3</f>
         <v>1.0405324209773694</v>
       </c>
-      <c r="K4" s="57" t="s">
-        <v>128</v>
+      <c r="K4" s="56" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B5" s="57" t="s">
+      <c r="B5" s="56" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="18">
@@ -2741,19 +2943,19 @@
       </c>
       <c r="C6" s="18">
         <f>COUNTA([4]Main!$B$4:$B$1048576)</f>
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D6" s="19">
         <f>[4]Main!$AL$3</f>
-        <v>-0.47586149868430783</v>
+        <v>-0.35905903268240191</v>
       </c>
       <c r="E6" s="21">
-        <f>[4]Main!$R$3</f>
-        <v>37.082954294919055</v>
+        <f>[4]Main!$S$3</f>
+        <v>30.621705228448555</v>
       </c>
       <c r="F6" s="22">
         <f>[4]Main!$AE$3</f>
-        <v>3.0547812365039473</v>
+        <v>2.9141040899024544</v>
       </c>
       <c r="K6" s="12" t="s">
         <v>36</v>
@@ -2811,19 +3013,19 @@
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C9" s="18">
         <f>SUM(C3:C8)</f>
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="D9" s="19">
         <f>AVERAGE(D3:D8)</f>
-        <v>-0.44101007235961714</v>
+        <v>-0.41225243509342624</v>
       </c>
       <c r="E9" s="21">
         <f>AVERAGE(E3:E8)</f>
-        <v>27.482817665462889</v>
+        <v>25.730350221673085</v>
       </c>
       <c r="F9" s="22">
         <f>AVERAGE(F3:F8)</f>
-        <v>7.73597190314094</v>
+        <v>7.5529675802344114</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>33</v>
@@ -2832,7 +3034,7 @@
         <v>29</v>
       </c>
       <c r="O9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.3">
@@ -2855,7 +3057,7 @@
         <v>29</v>
       </c>
       <c r="O11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.3">
@@ -2912,66 +3114,66 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D82D2D3-5236-4339-AF4C-11B73B17E08A}">
   <dimension ref="B3:B13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="42"/>
-    <col min="2" max="2" width="105.44140625" style="42" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="42"/>
+    <col min="1" max="1" width="8.88671875" style="41"/>
+    <col min="2" max="2" width="105.44140625" style="41" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="41"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="42" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="42" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="42" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="42" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="41" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="41" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="42" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="42" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="41" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B12" s="41" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B13" s="41" t="s">
         <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B12" s="42" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B13" s="42" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -2981,7 +3183,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04147068-271F-415A-A4EA-D0D6DE05E2E6}">
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AH54"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.44140625" style="24" bestFit="1" customWidth="1"/>
@@ -2998,156 +3200,187 @@
     <col min="13" max="13" width="10.44140625" style="29" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15" style="25" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.44140625" style="25" customWidth="1"/>
-    <col min="16" max="16" width="12" style="25" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.109375" style="25" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.109375" style="25" customWidth="1"/>
-    <col min="19" max="19" width="10.88671875" style="25" customWidth="1"/>
-    <col min="20" max="20" width="11.44140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.44140625" style="24" customWidth="1"/>
-    <col min="22" max="22" width="11.44140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.109375" style="24" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.109375" style="24" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.44140625" style="24" customWidth="1"/>
-    <col min="26" max="26" width="8.88671875" style="24"/>
-    <col min="27" max="28" width="10.44140625" style="24" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="8.88671875" style="24"/>
+    <col min="16" max="16" width="12.44140625" style="34" customWidth="1"/>
+    <col min="17" max="17" width="12" style="25" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.109375" style="25" customWidth="1"/>
+    <col min="20" max="21" width="10.88671875" style="25" customWidth="1"/>
+    <col min="22" max="22" width="16.77734375" style="25" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.44140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.44140625" style="25" customWidth="1"/>
+    <col min="25" max="25" width="11.44140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.44140625" style="24" customWidth="1"/>
+    <col min="27" max="27" width="11.44140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="8.109375" style="24" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.44140625" style="24" customWidth="1"/>
+    <col min="31" max="31" width="8.88671875" style="24"/>
+    <col min="32" max="33" width="10.44140625" style="24" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="8.88671875" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="E1" s="41">
-        <f>AVERAGE(E3:E105)</f>
-        <v>4.4594594594594597</v>
-      </c>
-      <c r="F1" s="40"/>
-      <c r="G1" s="39">
-        <f>AVERAGE(G3:G105)</f>
-        <v>124.43243243243244</v>
-      </c>
-      <c r="H1" s="39">
-        <f>AVERAGE(H3:H105)</f>
-        <v>26.578217503217505</v>
-      </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="39">
-        <f ca="1">AVERAGE(L3:L105)</f>
-        <v>11.058823529411764</v>
-      </c>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="39">
-        <f ca="1">AVERAGE(O3:O105)</f>
-        <v>42.862068965517238</v>
-      </c>
-      <c r="P1" s="26"/>
+        <v>97</v>
+      </c>
+      <c r="E1" s="40">
+        <f>AVERAGE(E3:E106)</f>
+        <v>4.5135135135135132</v>
+      </c>
+      <c r="F1" s="39"/>
+      <c r="G1" s="38">
+        <f>AVERAGE(G3:G106)</f>
+        <v>128.27027027027026</v>
+      </c>
+      <c r="H1" s="38">
+        <f>AVERAGE(H3:H106)</f>
+        <v>26.91988416988417</v>
+      </c>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="38">
+        <f>AVERAGE(L3:L106)</f>
+        <v>11.432432432432432</v>
+      </c>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="38">
+        <f ca="1">AVERAGE(O3:O106)</f>
+        <v>49.222222222222221</v>
+      </c>
+      <c r="P1" s="38">
+        <f>AVERAGE(P3:P106)</f>
+        <v>35.617647058823529</v>
+      </c>
       <c r="Q1" s="26"/>
       <c r="R1" s="26"/>
-      <c r="V1" s="26">
-        <f>AVERAGE(V4:V45)</f>
+      <c r="S1" s="26"/>
+      <c r="W1" s="38">
+        <f>AVERAGE(W3:W106)</f>
+        <v>96.666666666666671</v>
+      </c>
+      <c r="X1" s="38">
+        <f>AVERAGE(X3:X106)</f>
+        <v>50.555555555555557</v>
+      </c>
+      <c r="AA1" s="26">
+        <f>AVERAGE(AA4:AA45)</f>
         <v>297.125</v>
       </c>
-      <c r="W1" s="26"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="AB1" s="26">
-        <f>AVERAGE(AB4:AB45)</f>
+      <c r="AB1" s="26"/>
+      <c r="AC1" s="26"/>
+      <c r="AD1" s="26"/>
+      <c r="AG1" s="26">
+        <f>AVERAGE(AG4:AG45)</f>
         <v>705.5</v>
       </c>
-      <c r="AC1" s="26"/>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AH1" s="26"/>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B2" s="24" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J2" s="25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K2" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L2" s="25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M2" s="25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="N2" s="25" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="O2" s="25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="P2" s="25" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="Q2" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="R2" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="S2" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="T2" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="U2" s="25" t="s">
+        <v>134</v>
+      </c>
+      <c r="V2" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="W2" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="X2" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y2" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z2" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA2" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="R2" s="25" t="s">
+      <c r="AB2" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="S2" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="T2" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="U2" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="V2" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="W2" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="X2" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y2" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z2" s="25" t="s">
+      <c r="AC2" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="AA2" s="25" t="s">
+      <c r="AD2" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="AB2" s="25" t="s">
+      <c r="AE2" s="25" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AF2" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="AG2" s="25" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B3" s="24" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D3" s="27">
         <v>39707</v>
@@ -3177,7 +3410,7 @@
         <v>39750</v>
       </c>
       <c r="L3" s="25">
-        <f t="shared" ref="L3:L32" si="3">K3-F3</f>
+        <f t="shared" ref="L3:L34" si="3">K3-F3</f>
         <v>1</v>
       </c>
       <c r="M3" s="29">
@@ -3191,13 +3424,24 @@
         <f t="shared" ref="O3:O28" si="5">+N3-F3</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="P3" s="28">
+        <f t="shared" ref="P3:P28" si="6">O3-L3</f>
+        <v>5</v>
+      </c>
+      <c r="U3" s="29">
+        <f>I3*0.375</f>
+        <v>354.375</v>
+      </c>
+      <c r="V3" s="27"/>
+      <c r="W3" s="29"/>
+      <c r="X3" s="29"/>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B4" s="24" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D4" s="27">
         <v>41642</v>
@@ -3241,17 +3485,28 @@
         <f t="shared" si="5"/>
         <v>59</v>
       </c>
-      <c r="S4" s="30">
-        <f t="shared" ref="S4:S11" si="6">+M4/I4-1</f>
+      <c r="P4" s="28">
+        <f t="shared" si="6"/>
+        <v>52</v>
+      </c>
+      <c r="T4" s="30">
+        <f t="shared" ref="T4:T11" si="7">+M4/I4-1</f>
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="U4" s="29">
+        <f t="shared" ref="U4:U39" si="8">I4*0.375</f>
+        <v>6369.1462499999998</v>
+      </c>
+      <c r="V4" s="27"/>
+      <c r="W4" s="29"/>
+      <c r="X4" s="29"/>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D5" s="27">
         <v>43045</v>
@@ -3295,17 +3550,28 @@
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="S5" s="25">
+      <c r="P5" s="28">
         <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="T5" s="25">
+        <f t="shared" si="7"/>
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="U5" s="29">
+        <f t="shared" si="8"/>
+        <v>665.55</v>
+      </c>
+      <c r="V5" s="27"/>
+      <c r="W5" s="29"/>
+      <c r="X5" s="29"/>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B6" s="24" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D6" s="27">
         <v>43327</v>
@@ -3349,43 +3615,54 @@
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="P6" s="28"/>
+      <c r="P6" s="28">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
       <c r="Q6" s="28"/>
       <c r="R6" s="28"/>
-      <c r="S6" s="30">
-        <f t="shared" si="6"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="30">
+        <f t="shared" si="7"/>
         <v>-0.5</v>
       </c>
-      <c r="T6" s="31">
+      <c r="U6" s="29">
+        <f t="shared" si="8"/>
+        <v>80.272500000000008</v>
+      </c>
+      <c r="V6" s="27"/>
+      <c r="W6" s="29"/>
+      <c r="X6" s="29"/>
+      <c r="Y6" s="31">
         <v>53.52</v>
       </c>
-      <c r="U6" s="32">
+      <c r="Z6" s="32">
         <v>43566</v>
       </c>
-      <c r="V6" s="33">
-        <f t="shared" ref="V6:V11" si="7">+U6-F6</f>
+      <c r="AA6" s="33">
+        <f t="shared" ref="AA6:AA11" si="9">+Z6-F6</f>
         <v>204</v>
       </c>
-      <c r="W6" s="33"/>
-      <c r="X6" s="33"/>
-      <c r="Y6" s="33"/>
-      <c r="Z6" s="31">
+      <c r="AB6" s="33"/>
+      <c r="AC6" s="33"/>
+      <c r="AD6" s="33"/>
+      <c r="AE6" s="31">
         <v>20.65</v>
       </c>
-      <c r="AA6" s="32">
+      <c r="AF6" s="32">
         <v>43748</v>
       </c>
-      <c r="AB6" s="33">
-        <f>+AA6-F6</f>
+      <c r="AG6" s="33">
+        <f>+AF6-F6</f>
         <v>386</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B7" s="24" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D7" s="27">
         <v>43591</v>
@@ -3429,43 +3706,54 @@
         <f t="shared" si="5"/>
         <v>113</v>
       </c>
-      <c r="P7" s="28"/>
+      <c r="P7" s="28">
+        <f t="shared" si="6"/>
+        <v>77</v>
+      </c>
       <c r="Q7" s="28"/>
       <c r="R7" s="28"/>
-      <c r="S7" s="30">
-        <f t="shared" si="6"/>
+      <c r="S7" s="28"/>
+      <c r="T7" s="30">
+        <f t="shared" si="7"/>
         <v>-0.5</v>
       </c>
-      <c r="T7" s="24">
+      <c r="U7" s="29">
+        <f t="shared" si="8"/>
+        <v>88.087500000000006</v>
+      </c>
+      <c r="V7" s="27"/>
+      <c r="W7" s="29"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="24">
         <v>54.02</v>
       </c>
-      <c r="U7" s="32">
+      <c r="Z7" s="32">
         <v>43908</v>
       </c>
-      <c r="V7" s="33">
-        <f t="shared" si="7"/>
+      <c r="AA7" s="33">
+        <f t="shared" si="9"/>
         <v>266</v>
       </c>
-      <c r="W7" s="33"/>
-      <c r="X7" s="33"/>
-      <c r="Y7" s="33"/>
-      <c r="Z7" s="24">
+      <c r="AB7" s="33"/>
+      <c r="AC7" s="33"/>
+      <c r="AD7" s="33"/>
+      <c r="AE7" s="24">
         <v>22.86</v>
       </c>
-      <c r="AA7" s="32">
+      <c r="AF7" s="32">
         <v>44721</v>
       </c>
-      <c r="AB7" s="33">
-        <f>+AA7-F7</f>
+      <c r="AG7" s="33">
+        <f>+AF7-F7</f>
         <v>1079</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B8" s="24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D8" s="27">
         <v>43808</v>
@@ -3509,43 +3797,54 @@
         <f t="shared" si="5"/>
         <v>19</v>
       </c>
-      <c r="P8" s="28"/>
+      <c r="P8" s="28">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
       <c r="Q8" s="28"/>
       <c r="R8" s="28"/>
-      <c r="S8" s="30">
-        <f t="shared" si="6"/>
+      <c r="S8" s="28"/>
+      <c r="T8" s="30">
+        <f t="shared" si="7"/>
         <v>-0.5</v>
       </c>
-      <c r="T8" s="31">
+      <c r="U8" s="29">
+        <f t="shared" si="8"/>
+        <v>280.125</v>
+      </c>
+      <c r="V8" s="27"/>
+      <c r="W8" s="29"/>
+      <c r="X8" s="29"/>
+      <c r="Y8" s="31">
         <v>267.60000000000002</v>
       </c>
-      <c r="U8" s="32">
+      <c r="Z8" s="32">
         <v>44561</v>
       </c>
-      <c r="V8" s="33">
-        <f t="shared" si="7"/>
+      <c r="AA8" s="33">
+        <f t="shared" si="9"/>
         <v>681</v>
       </c>
-      <c r="W8" s="33"/>
-      <c r="X8" s="33"/>
-      <c r="Y8" s="33"/>
-      <c r="Z8" s="31">
+      <c r="AB8" s="33"/>
+      <c r="AC8" s="33"/>
+      <c r="AD8" s="33"/>
+      <c r="AE8" s="31">
         <v>106.2</v>
       </c>
-      <c r="AA8" s="32">
+      <c r="AF8" s="32">
         <v>44820</v>
       </c>
-      <c r="AB8" s="33">
-        <f>+AA8-F8</f>
+      <c r="AG8" s="33">
+        <f>+AF8-F8</f>
         <v>940</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B9" s="24" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D9" s="27">
         <v>43893</v>
@@ -3589,37 +3888,48 @@
         <f t="shared" si="5"/>
         <v>41</v>
       </c>
-      <c r="P9" s="28"/>
+      <c r="P9" s="28">
+        <f t="shared" si="6"/>
+        <v>39</v>
+      </c>
       <c r="Q9" s="28"/>
       <c r="R9" s="28"/>
-      <c r="S9" s="30">
-        <f t="shared" si="6"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="30">
+        <f t="shared" si="7"/>
         <v>-0.5</v>
       </c>
-      <c r="T9" s="31">
+      <c r="U9" s="29">
+        <f t="shared" si="8"/>
+        <v>896.97</v>
+      </c>
+      <c r="V9" s="27"/>
+      <c r="W9" s="29"/>
+      <c r="X9" s="29"/>
+      <c r="Y9" s="31">
         <v>573.00570000000005</v>
       </c>
-      <c r="U9" s="32">
+      <c r="Z9" s="32">
         <v>44098</v>
       </c>
-      <c r="V9" s="33">
-        <f t="shared" si="7"/>
+      <c r="AA9" s="33">
+        <f t="shared" si="9"/>
         <v>107</v>
       </c>
-      <c r="W9" s="33"/>
-      <c r="X9" s="33"/>
-      <c r="Y9" s="33"/>
-      <c r="Z9" s="31">
+      <c r="AB9" s="33"/>
+      <c r="AC9" s="33"/>
+      <c r="AD9" s="33"/>
+      <c r="AE9" s="31">
         <f>+I9*0.1</f>
         <v>239.19200000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B10" s="24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D10" s="27">
         <v>43906</v>
@@ -3663,43 +3973,54 @@
         <f t="shared" si="5"/>
         <v>112</v>
       </c>
-      <c r="P10" s="28"/>
+      <c r="P10" s="28">
+        <f t="shared" si="6"/>
+        <v>72</v>
+      </c>
       <c r="Q10" s="28"/>
       <c r="R10" s="28"/>
-      <c r="S10" s="30">
-        <f t="shared" si="6"/>
+      <c r="S10" s="28"/>
+      <c r="T10" s="30">
+        <f t="shared" si="7"/>
         <v>-0.5</v>
       </c>
-      <c r="T10" s="24">
+      <c r="U10" s="29">
+        <f t="shared" si="8"/>
+        <v>62.782499999999999</v>
+      </c>
+      <c r="V10" s="27"/>
+      <c r="W10" s="29"/>
+      <c r="X10" s="29"/>
+      <c r="Y10" s="24">
         <v>41.78</v>
       </c>
-      <c r="U10" s="32">
+      <c r="Z10" s="32">
         <v>44537</v>
       </c>
-      <c r="V10" s="33">
-        <f t="shared" si="7"/>
+      <c r="AA10" s="33">
+        <f t="shared" si="9"/>
         <v>328</v>
       </c>
-      <c r="W10" s="33"/>
-      <c r="X10" s="33"/>
-      <c r="Y10" s="33"/>
-      <c r="Z10" s="31">
+      <c r="AB10" s="33"/>
+      <c r="AC10" s="33"/>
+      <c r="AD10" s="33"/>
+      <c r="AE10" s="31">
         <v>15.7</v>
       </c>
-      <c r="AA10" s="32">
+      <c r="AF10" s="32">
         <v>44687</v>
       </c>
-      <c r="AB10" s="33">
-        <f>+AA10-F10</f>
+      <c r="AG10" s="33">
+        <f>+AF10-F10</f>
         <v>478</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B11" s="24" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D11" s="27">
         <v>43986</v>
@@ -3743,24 +4064,35 @@
         <f t="shared" si="5"/>
         <v>38</v>
       </c>
-      <c r="S11" s="30">
+      <c r="P11" s="28">
         <f t="shared" si="6"/>
+        <v>17</v>
+      </c>
+      <c r="T11" s="30">
+        <f t="shared" si="7"/>
         <v>-0.5</v>
       </c>
-      <c r="U11" s="32">
+      <c r="U11" s="29">
+        <f t="shared" si="8"/>
+        <v>27.442500000000003</v>
+      </c>
+      <c r="V11" s="27"/>
+      <c r="W11" s="29"/>
+      <c r="X11" s="29"/>
+      <c r="Z11" s="32">
         <v>44327</v>
       </c>
-      <c r="V11" s="33">
-        <f t="shared" si="7"/>
+      <c r="AA11" s="33">
+        <f t="shared" si="9"/>
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B12" s="24" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D12" s="27">
         <v>44074</v>
@@ -3804,17 +4136,28 @@
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="V12" s="33"/>
-      <c r="W12" s="33"/>
-      <c r="X12" s="33"/>
-      <c r="Y12" s="33"/>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="P12" s="28">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U12" s="29">
+        <f t="shared" si="8"/>
+        <v>32.58</v>
+      </c>
+      <c r="V12" s="27"/>
+      <c r="W12" s="29"/>
+      <c r="X12" s="29"/>
+      <c r="AA12" s="33"/>
+      <c r="AB12" s="33"/>
+      <c r="AC12" s="33"/>
+      <c r="AD12" s="33"/>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B13" s="24" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" s="27">
         <v>44098</v>
@@ -3858,26 +4201,37 @@
         <f t="shared" si="5"/>
         <v>22</v>
       </c>
-      <c r="P13" s="28"/>
+      <c r="P13" s="28">
+        <f t="shared" si="6"/>
+        <v>10</v>
+      </c>
       <c r="Q13" s="28"/>
       <c r="R13" s="28"/>
-      <c r="S13" s="30"/>
-      <c r="T13" s="31"/>
-      <c r="U13" s="32"/>
-      <c r="V13" s="33"/>
-      <c r="W13" s="33"/>
-      <c r="X13" s="33"/>
-      <c r="Y13" s="33"/>
-      <c r="Z13" s="31"/>
-      <c r="AA13" s="32"/>
+      <c r="S13" s="28"/>
+      <c r="T13" s="30"/>
+      <c r="U13" s="29">
+        <f t="shared" si="8"/>
+        <v>445.57500000000005</v>
+      </c>
+      <c r="V13" s="27"/>
+      <c r="W13" s="29"/>
+      <c r="X13" s="29"/>
+      <c r="Y13" s="31"/>
+      <c r="Z13" s="32"/>
+      <c r="AA13" s="33"/>
       <c r="AB13" s="33"/>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="AC13" s="33"/>
+      <c r="AD13" s="33"/>
+      <c r="AE13" s="31"/>
+      <c r="AF13" s="32"/>
+      <c r="AG13" s="33"/>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B14" s="24" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D14" s="27">
         <v>44111</v>
@@ -3921,17 +4275,28 @@
         <f t="shared" si="5"/>
         <v>14</v>
       </c>
-      <c r="S14" s="30">
+      <c r="P14" s="28">
+        <f t="shared" si="6"/>
+        <v>5</v>
+      </c>
+      <c r="T14" s="30">
         <f>+M14/I14-1</f>
         <v>-0.5</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="U14" s="29">
+        <f t="shared" si="8"/>
+        <v>314.54999999999995</v>
+      </c>
+      <c r="V14" s="27"/>
+      <c r="W14" s="29"/>
+      <c r="X14" s="29"/>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B15" s="24" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D15" s="27">
         <v>44207</v>
@@ -3975,43 +4340,54 @@
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="P15" s="28"/>
+      <c r="P15" s="28">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
       <c r="Q15" s="28"/>
       <c r="R15" s="28"/>
-      <c r="S15" s="30">
+      <c r="S15" s="28"/>
+      <c r="T15" s="30">
         <f>+M15/I15-1</f>
         <v>-0.5</v>
       </c>
-      <c r="T15" s="24">
+      <c r="U15" s="29">
+        <f t="shared" si="8"/>
+        <v>217.6875</v>
+      </c>
+      <c r="V15" s="27"/>
+      <c r="W15" s="29"/>
+      <c r="X15" s="29"/>
+      <c r="Y15" s="24">
         <v>138.6</v>
       </c>
-      <c r="U15" s="32">
+      <c r="Z15" s="32">
         <v>44692</v>
       </c>
-      <c r="V15" s="33">
-        <f>+U15-F15</f>
+      <c r="AA15" s="33">
+        <f>+Z15-F15</f>
         <v>447</v>
       </c>
-      <c r="W15" s="33"/>
-      <c r="X15" s="33"/>
-      <c r="Y15" s="33"/>
-      <c r="Z15" s="24">
+      <c r="AB15" s="33"/>
+      <c r="AC15" s="33"/>
+      <c r="AD15" s="33"/>
+      <c r="AE15" s="24">
         <v>57.3</v>
       </c>
-      <c r="AA15" s="32">
+      <c r="AF15" s="32">
         <v>45099</v>
       </c>
-      <c r="AB15" s="33">
-        <f>+AA15-F15</f>
+      <c r="AG15" s="33">
+        <f>+AF15-F15</f>
         <v>854</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.25">
       <c r="B16" s="24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D16" s="27">
         <v>44215</v>
@@ -4055,44 +4431,55 @@
         <f t="shared" si="5"/>
         <v>47</v>
       </c>
-      <c r="P16" s="28"/>
+      <c r="P16" s="28">
+        <f t="shared" si="6"/>
+        <v>39</v>
+      </c>
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
-      <c r="S16" s="30">
+      <c r="S16" s="28"/>
+      <c r="T16" s="30">
         <f>+M16/I16-1</f>
         <v>-0.5</v>
       </c>
-      <c r="T16" s="31">
+      <c r="U16" s="29">
+        <f t="shared" si="8"/>
+        <v>127.14375000000001</v>
+      </c>
+      <c r="V16" s="27"/>
+      <c r="W16" s="29"/>
+      <c r="X16" s="29"/>
+      <c r="Y16" s="31">
         <f>+I16*0.25</f>
         <v>84.762500000000003</v>
       </c>
-      <c r="U16" s="32">
+      <c r="Z16" s="32">
         <v>44588</v>
       </c>
-      <c r="V16" s="33">
-        <f>+U16-F16</f>
+      <c r="AA16" s="33">
+        <f>+Z16-F16</f>
         <v>239</v>
       </c>
-      <c r="W16" s="33"/>
-      <c r="X16" s="33"/>
-      <c r="Y16" s="33"/>
-      <c r="Z16" s="31">
+      <c r="AB16" s="33"/>
+      <c r="AC16" s="33"/>
+      <c r="AD16" s="33"/>
+      <c r="AE16" s="31">
         <v>61.2</v>
       </c>
-      <c r="AA16" s="32">
+      <c r="AF16" s="32">
         <v>44845</v>
       </c>
-      <c r="AB16" s="33">
-        <f>+AA16-F16</f>
+      <c r="AG16" s="33">
+        <f>+AF16-F16</f>
         <v>496</v>
       </c>
     </row>
-    <row r="17" spans="2:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B17" s="24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D17" s="27">
         <v>44510</v>
@@ -4136,17 +4523,28 @@
         <f t="shared" si="5"/>
         <v>51</v>
       </c>
-      <c r="V17" s="33"/>
-      <c r="W17" s="33"/>
-      <c r="X17" s="33"/>
-      <c r="Y17" s="33"/>
-    </row>
-    <row r="18" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="P17" s="28">
+        <f t="shared" si="6"/>
+        <v>49</v>
+      </c>
+      <c r="U17" s="29">
+        <f t="shared" si="8"/>
+        <v>64.503749999999997</v>
+      </c>
+      <c r="V17" s="27"/>
+      <c r="W17" s="29"/>
+      <c r="X17" s="29"/>
+      <c r="AA17" s="33"/>
+      <c r="AB17" s="33"/>
+      <c r="AC17" s="33"/>
+      <c r="AD17" s="33"/>
+    </row>
+    <row r="18" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B18" s="24" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" s="27">
         <v>44617</v>
@@ -4190,17 +4588,28 @@
         <f t="shared" si="5"/>
         <v>41</v>
       </c>
-      <c r="V18" s="33"/>
-      <c r="W18" s="33"/>
-      <c r="X18" s="33"/>
-      <c r="Y18" s="33"/>
-    </row>
-    <row r="19" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="P18" s="28">
+        <f t="shared" si="6"/>
+        <v>32</v>
+      </c>
+      <c r="U18" s="29">
+        <f t="shared" si="8"/>
+        <v>4.75875</v>
+      </c>
+      <c r="V18" s="27"/>
+      <c r="W18" s="29"/>
+      <c r="X18" s="29"/>
+      <c r="AA18" s="33"/>
+      <c r="AB18" s="33"/>
+      <c r="AC18" s="33"/>
+      <c r="AD18" s="33"/>
+    </row>
+    <row r="19" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B19" s="24" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D19" s="27">
         <v>44938</v>
@@ -4244,17 +4653,28 @@
         <f t="shared" si="5"/>
         <v>22</v>
       </c>
-      <c r="V19" s="33"/>
-      <c r="W19" s="33"/>
-      <c r="X19" s="33"/>
-      <c r="Y19" s="33"/>
-    </row>
-    <row r="20" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="P19" s="28">
+        <f t="shared" si="6"/>
+        <v>15</v>
+      </c>
+      <c r="U19" s="29">
+        <f t="shared" si="8"/>
+        <v>2.2912500000000002</v>
+      </c>
+      <c r="V19" s="27"/>
+      <c r="W19" s="29"/>
+      <c r="X19" s="29"/>
+      <c r="AA19" s="33"/>
+      <c r="AB19" s="33"/>
+      <c r="AC19" s="33"/>
+      <c r="AD19" s="33"/>
+    </row>
+    <row r="20" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B20" s="24" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D20" s="27">
         <v>45482</v>
@@ -4298,17 +4718,36 @@
         <f t="shared" si="5"/>
         <v>49</v>
       </c>
-      <c r="V20" s="33"/>
-      <c r="W20" s="33"/>
-      <c r="X20" s="33"/>
-      <c r="Y20" s="33"/>
-    </row>
-    <row r="21" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="P20" s="28">
+        <f t="shared" si="6"/>
+        <v>45</v>
+      </c>
+      <c r="U20" s="29">
+        <f t="shared" si="8"/>
+        <v>5.32125</v>
+      </c>
+      <c r="V20" s="27">
+        <v>45722</v>
+      </c>
+      <c r="W20" s="34">
+        <f t="shared" ref="W20:W28" si="10">V20-F20</f>
+        <v>59</v>
+      </c>
+      <c r="X20" s="28">
+        <f>W20-O20</f>
+        <v>10</v>
+      </c>
+      <c r="AA20" s="33"/>
+      <c r="AB20" s="33"/>
+      <c r="AC20" s="33"/>
+      <c r="AD20" s="33"/>
+    </row>
+    <row r="21" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B21" s="24" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D21" s="27">
         <v>45488</v>
@@ -4352,13 +4791,32 @@
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-    </row>
-    <row r="22" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="P21" s="28">
+        <f t="shared" si="6"/>
+        <v>94</v>
+      </c>
+      <c r="U21" s="29">
+        <f t="shared" si="8"/>
+        <v>177.68625</v>
+      </c>
+      <c r="V21" s="27">
+        <v>45981</v>
+      </c>
+      <c r="W21" s="34">
+        <f t="shared" si="10"/>
+        <v>365</v>
+      </c>
+      <c r="X21" s="28">
+        <f>W21-O21</f>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="22" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B22" s="24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D22" s="27">
         <v>45512</v>
@@ -4402,13 +4860,32 @@
         <f t="shared" si="5"/>
         <v>113</v>
       </c>
-    </row>
-    <row r="23" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="P22" s="28">
+        <f t="shared" si="6"/>
+        <v>71</v>
+      </c>
+      <c r="U22" s="29">
+        <f t="shared" si="8"/>
+        <v>202.755</v>
+      </c>
+      <c r="V22" s="27">
+        <v>45967</v>
+      </c>
+      <c r="W22" s="34">
+        <f t="shared" si="10"/>
+        <v>176</v>
+      </c>
+      <c r="X22" s="28">
+        <f>W22-O22</f>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B23" s="24" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D23" s="27">
         <v>45562</v>
@@ -4452,22 +4929,41 @@
         <f t="shared" si="5"/>
         <v>52</v>
       </c>
-      <c r="T23" s="25"/>
-      <c r="U23" s="25"/>
-      <c r="V23" s="25"/>
-      <c r="W23" s="25"/>
-      <c r="X23" s="25"/>
+      <c r="P23" s="28">
+        <f t="shared" si="6"/>
+        <v>50</v>
+      </c>
+      <c r="U23" s="29">
+        <f t="shared" si="8"/>
+        <v>19.151250000000001</v>
+      </c>
+      <c r="V23" s="27">
+        <v>45726</v>
+      </c>
+      <c r="W23" s="34">
+        <f t="shared" si="10"/>
+        <v>63</v>
+      </c>
+      <c r="X23" s="28">
+        <f t="shared" ref="X23:X28" si="11">W23-O23</f>
+        <v>11</v>
+      </c>
       <c r="Y23" s="25"/>
       <c r="Z23" s="25"/>
       <c r="AA23" s="25"/>
       <c r="AB23" s="25"/>
-    </row>
-    <row r="24" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="AC23" s="25"/>
+      <c r="AD23" s="25"/>
+      <c r="AE23" s="25"/>
+      <c r="AF23" s="25"/>
+      <c r="AG23" s="25"/>
+    </row>
+    <row r="24" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B24" s="24" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D24" s="27">
         <v>45579</v>
@@ -4511,17 +5007,36 @@
         <f t="shared" si="5"/>
         <v>19</v>
       </c>
-      <c r="V24" s="33"/>
-      <c r="W24" s="33"/>
-      <c r="X24" s="33"/>
-      <c r="Y24" s="33"/>
-    </row>
-    <row r="25" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="P24" s="28">
+        <f t="shared" si="6"/>
+        <v>12</v>
+      </c>
+      <c r="U24" s="29">
+        <f t="shared" si="8"/>
+        <v>3.6674999999999995</v>
+      </c>
+      <c r="V24" s="27">
+        <v>45723</v>
+      </c>
+      <c r="W24" s="34">
+        <f t="shared" si="10"/>
+        <v>22</v>
+      </c>
+      <c r="X24" s="28">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="AA24" s="33"/>
+      <c r="AB24" s="33"/>
+      <c r="AC24" s="33"/>
+      <c r="AD24" s="33"/>
+    </row>
+    <row r="25" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B25" s="24" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D25" s="27">
         <v>45581</v>
@@ -4565,22 +5080,41 @@
         <f t="shared" si="5"/>
         <v>6</v>
       </c>
-      <c r="T25" s="25"/>
-      <c r="U25" s="25"/>
-      <c r="V25" s="25"/>
-      <c r="W25" s="25"/>
-      <c r="X25" s="25"/>
+      <c r="P25" s="28">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="U25" s="29">
+        <f t="shared" si="8"/>
+        <v>7.5</v>
+      </c>
+      <c r="V25" s="27">
+        <v>45670</v>
+      </c>
+      <c r="W25" s="34">
+        <f t="shared" si="10"/>
+        <v>11</v>
+      </c>
+      <c r="X25" s="28">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
       <c r="Y25" s="25"/>
       <c r="Z25" s="25"/>
       <c r="AA25" s="25"/>
       <c r="AB25" s="25"/>
-    </row>
-    <row r="26" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="AC25" s="25"/>
+      <c r="AD25" s="25"/>
+      <c r="AE25" s="25"/>
+      <c r="AF25" s="25"/>
+      <c r="AG25" s="25"/>
+    </row>
+    <row r="26" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B26" s="24" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D26" s="27">
         <v>45582</v>
@@ -4624,13 +5158,32 @@
         <f t="shared" si="5"/>
         <v>21</v>
       </c>
-    </row>
-    <row r="27" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="P26" s="28">
+        <f t="shared" si="6"/>
+        <v>20</v>
+      </c>
+      <c r="U26" s="29">
+        <f t="shared" si="8"/>
+        <v>9.629999999999999</v>
+      </c>
+      <c r="V26" s="27">
+        <v>45667</v>
+      </c>
+      <c r="W26" s="34">
+        <f t="shared" si="10"/>
+        <v>23</v>
+      </c>
+      <c r="X26" s="28">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B27" s="24" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D27" s="27">
         <v>45593</v>
@@ -4674,13 +5227,32 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-    </row>
-    <row r="28" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="P27" s="28">
+        <f t="shared" si="6"/>
+        <v>38</v>
+      </c>
+      <c r="U27" s="29">
+        <f t="shared" si="8"/>
+        <v>9.0862499999999997</v>
+      </c>
+      <c r="V27" s="27">
+        <v>45713</v>
+      </c>
+      <c r="W27" s="34">
+        <f t="shared" si="10"/>
+        <v>61</v>
+      </c>
+      <c r="X27" s="28">
+        <f t="shared" si="11"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B28" s="24" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D28" s="27">
         <v>45595</v>
@@ -4724,21 +5296,40 @@
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="2:28" x14ac:dyDescent="0.25">
+      <c r="P28" s="28">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="U28" s="29">
+        <f t="shared" si="8"/>
+        <v>7.0237499999999997</v>
+      </c>
+      <c r="V28" s="27">
+        <v>45715</v>
+      </c>
+      <c r="W28" s="34">
+        <f t="shared" si="10"/>
+        <v>90</v>
+      </c>
+      <c r="X28" s="28">
+        <f t="shared" si="11"/>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B29" s="35" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D29" s="27">
         <v>45601</v>
       </c>
-      <c r="E29" s="37">
+      <c r="E29" s="25">
         <v>8</v>
       </c>
-      <c r="F29" s="36">
+      <c r="F29" s="27">
         <v>45964</v>
       </c>
       <c r="G29" s="25">
@@ -4749,34 +5340,47 @@
         <f t="shared" si="1"/>
         <v>45.375</v>
       </c>
-      <c r="I29" s="38">
+      <c r="I29" s="29">
         <v>207.18</v>
       </c>
       <c r="J29" s="29">
         <f t="shared" si="2"/>
         <v>155.38499999999999</v>
       </c>
-      <c r="K29" s="36">
-        <f t="shared" ref="K29:K34" ca="1" si="8">F29+$L$1</f>
-        <v>45975.058823529413</v>
-      </c>
-      <c r="L29" s="44"/>
+      <c r="K29" s="27">
+        <v>45982</v>
+      </c>
+      <c r="L29" s="34">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
       <c r="M29" s="29">
         <f t="shared" si="4"/>
         <v>103.59</v>
       </c>
-      <c r="N29" s="36">
-        <f t="shared" ref="N29:N36" ca="1" si="9">F29+$O$1</f>
-        <v>46006.862068965514</v>
-      </c>
-      <c r="O29" s="44"/>
-    </row>
-    <row r="30" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B30" s="35" t="s">
-        <v>60</v>
+      <c r="N29" s="54">
+        <f t="shared" ref="N29:N36" ca="1" si="12">F29+$O$1</f>
+        <v>46013.222222222219</v>
+      </c>
+      <c r="O29" s="43">
+        <f ca="1">TODAY()-F29</f>
+        <v>102</v>
+      </c>
+      <c r="P29" s="28"/>
+      <c r="U29" s="29">
+        <f t="shared" si="8"/>
+        <v>77.692499999999995</v>
+      </c>
+      <c r="V29" s="27"/>
+      <c r="W29" s="29"/>
+      <c r="X29" s="29"/>
+    </row>
+    <row r="30" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B30" s="24" t="s">
+        <v>58</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D30" s="27">
         <v>45671</v>
@@ -4813,27 +5417,40 @@
         <f t="shared" si="4"/>
         <v>28.17</v>
       </c>
-      <c r="N30" s="36">
-        <f t="shared" ca="1" si="9"/>
-        <v>45987.862068965514</v>
-      </c>
-      <c r="O30" s="28"/>
-      <c r="T30" s="25"/>
-      <c r="U30" s="25"/>
-      <c r="V30" s="25"/>
-      <c r="W30" s="25"/>
-      <c r="X30" s="25"/>
+      <c r="N30" s="27">
+        <v>45974</v>
+      </c>
+      <c r="O30" s="25">
+        <f>+N30-F30</f>
+        <v>29</v>
+      </c>
+      <c r="P30" s="28">
+        <f>O30-L30</f>
+        <v>23</v>
+      </c>
+      <c r="U30" s="29">
+        <f t="shared" si="8"/>
+        <v>21.127500000000001</v>
+      </c>
+      <c r="V30" s="27"/>
+      <c r="W30" s="29"/>
+      <c r="X30" s="29"/>
       <c r="Y30" s="25"/>
       <c r="Z30" s="25"/>
       <c r="AA30" s="25"/>
       <c r="AB30" s="25"/>
-    </row>
-    <row r="31" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B31" s="35" t="s">
-        <v>59</v>
+      <c r="AC30" s="25"/>
+      <c r="AD30" s="25"/>
+      <c r="AE30" s="25"/>
+      <c r="AF30" s="25"/>
+      <c r="AG30" s="25"/>
+    </row>
+    <row r="31" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B31" s="24" t="s">
+        <v>57</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D31" s="27">
         <v>45728</v>
@@ -4870,26 +5487,40 @@
         <f t="shared" si="4"/>
         <v>41.045000000000002</v>
       </c>
-      <c r="N31" s="36">
-        <f t="shared" ca="1" si="9"/>
-        <v>45985.862068965514</v>
-      </c>
-      <c r="T31" s="25"/>
-      <c r="U31" s="25"/>
-      <c r="V31" s="25"/>
-      <c r="W31" s="25"/>
-      <c r="X31" s="25"/>
+      <c r="N31" s="27">
+        <v>45981</v>
+      </c>
+      <c r="O31" s="25">
+        <f>+N31-F31</f>
+        <v>38</v>
+      </c>
+      <c r="P31" s="28">
+        <f>O31-L31</f>
+        <v>31</v>
+      </c>
+      <c r="U31" s="29">
+        <f t="shared" si="8"/>
+        <v>30.783750000000001</v>
+      </c>
+      <c r="V31" s="27"/>
+      <c r="W31" s="29"/>
+      <c r="X31" s="29"/>
       <c r="Y31" s="25"/>
       <c r="Z31" s="25"/>
       <c r="AA31" s="25"/>
       <c r="AB31" s="25"/>
-    </row>
-    <row r="32" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B32" s="35" t="s">
-        <v>58</v>
+      <c r="AC31" s="25"/>
+      <c r="AD31" s="25"/>
+      <c r="AE31" s="25"/>
+      <c r="AF31" s="25"/>
+      <c r="AG31" s="25"/>
+    </row>
+    <row r="32" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B32" s="24" t="s">
+        <v>56</v>
       </c>
       <c r="C32" s="25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D32" s="27">
         <v>45754</v>
@@ -4926,34 +5557,48 @@
         <f t="shared" si="4"/>
         <v>87.07</v>
       </c>
-      <c r="N32" s="36">
-        <f t="shared" ca="1" si="9"/>
-        <v>45986.862068965514</v>
-      </c>
-      <c r="T32" s="25"/>
-      <c r="U32" s="25"/>
-      <c r="V32" s="25"/>
-      <c r="W32" s="25"/>
-      <c r="X32" s="25"/>
+      <c r="N32" s="27">
+        <v>45987</v>
+      </c>
+      <c r="O32" s="25">
+        <f>+N32-F32</f>
+        <v>43</v>
+      </c>
+      <c r="P32" s="28">
+        <f>O32-L32</f>
+        <v>35</v>
+      </c>
+      <c r="U32" s="29">
+        <f t="shared" si="8"/>
+        <v>65.302499999999995</v>
+      </c>
+      <c r="V32" s="27"/>
+      <c r="W32" s="29"/>
+      <c r="X32" s="29"/>
       <c r="Y32" s="25"/>
       <c r="Z32" s="25"/>
       <c r="AA32" s="25"/>
       <c r="AB32" s="25"/>
-    </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B33" s="35" t="s">
-        <v>132</v>
+      <c r="AC32" s="25"/>
+      <c r="AD32" s="25"/>
+      <c r="AE32" s="25"/>
+      <c r="AF32" s="25"/>
+      <c r="AG32" s="25"/>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="B33" s="24" t="s">
+        <v>129</v>
       </c>
       <c r="C33" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D33" s="27">
         <v>45756</v>
       </c>
-      <c r="E33" s="37">
+      <c r="E33" s="25">
         <v>6</v>
       </c>
-      <c r="F33" s="36">
+      <c r="F33" s="27">
         <v>45936</v>
       </c>
       <c r="G33" s="25">
@@ -4964,99 +5609,126 @@
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="I33" s="38">
+      <c r="I33" s="29">
         <v>110.89</v>
       </c>
       <c r="J33" s="29">
         <f t="shared" si="2"/>
         <v>83.167500000000004</v>
       </c>
-      <c r="K33" s="55">
-        <f t="shared" ca="1" si="8"/>
-        <v>45947.058823529413</v>
-      </c>
-      <c r="L33" s="44">
-        <f ca="1">TODAY()-F33</f>
-        <v>32</v>
+      <c r="K33" s="27">
+        <v>45972</v>
+      </c>
+      <c r="L33" s="34">
+        <f t="shared" si="3"/>
+        <v>36</v>
       </c>
       <c r="M33" s="29">
         <f t="shared" si="4"/>
         <v>55.445</v>
       </c>
-      <c r="N33" s="36">
-        <f t="shared" ca="1" si="9"/>
-        <v>45978.862068965514</v>
-      </c>
-      <c r="T33" s="25"/>
-      <c r="U33" s="25"/>
-      <c r="V33" s="25"/>
-      <c r="W33" s="25"/>
-      <c r="X33" s="25"/>
+      <c r="N33" s="27">
+        <v>46042</v>
+      </c>
+      <c r="O33" s="25">
+        <f>+N33-F33</f>
+        <v>106</v>
+      </c>
+      <c r="P33" s="28">
+        <f>O33-L33</f>
+        <v>70</v>
+      </c>
+      <c r="U33" s="29">
+        <f t="shared" si="8"/>
+        <v>41.583750000000002</v>
+      </c>
+      <c r="V33" s="27"/>
+      <c r="W33" s="29"/>
+      <c r="X33" s="29"/>
       <c r="Y33" s="25"/>
       <c r="Z33" s="25"/>
       <c r="AA33" s="25"/>
       <c r="AB33" s="25"/>
-    </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC33" s="25"/>
+      <c r="AD33" s="25"/>
+      <c r="AE33" s="25"/>
+      <c r="AF33" s="25"/>
+      <c r="AG33" s="25"/>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B34" s="35" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C34" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D34" s="27">
         <v>45756</v>
       </c>
-      <c r="E34" s="37">
-        <v>8</v>
-      </c>
-      <c r="F34" s="36">
-        <v>45945</v>
+      <c r="E34" s="25">
+        <v>9</v>
+      </c>
+      <c r="F34" s="27">
+        <v>45987</v>
       </c>
       <c r="G34" s="25">
         <f t="shared" si="0"/>
-        <v>189</v>
+        <v>231</v>
       </c>
       <c r="H34" s="34">
         <f t="shared" si="1"/>
-        <v>23.625</v>
-      </c>
-      <c r="I34" s="38">
-        <v>75.36</v>
+        <v>25.666666666666668</v>
+      </c>
+      <c r="I34" s="29">
+        <v>87.3</v>
       </c>
       <c r="J34" s="29">
         <f t="shared" si="2"/>
-        <v>56.519999999999996</v>
-      </c>
-      <c r="K34" s="36">
-        <f t="shared" ca="1" si="8"/>
-        <v>45956.058823529413</v>
+        <v>65.474999999999994</v>
+      </c>
+      <c r="K34" s="27">
+        <v>45995</v>
+      </c>
+      <c r="L34" s="34">
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="M34" s="29">
         <f t="shared" si="4"/>
-        <v>37.68</v>
-      </c>
-      <c r="N34" s="36">
-        <f t="shared" ca="1" si="9"/>
-        <v>45987.862068965514</v>
-      </c>
-      <c r="O34" s="44"/>
-      <c r="T34" s="25"/>
-      <c r="U34" s="25"/>
-      <c r="V34" s="25"/>
-      <c r="W34" s="25"/>
-      <c r="X34" s="25"/>
+        <v>43.65</v>
+      </c>
+      <c r="N34" s="54">
+        <f ca="1">F34+$O$1</f>
+        <v>46036.222222222219</v>
+      </c>
+      <c r="O34" s="43">
+        <f ca="1">TODAY()-F34</f>
+        <v>79</v>
+      </c>
+      <c r="P34" s="28"/>
+      <c r="U34" s="29">
+        <f t="shared" si="8"/>
+        <v>32.737499999999997</v>
+      </c>
+      <c r="V34" s="27"/>
+      <c r="W34" s="29"/>
+      <c r="X34" s="29"/>
       <c r="Y34" s="25"/>
       <c r="Z34" s="25"/>
       <c r="AA34" s="25"/>
       <c r="AB34" s="25"/>
-    </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B35" s="35" t="s">
-        <v>108</v>
+      <c r="AC34" s="25"/>
+      <c r="AD34" s="25"/>
+      <c r="AE34" s="25"/>
+      <c r="AF34" s="25"/>
+      <c r="AG34" s="25"/>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="B35" s="24" t="s">
+        <v>106</v>
       </c>
       <c r="C35" s="25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D35" s="27">
         <v>45756</v>
@@ -5093,74 +5765,95 @@
         <f t="shared" si="4"/>
         <v>10.195</v>
       </c>
-      <c r="N35" s="55">
-        <f t="shared" ca="1" si="9"/>
-        <v>45915.862068965514</v>
-      </c>
-      <c r="O35" s="44">
-        <f ca="1">TODAY()-F35</f>
-        <v>95</v>
-      </c>
-    </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="N35" s="27">
+        <v>46056</v>
+      </c>
+      <c r="O35" s="25">
+        <f>+N35-F35</f>
+        <v>183</v>
+      </c>
+      <c r="P35" s="28">
+        <f>O35-L35</f>
+        <v>168</v>
+      </c>
+      <c r="U35" s="29">
+        <f t="shared" si="8"/>
+        <v>7.6462500000000002</v>
+      </c>
+      <c r="V35" s="27"/>
+      <c r="W35" s="29"/>
+      <c r="X35" s="29"/>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B36" s="35" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C36" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D36" s="27">
         <v>45756</v>
       </c>
-      <c r="E36" s="37">
-        <v>5</v>
-      </c>
-      <c r="F36" s="36">
-        <v>45938</v>
+      <c r="E36" s="25">
+        <v>6</v>
+      </c>
+      <c r="F36" s="27">
+        <v>46038</v>
       </c>
       <c r="G36" s="25">
         <f t="shared" si="0"/>
-        <v>182</v>
+        <v>282</v>
       </c>
       <c r="H36" s="34">
         <f t="shared" si="1"/>
-        <v>36.4</v>
-      </c>
-      <c r="I36" s="38">
-        <v>105.67</v>
+        <v>47</v>
+      </c>
+      <c r="I36" s="29">
+        <v>130.72</v>
       </c>
       <c r="J36" s="29">
         <f t="shared" si="2"/>
-        <v>79.252499999999998</v>
-      </c>
-      <c r="K36" s="36">
-        <f ca="1">F36+$L$1</f>
-        <v>45949.058823529413</v>
+        <v>98.039999999999992</v>
+      </c>
+      <c r="K36" s="27">
+        <v>46055</v>
+      </c>
+      <c r="L36" s="34">
+        <f>K36-F36</f>
+        <v>17</v>
       </c>
       <c r="M36" s="29">
         <f t="shared" si="4"/>
-        <v>52.835000000000001</v>
+        <v>65.36</v>
       </c>
       <c r="N36" s="36">
-        <f t="shared" ca="1" si="9"/>
-        <v>45980.862068965514</v>
-      </c>
-      <c r="T36" s="25"/>
-      <c r="U36" s="25"/>
-      <c r="V36" s="25"/>
-      <c r="W36" s="25"/>
-      <c r="X36" s="25"/>
+        <f t="shared" ca="1" si="12"/>
+        <v>46087.222222222219</v>
+      </c>
+      <c r="P36" s="28"/>
+      <c r="U36" s="29">
+        <f t="shared" si="8"/>
+        <v>49.019999999999996</v>
+      </c>
+      <c r="V36" s="27"/>
+      <c r="W36" s="29"/>
+      <c r="X36" s="29"/>
       <c r="Y36" s="25"/>
       <c r="Z36" s="25"/>
       <c r="AA36" s="25"/>
       <c r="AB36" s="25"/>
-    </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC36" s="25"/>
+      <c r="AD36" s="25"/>
+      <c r="AE36" s="25"/>
+      <c r="AF36" s="25"/>
+      <c r="AG36" s="25"/>
+    </row>
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B37" s="24" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D37" s="27">
         <v>45779</v>
@@ -5204,22 +5897,33 @@
         <f>+N37-F37</f>
         <v>61</v>
       </c>
-      <c r="T37" s="25"/>
-      <c r="U37" s="25"/>
-      <c r="V37" s="25"/>
-      <c r="W37" s="25"/>
-      <c r="X37" s="25"/>
+      <c r="P37" s="28">
+        <f>O37-L37</f>
+        <v>40</v>
+      </c>
+      <c r="U37" s="29">
+        <f t="shared" si="8"/>
+        <v>68.842500000000001</v>
+      </c>
+      <c r="V37" s="27"/>
+      <c r="W37" s="29"/>
+      <c r="X37" s="29"/>
       <c r="Y37" s="25"/>
       <c r="Z37" s="25"/>
       <c r="AA37" s="25"/>
       <c r="AB37" s="25"/>
-    </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B38" s="35" t="s">
-        <v>131</v>
+      <c r="AC37" s="25"/>
+      <c r="AD37" s="25"/>
+      <c r="AE37" s="25"/>
+      <c r="AF37" s="25"/>
+      <c r="AG37" s="25"/>
+    </row>
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="B38" s="24" t="s">
+        <v>128</v>
       </c>
       <c r="C38" s="25" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D38" s="27">
         <v>45793</v>
@@ -5256,26 +5960,40 @@
         <f t="shared" si="4"/>
         <v>2.0649999999999999</v>
       </c>
-      <c r="N38" s="36">
-        <f ca="1">F38+$O$1</f>
-        <v>45978.862068965514</v>
-      </c>
-      <c r="T38" s="25"/>
-      <c r="U38" s="25"/>
-      <c r="V38" s="25"/>
-      <c r="W38" s="25"/>
-      <c r="X38" s="25"/>
+      <c r="N38" s="27">
+        <v>45980</v>
+      </c>
+      <c r="O38" s="25">
+        <f>+N38-F38</f>
+        <v>44</v>
+      </c>
+      <c r="P38" s="28">
+        <f>O38-L38</f>
+        <v>28</v>
+      </c>
+      <c r="U38" s="29">
+        <f t="shared" si="8"/>
+        <v>1.5487500000000001</v>
+      </c>
+      <c r="V38" s="27"/>
+      <c r="W38" s="29"/>
+      <c r="X38" s="29"/>
       <c r="Y38" s="25"/>
       <c r="Z38" s="25"/>
       <c r="AA38" s="25"/>
       <c r="AB38" s="25"/>
-    </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC38" s="25"/>
+      <c r="AD38" s="25"/>
+      <c r="AE38" s="25"/>
+      <c r="AF38" s="25"/>
+      <c r="AG38" s="25"/>
+    </row>
+    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B39" s="24" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D39" s="27">
         <v>45814</v>
@@ -5319,38 +6037,49 @@
         <f>+N39-F39</f>
         <v>57</v>
       </c>
-      <c r="T39" s="25"/>
-      <c r="U39" s="25"/>
-      <c r="V39" s="25"/>
-      <c r="W39" s="25"/>
-      <c r="X39" s="25"/>
+      <c r="P39" s="28">
+        <f>O39-L39</f>
+        <v>53</v>
+      </c>
+      <c r="U39" s="29">
+        <f t="shared" si="8"/>
+        <v>98.793749999999989</v>
+      </c>
+      <c r="V39" s="27"/>
+      <c r="W39" s="29"/>
+      <c r="X39" s="29"/>
       <c r="Y39" s="25"/>
       <c r="Z39" s="25"/>
       <c r="AA39" s="25"/>
       <c r="AB39" s="25"/>
-    </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC39" s="25"/>
+      <c r="AD39" s="25"/>
+      <c r="AE39" s="25"/>
+      <c r="AF39" s="25"/>
+      <c r="AG39" s="25"/>
+    </row>
+    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B40" s="24" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B41" s="24" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B42" s="24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N42" s="25" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="43" spans="1:28" s="35" customFormat="1" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:33" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="24"/>
       <c r="B43" s="24" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C43" s="25"/>
       <c r="D43" s="25"/>
@@ -5364,73 +6093,85 @@
       <c r="L43" s="34"/>
       <c r="M43" s="29"/>
       <c r="N43" s="25" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="O43" s="37"/>
-      <c r="P43" s="37"/>
+      <c r="P43" s="34"/>
       <c r="Q43" s="37"/>
       <c r="R43" s="37"/>
       <c r="S43" s="37"/>
-    </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="T43" s="37"/>
+      <c r="U43" s="37"/>
+      <c r="V43" s="37"/>
+      <c r="W43" s="37"/>
+      <c r="X43" s="37"/>
+    </row>
+    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B44" s="24" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N44" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="S44" s="30"/>
-    </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+      <c r="T44" s="30"/>
+      <c r="U44" s="30"/>
+      <c r="V44" s="30"/>
+      <c r="W44" s="30"/>
+      <c r="X44" s="30"/>
+    </row>
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B45" s="24" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="B46" s="24" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B46" s="24" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B48" s="58" t="s">
-        <v>129</v>
+    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="I47" s="55" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="B48" s="57"/>
+      <c r="I48" s="55" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="49" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I49" s="55" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="50" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I50" s="55" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="51" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I51" s="56" t="s">
-        <v>20</v>
+      <c r="I51" s="58" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="52" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I52" s="56" t="s">
-        <v>124</v>
+      <c r="I52" s="55" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="53" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I53" s="56" t="s">
-        <v>125</v>
+      <c r="I53" s="55" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="54" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I54" s="56" t="s">
+      <c r="I54" s="55" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="55" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I55" s="59" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="56" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I56" s="56" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="57" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I57" s="56"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AB46">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AG46">
     <sortCondition ref="D3:D46"/>
   </sortState>
   <hyperlinks>
@@ -5445,68 +6186,68 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3B95373-36E1-4041-B321-49E0FB572644}">
   <dimension ref="A1:AC7"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" style="54" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" style="54" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.77734375" style="54" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" style="54" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.77734375" style="54" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.21875" style="54" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.88671875" style="54" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.21875" style="54" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.77734375" style="54" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.88671875" style="54" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.21875" style="54" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.77734375" style="54" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.88671875" style="54" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8" style="54" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12" style="54" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.44140625" style="54" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.77734375" style="54" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.21875" style="54" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.77734375" style="54" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.109375" style="54" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8" style="54" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12" style="54" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.77734375" style="54" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.21875" style="54" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.77734375" style="54" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="8.88671875" style="54"/>
+    <col min="1" max="1" width="4.88671875" style="53" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="53" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" style="53" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.77734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" style="53" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.77734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.21875" style="53" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="53" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.21875" style="53" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.77734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.88671875" style="53" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.21875" style="53" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.77734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.88671875" style="53" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8" style="53" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12" style="53" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.44140625" style="53" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.77734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.21875" style="53" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.77734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8" style="53" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12" style="53" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.77734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.21875" style="53" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.77734375" style="53" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="53"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="E1" s="41">
+      <c r="E1" s="40">
         <f>AVERAGE(E3:E106)</f>
         <v>8</v>
       </c>
-      <c r="F1" s="40"/>
-      <c r="G1" s="39">
+      <c r="F1" s="39"/>
+      <c r="G1" s="38">
         <f ca="1">AVERAGE(G3:G106)</f>
-        <v>247</v>
-      </c>
-      <c r="H1" s="39">
+        <v>296</v>
+      </c>
+      <c r="H1" s="38">
         <f ca="1">AVERAGE(H3:H106)</f>
-        <v>30.875</v>
-      </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="39">
+        <v>37</v>
+      </c>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="38">
         <f>AVERAGE(L3:L106)</f>
         <v>21</v>
       </c>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="39">
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="38">
         <f>AVERAGE(O3:O106)</f>
         <v>271</v>
       </c>
@@ -5529,119 +6270,119 @@
     </row>
     <row r="2" spans="1:29" s="24" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B2" s="24" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G2" s="25" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J2" s="25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K2" s="25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L2" s="25" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M2" s="25" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="N2" s="25" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="O2" s="25" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="P2" s="25" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Q2" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="R2" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="S2" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="T2" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="U2" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="V2" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="R2" s="25" t="s">
+      <c r="W2" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="S2" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="T2" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="U2" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="V2" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="W2" s="25" t="s">
-        <v>79</v>
-      </c>
       <c r="X2" s="25" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Y2" s="25" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Z2" s="25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AA2" s="25" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AB2" s="25" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:29" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="50" t="s">
-        <v>118</v>
-      </c>
-      <c r="C3" s="45" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="52">
+      <c r="B3" s="49" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="51">
         <v>45756</v>
       </c>
-      <c r="E3" s="45">
+      <c r="E3" s="44">
         <v>8</v>
       </c>
-      <c r="F3" s="46">
+      <c r="F3" s="45">
         <f>D3+'Equity Bubbles'!G1</f>
-        <v>45880.432432432433</v>
-      </c>
-      <c r="G3" s="47">
+        <v>45884.270270270274</v>
+      </c>
+      <c r="G3" s="46">
         <f ca="1">TODAY()-D3</f>
-        <v>212</v>
-      </c>
-      <c r="H3" s="48">
+        <v>310</v>
+      </c>
+      <c r="H3" s="47">
         <f ca="1">G3/E3</f>
-        <v>26.5</v>
-      </c>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="46"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="49"/>
-      <c r="N3" s="46"/>
-      <c r="O3" s="45"/>
+        <v>38.75</v>
+      </c>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="44"/>
       <c r="P3" s="25"/>
       <c r="Q3" s="25"/>
       <c r="R3" s="25"/>
@@ -5657,13 +6398,13 @@
       <c r="AB3" s="25"/>
     </row>
     <row r="4" spans="1:29" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="51" t="s">
-        <v>119</v>
+      <c r="B4" s="50" t="s">
+        <v>117</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" s="53">
+        <v>51</v>
+      </c>
+      <c r="D4" s="52">
         <v>36327</v>
       </c>
       <c r="E4" s="25">
@@ -5720,11 +6461,11 @@
       <c r="AB4" s="25"/>
     </row>
     <row r="5" spans="1:29" s="24" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="51" t="s">
-        <v>120</v>
+      <c r="B5" s="50" t="s">
+        <v>118</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D5" s="27"/>
       <c r="E5" s="25"/>
@@ -5753,13 +6494,13 @@
       <c r="AB5" s="25"/>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="B6" s="54" t="s">
-        <v>121</v>
+      <c r="B6" s="53" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="B7" s="54" t="s">
-        <v>122</v>
+      <c r="B7" s="53" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -5769,4 +6510,191 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F01B1BDF-B02A-4348-8E7D-F20BA5497248}">
+  <dimension ref="B3:D22"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="59"/>
+    <col min="2" max="2" width="24.21875" style="59" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" style="59" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="76.77734375" style="59" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="59"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B3" s="60" t="s">
+        <v>139</v>
+      </c>
+      <c r="C3" s="61" t="s">
+        <v>147</v>
+      </c>
+      <c r="D3" s="61" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B4" s="59" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="59" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" s="59" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B5" s="59" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" s="59" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" s="59" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="59" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>150</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="59" t="s">
+        <v>143</v>
+      </c>
+      <c r="C7" s="59" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" s="59" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="59" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="59" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8" s="59" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="59" t="s">
+        <v>145</v>
+      </c>
+      <c r="C9" s="59" t="s">
+        <v>157</v>
+      </c>
+      <c r="D9" s="59" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="59" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10" s="59" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" s="59" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B11" s="62" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" s="62" t="s">
+        <v>164</v>
+      </c>
+      <c r="D11" s="62" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B13" s="59" t="s">
+        <v>166</v>
+      </c>
+      <c r="C13" s="59" t="s">
+        <v>167</v>
+      </c>
+      <c r="D13" s="59" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B14" s="59" t="s">
+        <v>171</v>
+      </c>
+      <c r="C14" s="59" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" s="60" t="s">
+        <v>173</v>
+      </c>
+      <c r="C18" s="61" t="s">
+        <v>147</v>
+      </c>
+      <c r="D18" s="61" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" s="59" t="s">
+        <v>141</v>
+      </c>
+      <c r="C19" s="59" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="59" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="59" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="59" t="s">
+        <v>175</v>
+      </c>
+      <c r="D20" s="59" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21" s="59" t="s">
+        <v>143</v>
+      </c>
+      <c r="C21" s="59" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B22" s="59" t="s">
+        <v>178</v>
+      </c>
+      <c r="C22" s="59" t="s">
+        <v>161</v>
+      </c>
+      <c r="D22" s="59" t="s">
+        <v>179</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Financial Analysis/Models.xlsx
+++ b/Financial Analysis/Models.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7AF0A32-B77E-41EA-A8E0-E5EDE5AFEDD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EAAB2B4-491A-42EA-8099-9452C35E8369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{40711DBD-7A53-4994-9FF1-9E754821B18D}"/>
   </bookViews>
@@ -1344,25 +1344,15 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="3">
-          <cell r="N3">
-            <v>26.62062128663548</v>
-          </cell>
-          <cell r="T3">
-            <v>3.687787857781355</v>
-          </cell>
-          <cell r="AA3">
-            <v>-0.16118420686945295</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7" t="str">
-            <v>Microsoft</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8" t="str">
-            <v>Amazon</v>
+        <row r="5">
+          <cell r="N5">
+            <v>29.012325792539912</v>
+          </cell>
+          <cell r="T5">
+            <v>9.5189086874062898</v>
+          </cell>
+          <cell r="AA5">
+            <v>-0.2173697345984017</v>
           </cell>
         </row>
         <row r="9">
@@ -1497,92 +1487,92 @@
         </row>
         <row r="35">
           <cell r="B35" t="str">
-            <v>IonQ</v>
+            <v>Zoom Video</v>
           </cell>
         </row>
         <row r="36">
           <cell r="B36" t="str">
-            <v>Zoom Video</v>
+            <v>IonQ</v>
           </cell>
         </row>
         <row r="37">
           <cell r="B37" t="str">
-            <v>Rigetti</v>
+            <v>Roku</v>
           </cell>
         </row>
         <row r="38">
           <cell r="B38" t="str">
-            <v>Roku</v>
+            <v>Logitech</v>
           </cell>
         </row>
         <row r="39">
           <cell r="B39" t="str">
-            <v>Logitech</v>
+            <v>Snap Inc</v>
           </cell>
         </row>
         <row r="40">
           <cell r="B40" t="str">
-            <v>Snap Inc</v>
+            <v>Shift4</v>
           </cell>
         </row>
         <row r="41">
           <cell r="B41" t="str">
-            <v>Shift4</v>
+            <v>EPAM</v>
           </cell>
         </row>
         <row r="42">
           <cell r="B42" t="str">
-            <v>EPAM</v>
+            <v>Novami</v>
           </cell>
         </row>
         <row r="43">
           <cell r="B43" t="str">
-            <v>Novami</v>
+            <v>StoneCo</v>
           </cell>
         </row>
         <row r="44">
           <cell r="B44" t="str">
-            <v>StoneCo</v>
+            <v>GameStop</v>
           </cell>
         </row>
         <row r="45">
           <cell r="B45" t="str">
-            <v>GameStop</v>
+            <v>Rigetti</v>
           </cell>
         </row>
         <row r="46">
           <cell r="B46" t="str">
-            <v>Life360</v>
+            <v>Duolingo</v>
           </cell>
         </row>
         <row r="47">
           <cell r="B47" t="str">
-            <v>Duolingo</v>
+            <v>Life360</v>
           </cell>
         </row>
         <row r="48">
           <cell r="B48" t="str">
-            <v>Wise</v>
+            <v>Stride</v>
           </cell>
         </row>
         <row r="49">
           <cell r="B49" t="str">
-            <v>Stride</v>
+            <v>PagSeguro</v>
           </cell>
         </row>
         <row r="50">
           <cell r="B50" t="str">
-            <v>PlugPower</v>
+            <v>Paysafe</v>
           </cell>
         </row>
         <row r="51">
           <cell r="B51" t="str">
-            <v>PagSeguro</v>
+            <v>Wise</v>
           </cell>
         </row>
         <row r="52">
           <cell r="B52" t="str">
-            <v>Paysafe</v>
+            <v>PlugPower</v>
           </cell>
         </row>
         <row r="53">
@@ -1597,12 +1587,12 @@
         </row>
         <row r="55">
           <cell r="B55" t="str">
-            <v>Bandwidth</v>
+            <v>Corsair Gaming</v>
           </cell>
         </row>
         <row r="56">
           <cell r="B56" t="str">
-            <v>Corsair Gaming</v>
+            <v>Bandwidth</v>
           </cell>
         </row>
         <row r="57">
@@ -1756,369 +1746,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="O3">
-            <v>16.412502823367006</v>
-          </cell>
-          <cell r="U3">
-            <v>1.0405324209773694</v>
-          </cell>
-          <cell r="AA3">
-            <v>-0.30225003994070132</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4" t="str">
-            <v>Tesla</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5" t="str">
-            <v>Toyota</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6" t="str">
-            <v>Volkswagen</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7" t="str">
-            <v>General Motors</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8" t="str">
-            <v>Ford</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9" t="str">
-            <v>Mercedes-Benz</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10" t="str">
-            <v>BMW</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11" t="str">
-            <v>Honda</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12" t="str">
-            <v>Porsche</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13" t="str">
-            <v>Stellantis</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14" t="str">
-            <v>Ferrari</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15" t="str">
-            <v>Rivian</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16" t="str">
-            <v>Lucid</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17" t="str">
-            <v>Aston Martin</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18" t="str">
-            <v>Hyundai</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="B19" t="str">
-            <v>Kia</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20" t="str">
-            <v>Renault</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21" t="str">
-            <v>PACCAR</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22" t="str">
-            <v>Geely</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23" t="str">
-            <v>NIO</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="B24" t="str">
-            <v>Subaru</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25" t="str">
-            <v>Nissan</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26" t="str">
-            <v>BYD</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27" t="str">
-            <v>Daimler Trucks</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="B28" t="str">
-            <v>Volvo</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="O3">
-            <v>29.266571548241291</v>
-          </cell>
-          <cell r="U3">
-            <v>1.3971942342652697</v>
-          </cell>
-          <cell r="AB3">
-            <v>-0.21162257953759367</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4" t="str">
-            <v>Walmart</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5" t="str">
-            <v>LVMH</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6" t="str">
-            <v>Hermès</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7" t="str">
-            <v>TKMaxx</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8" t="str">
-            <v>Inditex</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9" t="str">
-            <v>Nike</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="B10" t="str">
-            <v>Kering</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="B11" t="str">
-            <v>Adidas</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="B12" t="str">
-            <v>H&amp;M</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="B13" t="str">
-            <v>Tesco</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="B14" t="str">
-            <v>Lululemon</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="B15" t="str">
-            <v>Next</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="B16" t="str">
-            <v>Levi's</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17" t="str">
-            <v>Phillips-Van Heusen</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="B18" t="str">
-            <v>Ralph Lauren</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="B19" t="str">
-            <v>Burberry</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="B20" t="str">
-            <v>Vanity Fair</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21" t="str">
-            <v>Marks &amp; Spencer</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22" t="str">
-            <v>Capri</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23" t="str">
-            <v>Sainsbury's</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="B24" t="str">
-            <v>Deliveroo</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25" t="str">
-            <v>Foot Locker</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26" t="str">
-            <v>Frasers</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="B27" t="str">
-            <v>Hugo Boss</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="B28" t="str">
-            <v>Guess</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="B29" t="str">
-            <v>HelloFresh</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="B30" t="str">
-            <v>Asos</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="B31" t="str">
-            <v>Boohoo</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="B32" t="str">
-            <v>Superdry</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="B33" t="str">
-            <v>Joules</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="B34" t="str">
-            <v>Mulberry</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="B35" t="str">
-            <v>Gap</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="B36" t="str">
-            <v>Puma</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="B37" t="str">
-            <v>CostCo</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="B38" t="str">
-            <v>A&amp;F</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2140,13 +1774,13 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="S3">
-            <v>30.621705228448555</v>
-          </cell>
-          <cell r="AE3">
-            <v>2.9141040899024544</v>
-          </cell>
-          <cell r="AL3">
-            <v>-0.35905903268240191</v>
+            <v>32.181997252204141</v>
+          </cell>
+          <cell r="AC3">
+            <v>3.1798904197297571</v>
+          </cell>
+          <cell r="AJ3">
+            <v>-0.38474356903907542</v>
           </cell>
         </row>
         <row r="4">
@@ -2191,245 +1825,686 @@
         </row>
         <row r="12">
           <cell r="B12" t="str">
-            <v>General Dynamics</v>
+            <v>TransDigm</v>
           </cell>
         </row>
         <row r="13">
           <cell r="B13" t="str">
-            <v>Rolls Royce</v>
+            <v>General Dynamics</v>
           </cell>
         </row>
         <row r="14">
           <cell r="B14" t="str">
-            <v>Rheinmetall</v>
+            <v>Rolls Royce</v>
           </cell>
         </row>
         <row r="15">
           <cell r="B15" t="str">
-            <v>L3Harris</v>
+            <v>Rheinmetall</v>
           </cell>
         </row>
         <row r="16">
           <cell r="B16" t="str">
-            <v>BAE</v>
+            <v>L3Harris</v>
           </cell>
         </row>
         <row r="17">
           <cell r="B17" t="str">
-            <v>Anduril*</v>
+            <v>BAE</v>
           </cell>
         </row>
         <row r="18">
           <cell r="B18" t="str">
-            <v>Thales</v>
+            <v>Anduril*</v>
           </cell>
         </row>
         <row r="19">
           <cell r="B19" t="str">
-            <v>Dassault</v>
+            <v>Thales</v>
           </cell>
         </row>
         <row r="20">
           <cell r="B20" t="str">
-            <v>Leonardo</v>
+            <v>Saab</v>
           </cell>
         </row>
         <row r="21">
           <cell r="B21" t="str">
-            <v>Leidos</v>
+            <v>Dassault</v>
           </cell>
         </row>
         <row r="22">
           <cell r="B22" t="str">
-            <v>Bombardier</v>
+            <v>Kongsberg</v>
           </cell>
         </row>
         <row r="23">
           <cell r="B23" t="str">
-            <v>Textron</v>
+            <v>Teledyne</v>
           </cell>
         </row>
         <row r="24">
           <cell r="B24" t="str">
-            <v>AeroVironment</v>
+            <v>Leonardo</v>
           </cell>
         </row>
         <row r="25">
           <cell r="B25" t="str">
-            <v>Embraer</v>
+            <v>Curtiss-Wright</v>
           </cell>
         </row>
         <row r="26">
           <cell r="B26" t="str">
-            <v>Kratos</v>
+            <v>Leidos</v>
           </cell>
         </row>
         <row r="27">
           <cell r="B27" t="str">
-            <v>Oshkosh</v>
+            <v>Bombardier</v>
           </cell>
         </row>
         <row r="28">
           <cell r="B28" t="str">
-            <v>Hensoldt</v>
+            <v>Textron</v>
           </cell>
         </row>
         <row r="29">
           <cell r="B29" t="str">
-            <v>Renk</v>
+            <v>Kratos</v>
           </cell>
         </row>
         <row r="30">
           <cell r="B30" t="str">
-            <v>National Presto</v>
+            <v>AeroVironment</v>
           </cell>
         </row>
         <row r="31">
           <cell r="B31" t="str">
-            <v>Red Cat</v>
+            <v>Embraer</v>
           </cell>
         </row>
         <row r="32">
           <cell r="B32" t="str">
-            <v>Unusual Machines</v>
+            <v>Oshkosh</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="B33" t="str">
+            <v>Moog</v>
           </cell>
         </row>
         <row r="34">
           <cell r="B34" t="str">
-            <v>Norinco</v>
+            <v>Melrose</v>
           </cell>
         </row>
         <row r="35">
           <cell r="B35" t="str">
-            <v>SAAB</v>
+            <v>Hensoldt</v>
           </cell>
         </row>
         <row r="36">
           <cell r="B36" t="str">
-            <v>General Atomics*</v>
+            <v>Babcock</v>
           </cell>
         </row>
         <row r="37">
           <cell r="B37" t="str">
-            <v>Archer Aviation</v>
+            <v>Renk</v>
           </cell>
         </row>
         <row r="38">
           <cell r="B38" t="str">
-            <v>Sierra Nevada*</v>
+            <v>Red Cat</v>
           </cell>
         </row>
         <row r="39">
           <cell r="B39" t="str">
-            <v>Patria*</v>
+            <v>National Presto</v>
           </cell>
         </row>
         <row r="40">
           <cell r="B40" t="str">
-            <v>Kongsberg</v>
+            <v>Avio</v>
           </cell>
         </row>
         <row r="41">
           <cell r="B41" t="str">
-            <v>Babcock</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="B42" t="str">
-            <v>GKN*</v>
+            <v>Unusual Machines</v>
           </cell>
         </row>
         <row r="43">
           <cell r="B43" t="str">
-            <v>Melrose</v>
+            <v>Norinco</v>
           </cell>
         </row>
         <row r="44">
           <cell r="B44" t="str">
-            <v>Avio</v>
+            <v>General Atomics*</v>
           </cell>
         </row>
         <row r="45">
           <cell r="B45" t="str">
-            <v>QinetiQ</v>
+            <v>Archer Aviation</v>
           </cell>
         </row>
         <row r="46">
           <cell r="B46" t="str">
-            <v>KNDS*</v>
+            <v>Sierra Nevada*</v>
           </cell>
         </row>
         <row r="47">
           <cell r="B47" t="str">
-            <v>Indra</v>
+            <v>Patria*</v>
           </cell>
         </row>
         <row r="48">
           <cell r="B48" t="str">
-            <v>InQTel*</v>
+            <v>Avio</v>
           </cell>
         </row>
         <row r="49">
           <cell r="B49" t="str">
-            <v>Teledyne</v>
+            <v>QinetiQ</v>
           </cell>
         </row>
         <row r="50">
           <cell r="B50" t="str">
-            <v>Jenoptics</v>
+            <v>KNDS*</v>
           </cell>
         </row>
         <row r="51">
           <cell r="B51" t="str">
-            <v>TransDigm</v>
+            <v>Indra</v>
           </cell>
         </row>
         <row r="52">
           <cell r="B52" t="str">
-            <v>Heico</v>
+            <v>InQTel*</v>
           </cell>
         </row>
         <row r="53">
           <cell r="B53" t="str">
-            <v>Elbit Systems</v>
+            <v>Jenoptics</v>
           </cell>
         </row>
         <row r="54">
           <cell r="B54" t="str">
-            <v>Hyundai WIA</v>
+            <v>Heico</v>
           </cell>
         </row>
         <row r="55">
           <cell r="B55" t="str">
-            <v>SNT Dynamics</v>
+            <v>Elbit Systems</v>
           </cell>
         </row>
         <row r="56">
           <cell r="B56" t="str">
-            <v>Samyang Comtech</v>
+            <v>Hyundai WIA</v>
           </cell>
         </row>
         <row r="57">
           <cell r="B57" t="str">
+            <v>SNT Dynamics</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="B58" t="str">
+            <v>Samyang Comtech</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="B59" t="str">
             <v>ST Engineering</v>
           </cell>
         </row>
+        <row r="60">
+          <cell r="B60" t="str">
+            <v>CSG</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="B61" t="str">
+            <v>Smiths</v>
+          </cell>
+        </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="O3">
+            <v>16.412502823367006</v>
+          </cell>
+          <cell r="U3">
+            <v>1.0405324209773694</v>
+          </cell>
+          <cell r="AA3">
+            <v>-0.21453441990870947</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4" t="str">
+            <v>Tesla</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5" t="str">
+            <v>Toyota</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6" t="str">
+            <v>Volkswagen</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7" t="str">
+            <v>General Motors</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8" t="str">
+            <v>Ford</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9" t="str">
+            <v>Mercedes-Benz</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10" t="str">
+            <v>BMW</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11" t="str">
+            <v>Honda</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12" t="str">
+            <v>Porsche</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13" t="str">
+            <v>Stellantis</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14" t="str">
+            <v>Ferrari</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15" t="str">
+            <v>Rivian</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16" t="str">
+            <v>Lucid</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17" t="str">
+            <v>Aston Martin</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18" t="str">
+            <v>Hyundai</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19" t="str">
+            <v>Kia</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20" t="str">
+            <v>Renault</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21" t="str">
+            <v>PACCAR</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22" t="str">
+            <v>Geely</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23" t="str">
+            <v>NIO</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24" t="str">
+            <v>Subaru</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25" t="str">
+            <v>Nissan</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="B26" t="str">
+            <v>BYD</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27" t="str">
+            <v>Daimler Trucks</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="B28" t="str">
+            <v>Volvo</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="O3">
+            <v>29.266571548241291</v>
+          </cell>
+          <cell r="U3">
+            <v>1.3971942342652697</v>
+          </cell>
+          <cell r="AB3">
+            <v>-0.21162257953759367</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4" t="str">
+            <v>Walmart</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5" t="str">
+            <v>LVMH</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6" t="str">
+            <v>Hermès</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7" t="str">
+            <v>TKMaxx</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8" t="str">
+            <v>Inditex</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9" t="str">
+            <v>Nike</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10" t="str">
+            <v>Kering</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11" t="str">
+            <v>Adidas</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12" t="str">
+            <v>H&amp;M</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13" t="str">
+            <v>Tesco</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14" t="str">
+            <v>Lululemon</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15" t="str">
+            <v>Next</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16" t="str">
+            <v>Levi's</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17" t="str">
+            <v>Phillips-Van Heusen</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18" t="str">
+            <v>Ralph Lauren</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19" t="str">
+            <v>Burberry</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20" t="str">
+            <v>Vanity Fair</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21" t="str">
+            <v>Marks &amp; Spencer</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22" t="str">
+            <v>Capri</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23" t="str">
+            <v>Sainsbury's</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="B24" t="str">
+            <v>Deliveroo</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25" t="str">
+            <v>Foot Locker</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="B26" t="str">
+            <v>Frasers</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="B27" t="str">
+            <v>Hugo Boss</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="B28" t="str">
+            <v>Guess</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="B29" t="str">
+            <v>HelloFresh</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="B30" t="str">
+            <v>Asos</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="B31" t="str">
+            <v>Boohoo</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="B32" t="str">
+            <v>Superdry</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="B33" t="str">
+            <v>Joules</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="B34" t="str">
+            <v>Mulberry</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="B35" t="str">
+            <v>Gap</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="B36" t="str">
+            <v>Puma</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="B37" t="str">
+            <v>CostCo</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="B38" t="str">
+            <v>A&amp;F</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="W3">
+            <v>4.0293530724944189</v>
+          </cell>
+          <cell r="AC3">
+            <v>-0.57825989044158654</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4" t="str">
+            <v>Constellation</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5" t="str">
+            <v>Bloom</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6" t="str">
+            <v>Oklo</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7" t="str">
+            <v>Enphase</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8" t="str">
+            <v>PlugPower</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9" t="str">
+            <v>FuelCell</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10" t="str">
+            <v>NuScale</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11" t="str">
+            <v>General Electric</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2466,58 +2541,6 @@
         <row r="8">
           <cell r="B8" t="str">
             <v>Intuitive Machines</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="AC3">
-            <v>-0.7852827016272812</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="B4" t="str">
-            <v>Constellation</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="B5" t="str">
-            <v>Bloom</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="B6" t="str">
-            <v>Oklo</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="B7" t="str">
-            <v>PlugPower</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="B8" t="str">
-            <v>FuelCell</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="B9" t="str">
-            <v>NuScale</v>
           </cell>
         </row>
       </sheetData>
@@ -2866,27 +2889,27 @@
         <v>0</v>
       </c>
       <c r="C3" s="18">
-        <f>COUNTA([1]Models!$B$7:$B$1048576)</f>
-        <v>80</v>
+        <f>COUNTA([1]Models!$B$9:$B$1048576)</f>
+        <v>78</v>
       </c>
       <c r="D3" s="19">
-        <f>[1]Models!$AA$3</f>
-        <v>-0.16118420686945295</v>
+        <f>[1]Models!$AA$5</f>
+        <v>-0.2173697345984017</v>
       </c>
       <c r="E3" s="21">
-        <f>[1]Models!$N$3</f>
-        <v>26.62062128663548</v>
+        <f>[1]Models!$N$5</f>
+        <v>29.012325792539912</v>
       </c>
       <c r="F3" s="22">
-        <f>[1]Models!$T$3</f>
-        <v>3.687787857781355</v>
+        <f>[1]Models!$T$5</f>
+        <v>9.5189086874062898</v>
       </c>
       <c r="G3" s="15">
         <v>45932</v>
       </c>
       <c r="H3" s="15">
         <f ca="1">TODAY()</f>
-        <v>46066</v>
+        <v>46080</v>
       </c>
       <c r="K3" s="17" t="s">
         <v>7</v>
@@ -2894,68 +2917,68 @@
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B4" s="17" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" s="18">
         <f>COUNTA([2]Main!$B$4:$B$1048576)</f>
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="D4" s="19">
-        <f>[2]Main!$AA$3</f>
-        <v>-0.30225003994070132</v>
+        <f>[2]Main!$AJ$3</f>
+        <v>-0.38474356903907542</v>
       </c>
       <c r="E4" s="21">
-        <f>[2]Main!$O$3</f>
-        <v>16.412502823367006</v>
+        <f>[2]Main!$S$3</f>
+        <v>32.181997252204141</v>
       </c>
       <c r="F4" s="22">
-        <f>[2]Main!$U$3</f>
-        <v>1.0405324209773694</v>
+        <f>[2]Main!$AC$3</f>
+        <v>3.1798904197297571</v>
       </c>
       <c r="K4" s="56" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B5" s="56" t="s">
-        <v>3</v>
+      <c r="B5" s="17" t="s">
+        <v>2</v>
       </c>
       <c r="C5" s="18">
         <f>COUNTA([3]Main!$B$4:$B$1048576)</f>
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D5" s="19">
-        <f>[3]Main!$AB$3</f>
-        <v>-0.21162257953759367</v>
+        <f>[3]Main!$AA$3</f>
+        <v>-0.21453441990870947</v>
       </c>
       <c r="E5" s="21">
         <f>[3]Main!$O$3</f>
-        <v>29.266571548241291</v>
+        <v>16.412502823367006</v>
       </c>
       <c r="F5" s="22">
         <f>[3]Main!$U$3</f>
-        <v>1.3971942342652697</v>
+        <v>1.0405324209773694</v>
       </c>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B6" s="17" t="s">
-        <v>4</v>
+      <c r="B6" s="56" t="s">
+        <v>3</v>
       </c>
       <c r="C6" s="18">
         <f>COUNTA([4]Main!$B$4:$B$1048576)</f>
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="D6" s="19">
-        <f>[4]Main!$AL$3</f>
-        <v>-0.35905903268240191</v>
+        <f>[4]Main!$AB$3</f>
+        <v>-0.21162257953759367</v>
       </c>
       <c r="E6" s="21">
-        <f>[4]Main!$S$3</f>
-        <v>30.621705228448555</v>
+        <f>[4]Main!$O$3</f>
+        <v>29.266571548241291</v>
       </c>
       <c r="F6" s="22">
-        <f>[4]Main!$AE$3</f>
-        <v>2.9141040899024544</v>
+        <f>[4]Main!$U$3</f>
+        <v>1.3971942342652697</v>
       </c>
       <c r="K6" s="12" t="s">
         <v>36</v>
@@ -2964,20 +2987,20 @@
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B7" s="17" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="18">
-        <f>COUNTA([5]Models!$B$5:$B$1048576)</f>
-        <v>4</v>
+        <f>COUNTA([5]Main!$B$4:$B$1048576)</f>
+        <v>8</v>
       </c>
       <c r="D7" s="19">
-        <f>[5]Models!$AB$3</f>
-        <v>-0.65411604990312666</v>
+        <f>[5]Main!$AC$3</f>
+        <v>-0.57825989044158654</v>
       </c>
       <c r="E7" s="21"/>
       <c r="F7" s="22">
-        <f>[5]Models!$V$3</f>
-        <v>28.725219298245612</v>
+        <f>[5]Main!$W$3</f>
+        <v>4.0293530724944189</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>35</v>
@@ -2988,18 +3011,21 @@
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B8" s="17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="18">
-        <f>COUNTA([6]Main!$B$4:$B$1048576)</f>
-        <v>6</v>
+        <f>COUNTA([6]Models!$B$5:$B$1048576)</f>
+        <v>4</v>
       </c>
       <c r="D8" s="19">
-        <f>[6]Main!$AC$3</f>
-        <v>-0.7852827016272812</v>
+        <f>[6]Models!$AB$3</f>
+        <v>-0.65411604990312666</v>
       </c>
       <c r="E8" s="21"/>
-      <c r="F8" s="20"/>
+      <c r="F8" s="22">
+        <f>[6]Models!$V$3</f>
+        <v>28.725219298245612</v>
+      </c>
       <c r="K8" s="1" t="s">
         <v>34</v>
       </c>
@@ -3013,19 +3039,19 @@
     <row r="9" spans="2:15" x14ac:dyDescent="0.3">
       <c r="C9" s="18">
         <f>SUM(C3:C8)</f>
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D9" s="19">
         <f>AVERAGE(D3:D8)</f>
-        <v>-0.41225243509342624</v>
+        <v>-0.37677437390474894</v>
       </c>
       <c r="E9" s="21">
         <f>AVERAGE(E3:E8)</f>
-        <v>25.730350221673085</v>
+        <v>26.718349354088087</v>
       </c>
       <c r="F9" s="22">
         <f>AVERAGE(F3:F8)</f>
-        <v>7.5529675802344114</v>
+        <v>7.9818496888531199</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>33</v>
@@ -3099,11 +3125,11 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{14C9F10C-4241-4381-9A58-C45CBE1D0EC1}"/>
-    <hyperlink ref="B4" r:id="rId2" xr:uid="{956A622F-4129-49E8-B3F9-286229411C4E}"/>
-    <hyperlink ref="B5" r:id="rId3" xr:uid="{89548BBF-66AA-4EED-8862-90CB1E3EFBBF}"/>
-    <hyperlink ref="B6" r:id="rId4" xr:uid="{DE0AC776-4712-4CE4-A502-2FEC545FA729}"/>
-    <hyperlink ref="B7" r:id="rId5" xr:uid="{A17DCD71-EE89-4DC1-A07D-05642306D744}"/>
-    <hyperlink ref="B8" r:id="rId6" xr:uid="{8B455401-3CF0-478F-90EE-4BCE8AFD4668}"/>
+    <hyperlink ref="B5" r:id="rId2" xr:uid="{956A622F-4129-49E8-B3F9-286229411C4E}"/>
+    <hyperlink ref="B6" r:id="rId3" xr:uid="{89548BBF-66AA-4EED-8862-90CB1E3EFBBF}"/>
+    <hyperlink ref="B4" r:id="rId4" xr:uid="{DE0AC776-4712-4CE4-A502-2FEC545FA729}"/>
+    <hyperlink ref="B8" r:id="rId5" xr:uid="{A17DCD71-EE89-4DC1-A07D-05642306D744}"/>
+    <hyperlink ref="B7" r:id="rId6" xr:uid="{8B455401-3CF0-478F-90EE-4BCE8AFD4668}"/>
     <hyperlink ref="K3" r:id="rId7" xr:uid="{119BFD1D-40CB-4E53-88E7-0B54106196A1}"/>
     <hyperlink ref="K4" r:id="rId8" xr:uid="{96C3EF73-BFB4-4813-A0FA-B46F9F5E5121}"/>
   </hyperlinks>
@@ -3247,7 +3273,7 @@
       <c r="N1" s="39"/>
       <c r="O1" s="38">
         <f ca="1">AVERAGE(O3:O106)</f>
-        <v>49.222222222222221</v>
+        <v>50</v>
       </c>
       <c r="P1" s="38">
         <f>AVERAGE(P3:P106)</f>
@@ -5360,11 +5386,11 @@
       </c>
       <c r="N29" s="54">
         <f t="shared" ref="N29:N36" ca="1" si="12">F29+$O$1</f>
-        <v>46013.222222222219</v>
+        <v>46014</v>
       </c>
       <c r="O29" s="43">
         <f ca="1">TODAY()-F29</f>
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="P29" s="28"/>
       <c r="U29" s="29">
@@ -5699,11 +5725,11 @@
       </c>
       <c r="N34" s="54">
         <f ca="1">F34+$O$1</f>
-        <v>46036.222222222219</v>
+        <v>46037</v>
       </c>
       <c r="O34" s="43">
         <f ca="1">TODAY()-F34</f>
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="P34" s="28"/>
       <c r="U34" s="29">
@@ -5828,7 +5854,7 @@
       </c>
       <c r="N36" s="36">
         <f t="shared" ca="1" si="12"/>
-        <v>46087.222222222219</v>
+        <v>46088</v>
       </c>
       <c r="P36" s="28"/>
       <c r="U36" s="29">
@@ -6232,11 +6258,11 @@
       <c r="F1" s="39"/>
       <c r="G1" s="38">
         <f ca="1">AVERAGE(G3:G106)</f>
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="H1" s="38">
         <f ca="1">AVERAGE(H3:H106)</f>
-        <v>37</v>
+        <v>37.875</v>
       </c>
       <c r="I1" s="39"/>
       <c r="J1" s="39"/>
@@ -6370,11 +6396,11 @@
       </c>
       <c r="G3" s="46">
         <f ca="1">TODAY()-D3</f>
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="H3" s="47">
         <f ca="1">G3/E3</f>
-        <v>38.75</v>
+        <v>40.5</v>
       </c>
       <c r="I3" s="48"/>
       <c r="J3" s="48"/>

--- a/Financial Analysis/Models.xlsx
+++ b/Financial Analysis/Models.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EAAB2B4-491A-42EA-8099-9452C35E8369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC00EE9F-C83A-4810-B178-C57E574C3A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{40711DBD-7A53-4994-9FF1-9E754821B18D}"/>
   </bookViews>
@@ -1344,15 +1344,15 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="5">
-          <cell r="N5">
-            <v>29.012325792539912</v>
-          </cell>
-          <cell r="T5">
-            <v>9.5189086874062898</v>
-          </cell>
-          <cell r="AA5">
-            <v>-0.2173697345984017</v>
+        <row r="3">
+          <cell r="N3">
+            <v>26.488441906764592</v>
+          </cell>
+          <cell r="T3">
+            <v>3.4743711614160868</v>
+          </cell>
+          <cell r="AA3">
+            <v>-0.170797740993226</v>
           </cell>
         </row>
         <row r="9">
@@ -1773,13 +1773,13 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="S3">
+          <cell r="R3">
             <v>32.181997252204141</v>
           </cell>
-          <cell r="AC3">
+          <cell r="AB3">
             <v>3.1798904197297571</v>
           </cell>
-          <cell r="AJ3">
+          <cell r="AI3">
             <v>-0.38474356903907542</v>
           </cell>
         </row>
@@ -2069,15 +2069,15 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2893,23 +2893,23 @@
         <v>78</v>
       </c>
       <c r="D3" s="19">
-        <f>[1]Models!$AA$5</f>
-        <v>-0.2173697345984017</v>
+        <f>[1]Models!$AA$3</f>
+        <v>-0.170797740993226</v>
       </c>
       <c r="E3" s="21">
-        <f>[1]Models!$N$5</f>
-        <v>29.012325792539912</v>
+        <f>[1]Models!$N$3</f>
+        <v>26.488441906764592</v>
       </c>
       <c r="F3" s="22">
-        <f>[1]Models!$T$5</f>
-        <v>9.5189086874062898</v>
+        <f>[1]Models!$T$3</f>
+        <v>3.4743711614160868</v>
       </c>
       <c r="G3" s="15">
         <v>45932</v>
       </c>
       <c r="H3" s="15">
         <f ca="1">TODAY()</f>
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="K3" s="17" t="s">
         <v>7</v>
@@ -2924,15 +2924,15 @@
         <v>57</v>
       </c>
       <c r="D4" s="19">
-        <f>[2]Main!$AJ$3</f>
+        <f>[2]Main!$AI$3</f>
         <v>-0.38474356903907542</v>
       </c>
       <c r="E4" s="21">
-        <f>[2]Main!$S$3</f>
+        <f>[2]Main!$R$3</f>
         <v>32.181997252204141</v>
       </c>
       <c r="F4" s="22">
-        <f>[2]Main!$AC$3</f>
+        <f>[2]Main!$AB$3</f>
         <v>3.1798904197297571</v>
       </c>
       <c r="K4" s="56" t="s">
@@ -3043,15 +3043,15 @@
       </c>
       <c r="D9" s="19">
         <f>AVERAGE(D3:D8)</f>
-        <v>-0.37677437390474894</v>
+        <v>-0.36901237497055295</v>
       </c>
       <c r="E9" s="21">
         <f>AVERAGE(E3:E8)</f>
-        <v>26.718349354088087</v>
+        <v>26.087378382644257</v>
       </c>
       <c r="F9" s="22">
         <f>AVERAGE(F3:F8)</f>
-        <v>7.9818496888531199</v>
+        <v>6.9744267678547516</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>33</v>
@@ -3273,7 +3273,7 @@
       <c r="N1" s="39"/>
       <c r="O1" s="38">
         <f ca="1">AVERAGE(O3:O106)</f>
-        <v>50</v>
+        <v>50.166666666666664</v>
       </c>
       <c r="P1" s="38">
         <f>AVERAGE(P3:P106)</f>
@@ -5386,11 +5386,11 @@
       </c>
       <c r="N29" s="54">
         <f t="shared" ref="N29:N36" ca="1" si="12">F29+$O$1</f>
-        <v>46014</v>
+        <v>46014.166666666664</v>
       </c>
       <c r="O29" s="43">
         <f ca="1">TODAY()-F29</f>
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="P29" s="28"/>
       <c r="U29" s="29">
@@ -5725,11 +5725,11 @@
       </c>
       <c r="N34" s="54">
         <f ca="1">F34+$O$1</f>
-        <v>46037</v>
+        <v>46037.166666666664</v>
       </c>
       <c r="O34" s="43">
         <f ca="1">TODAY()-F34</f>
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="P34" s="28"/>
       <c r="U34" s="29">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="N36" s="36">
         <f t="shared" ca="1" si="12"/>
-        <v>46088</v>
+        <v>46088.166666666664</v>
       </c>
       <c r="P36" s="28"/>
       <c r="U36" s="29">
@@ -6258,11 +6258,11 @@
       <c r="F1" s="39"/>
       <c r="G1" s="38">
         <f ca="1">AVERAGE(G3:G106)</f>
-        <v>303</v>
+        <v>304.5</v>
       </c>
       <c r="H1" s="38">
         <f ca="1">AVERAGE(H3:H106)</f>
-        <v>37.875</v>
+        <v>38.0625</v>
       </c>
       <c r="I1" s="39"/>
       <c r="J1" s="39"/>
@@ -6396,11 +6396,11 @@
       </c>
       <c r="G3" s="46">
         <f ca="1">TODAY()-D3</f>
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="H3" s="47">
         <f ca="1">G3/E3</f>
-        <v>40.5</v>
+        <v>40.875</v>
       </c>
       <c r="I3" s="48"/>
       <c r="J3" s="48"/>
